--- a/VNL Feminina 2025.xlsx
+++ b/VNL Feminina 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mjunior\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31FC7C25-9EAB-4800-A133-A9FC5927D24A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA85BE2B-F53B-4B17-87AC-CD81FBCE7255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="CC01" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="1" activeTab="1" xr2:uid="{701403F6-3112-456D-B33A-FC5595D41656}"/>
@@ -19,7 +19,6 @@
     <sheet name="Finais" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -630,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -808,7 +807,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -820,6 +831,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -829,32 +843,26 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="81">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2018,18 +2026,18 @@
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>RANK(E3,$E$3:$E$20)+SUM(S3:V3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="1">
         <f>SUM(G3*3,H3*3,I3*2,J3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1">
         <f>E3+F3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B3)</f>
@@ -2037,7 +2045,7 @@
       </c>
       <c r="F3" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B3,Jogos!AF:AF)</f>
@@ -2053,7 +2061,7 @@
       </c>
       <c r="J3" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B3,Jogos!AP:AP)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B3,Jogos!AQ:AQ)</f>
@@ -2065,27 +2073,27 @@
       </c>
       <c r="M3" s="1">
         <f>SUMIF(Jogos!AB:AB,B3,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B3,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N3" s="1">
         <f>SUMIF(Jogos!AB:AB,B3,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B3,Jogos!AO:AO)</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="15" t="str">
+        <v>3</v>
+      </c>
+      <c r="O3" s="15">
         <f>IFERROR((M3/N3)*1000,"MAX")</f>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="P3" s="1">
         <f>SUMIF(Jogos!AB:AB,B3,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B3,Jogos!AS:AS)</f>
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="1">
         <f>SUMIF(Jogos!AB:AB,B3,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B3,Jogos!AT:AT)</f>
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="R3" s="15">
         <f t="shared" ref="R3:R20" si="0">IFERROR((P3/Q3)*1000,"MAX")</f>
-        <v>1415.0943396226414</v>
+        <v>981.25</v>
       </c>
       <c r="S3" s="1">
         <f>SUMPRODUCT(($E$3:$E$20=E3)*($C$3:$C$20&gt;C3))</f>
@@ -2097,7 +2105,7 @@
       </c>
       <c r="U3" s="1">
         <f>SUMPRODUCT(($E$3:$E$20=E3)*($C$3:$C$20=C3)*($O$3:$O$20=O3)*($R$3:$R$20&gt;R3))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1">
         <f>SUMPRODUCT(($E$3:$E$20=E3)*($C$3:$C$20=C3)*($O$3:$O$20=O3)*($R$3:$R$20=R3)*($W$3:$W$20&lt;W3))</f>
@@ -2121,22 +2129,22 @@
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A20" si="1">RANK(E4,$E$3:$E$20)+SUM(S4:V4)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="2">SUM(G4*3,H4*3,I4*2,J4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" ref="D4:D20" si="3">E4+F4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B4)</f>
@@ -2148,7 +2156,7 @@
       </c>
       <c r="H4" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B4,Jogos!AG:AG)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B4,Jogos!AH:AH)</f>
@@ -2168,27 +2176,27 @@
       </c>
       <c r="M4" s="1">
         <f>SUMIF(Jogos!AB:AB,B4,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B4,Jogos!AN:AN)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" s="1">
         <f>SUMIF(Jogos!AB:AB,B4,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B4,Jogos!AO:AO)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" s="15">
         <f t="shared" ref="O4:O20" si="4">IFERROR((M4/N4)*1000,"MAX")</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="P4" s="1">
         <f>SUMIF(Jogos!AB:AB,B4,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B4,Jogos!AS:AS)</f>
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="Q4" s="1">
         <f>SUMIF(Jogos!AB:AB,B4,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B4,Jogos!AT:AT)</f>
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="R4" s="15">
         <f t="shared" si="0"/>
-        <v>727.27272727272725</v>
+        <v>911.76470588235293</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" ref="S4:S20" si="5">SUMPRODUCT(($E$3:$E$20=E4)*($C$3:$C$20&gt;C4))</f>
@@ -2196,11 +2204,11 @@
       </c>
       <c r="T4" s="1">
         <f t="shared" ref="T4:T20" si="6">SUMPRODUCT(($E$3:$E$20=E4)*($C$3:$C$20=C4)*($O$3:$O$20&gt;O4))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" ref="U4:U20" si="7">SUMPRODUCT(($E$3:$E$20=E4)*($C$3:$C$20=C4)*($O$3:$O$20=O4)*($R$3:$R$20&gt;R4))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4" s="1">
         <f t="shared" ref="V4:V20" si="8">SUMPRODUCT(($E$3:$E$20=E4)*($C$3:$C$20=C4)*($O$3:$O$20=O4)*($R$3:$R$20=R4)*($W$3:$W$20&lt;W4))</f>
@@ -2214,28 +2222,28 @@
       </c>
       <c r="Z4" s="1">
         <f t="shared" ref="Z4:Z9" si="9">IF(Y4&gt;=$A$16,Y4+$AA$3,Y4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B5)</f>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="G5" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B5,Jogos!AF:AF)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B5,Jogos!AG:AG)</f>
@@ -2267,7 +2275,7 @@
       </c>
       <c r="M5" s="1">
         <f>SUMIF(Jogos!AB:AB,B5,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B5,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" s="1">
         <f>SUMIF(Jogos!AB:AB,B5,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B5,Jogos!AO:AO)</f>
@@ -2279,15 +2287,15 @@
       </c>
       <c r="P5" s="1">
         <f>SUMIF(Jogos!AB:AB,B5,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B5,Jogos!AS:AS)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q5" s="1">
         <f>SUMIF(Jogos!AB:AB,B5,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B5,Jogos!AT:AT)</f>
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="R5" s="15">
         <f t="shared" si="0"/>
-        <v>1293.1034482758621</v>
+        <v>1339.2857142857142</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="5"/>
@@ -2299,7 +2307,7 @@
       </c>
       <c r="U5" s="1">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="8"/>
@@ -2313,28 +2321,28 @@
       </c>
       <c r="Z5" s="1">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B6)</f>
@@ -2346,7 +2354,7 @@
       </c>
       <c r="H6" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B6,Jogos!AG:AG)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B6,Jogos!AH:AH)</f>
@@ -2366,27 +2374,27 @@
       </c>
       <c r="M6" s="1">
         <f>SUMIF(Jogos!AB:AB,B6,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B6,Jogos!AN:AN)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N6" s="1">
         <f>SUMIF(Jogos!AB:AB,B6,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B6,Jogos!AO:AO)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" s="15">
         <f t="shared" si="4"/>
-        <v>666.66666666666663</v>
+        <v>1250</v>
       </c>
       <c r="P6" s="1">
         <f>SUMIF(Jogos!AB:AB,B6,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B6,Jogos!AS:AS)</f>
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="Q6" s="1">
         <f>SUMIF(Jogos!AB:AB,B6,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B6,Jogos!AT:AT)</f>
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="R6" s="15">
         <f t="shared" si="0"/>
-        <v>785.04672897196258</v>
+        <v>958.90410958904101</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="5"/>
@@ -2394,11 +2402,11 @@
       </c>
       <c r="T6" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" si="8"/>
@@ -2412,13 +2420,13 @@
       </c>
       <c r="Z6" s="1">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>51</v>
@@ -2429,7 +2437,7 @@
       </c>
       <c r="D7" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B7)</f>
@@ -2437,7 +2445,7 @@
       </c>
       <c r="F7" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B7,Jogos!AF:AF)</f>
@@ -2457,7 +2465,7 @@
       </c>
       <c r="K7" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B7,Jogos!AQ:AQ)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B7,Jogos!AR:AR)</f>
@@ -2465,27 +2473,27 @@
       </c>
       <c r="M7" s="1">
         <f>SUMIF(Jogos!AB:AB,B7,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B7,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" s="1">
         <f>SUMIF(Jogos!AB:AB,B7,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B7,Jogos!AO:AO)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O7" s="15">
         <f t="shared" si="4"/>
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="P7" s="1">
         <f>SUMIF(Jogos!AB:AB,B7,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B7,Jogos!AS:AS)</f>
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="Q7" s="1">
         <f>SUMIF(Jogos!AB:AB,B7,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B7,Jogos!AT:AT)</f>
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="R7" s="15">
         <f t="shared" si="0"/>
-        <v>1273.8095238095236</v>
+        <v>1038.6740331491712</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" si="5"/>
@@ -2511,13 +2519,13 @@
       </c>
       <c r="Z7" s="1">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>59</v>
@@ -2588,15 +2596,15 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="1">
         <f t="shared" si="8"/>
@@ -2616,7 +2624,7 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>53</v>
@@ -2627,7 +2635,7 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B9)</f>
@@ -2635,7 +2643,7 @@
       </c>
       <c r="F9" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B9,Jogos!AF:AF)</f>
@@ -2655,7 +2663,7 @@
       </c>
       <c r="K9" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B9,Jogos!AQ:AQ)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B9,Jogos!AR:AR)</f>
@@ -2663,39 +2671,39 @@
       </c>
       <c r="M9" s="1">
         <f>SUMIF(Jogos!AB:AB,B9,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B9,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" s="1">
         <f>SUMIF(Jogos!AB:AB,B9,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B9,Jogos!AO:AO)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="15" t="str">
+        <v>3</v>
+      </c>
+      <c r="O9" s="15">
         <f t="shared" si="4"/>
-        <v>MAX</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="P9" s="1">
         <f>SUMIF(Jogos!AB:AB,B9,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B9,Jogos!AS:AS)</f>
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="Q9" s="1">
         <f>SUMIF(Jogos!AB:AB,B9,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B9,Jogos!AT:AT)</f>
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="R9" s="15">
         <f t="shared" si="0"/>
-        <v>1375</v>
+        <v>1086.0927152317881</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" s="1">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" s="1">
         <f t="shared" si="8"/>
@@ -2715,7 +2723,7 @@
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>54</v>
@@ -2786,15 +2794,15 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" s="1">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V10" s="1">
         <f t="shared" si="8"/>
@@ -2807,7 +2815,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>55</v>
@@ -2818,7 +2826,7 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B11)</f>
@@ -2826,7 +2834,7 @@
       </c>
       <c r="F11" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B11,Jogos!AF:AF)</f>
@@ -2850,7 +2858,7 @@
       </c>
       <c r="L11" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B11,Jogos!AR:AR)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="1">
         <f>SUMIF(Jogos!AB:AB,B11,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B11,Jogos!AN:AN)</f>
@@ -2858,7 +2866,7 @@
       </c>
       <c r="N11" s="1">
         <f>SUMIF(Jogos!AB:AB,B11,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B11,Jogos!AO:AO)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O11" s="15">
         <f t="shared" si="4"/>
@@ -2866,27 +2874,27 @@
       </c>
       <c r="P11" s="1">
         <f>SUMIF(Jogos!AB:AB,B11,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B11,Jogos!AS:AS)</f>
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="Q11" s="1">
         <f>SUMIF(Jogos!AB:AB,B11,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B11,Jogos!AT:AT)</f>
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="R11" s="15">
         <f t="shared" si="0"/>
-        <v>675</v>
+        <v>696.77419354838707</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V11" s="1">
         <f t="shared" si="8"/>
@@ -2899,7 +2907,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>41</v>
@@ -2970,7 +2978,7 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="6"/>
@@ -2991,22 +2999,22 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B13)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B13)</f>
@@ -3022,7 +3030,7 @@
       </c>
       <c r="I13" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B13,Jogos!AH:AH)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B13,Jogos!AP:AP)</f>
@@ -3038,31 +3046,31 @@
       </c>
       <c r="M13" s="1">
         <f>SUMIF(Jogos!AB:AB,B13,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B13,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13" s="1">
         <f>SUMIF(Jogos!AB:AB,B13,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B13,Jogos!AO:AO)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="15" t="str">
+        <v>2</v>
+      </c>
+      <c r="O13" s="15">
         <f t="shared" si="4"/>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="P13" s="1">
         <f>SUMIF(Jogos!AB:AB,B13,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B13,Jogos!AS:AS)</f>
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Q13" s="1">
         <f>SUMIF(Jogos!AB:AB,B13,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B13,Jogos!AT:AT)</f>
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="R13" s="15">
         <f t="shared" si="0"/>
-        <v>1481.4814814814813</v>
+        <v>1375</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" si="6"/>
@@ -3070,7 +3078,7 @@
       </c>
       <c r="U13" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" si="8"/>
@@ -3083,7 +3091,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>29</v>
@@ -3154,7 +3162,7 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="6"/>
@@ -3175,22 +3183,22 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B15)</f>
@@ -3202,7 +3210,7 @@
       </c>
       <c r="H15" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B15,Jogos!AG:AG)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B15,Jogos!AH:AH)</f>
@@ -3222,27 +3230,27 @@
       </c>
       <c r="M15" s="1">
         <f>SUMIF(Jogos!AB:AB,B15,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B15,Jogos!AN:AN)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" s="1">
         <f>SUMIF(Jogos!AB:AB,B15,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B15,Jogos!AO:AO)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="P15" s="1">
         <f>SUMIF(Jogos!AB:AB,B15,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B15,Jogos!AS:AS)</f>
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="Q15" s="1">
         <f>SUMIF(Jogos!AB:AB,B15,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B15,Jogos!AT:AT)</f>
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="R15" s="15">
         <f t="shared" si="0"/>
-        <v>640</v>
+        <v>929.48717948717956</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="5"/>
@@ -3250,11 +3258,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" si="8"/>
@@ -3267,22 +3275,22 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B16)</f>
@@ -3294,7 +3302,7 @@
       </c>
       <c r="H16" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B16,Jogos!AG:AG)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B16,Jogos!AH:AH)</f>
@@ -3314,27 +3322,27 @@
       </c>
       <c r="M16" s="1">
         <f>SUMIF(Jogos!AB:AB,B16,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B16,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N16" s="1">
         <f>SUMIF(Jogos!AB:AB,B16,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B16,Jogos!AO:AO)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="str">
+        <v>1</v>
+      </c>
+      <c r="O16" s="15">
         <f t="shared" si="4"/>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="P16" s="1">
         <f>SUMIF(Jogos!AB:AB,B16,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B16,Jogos!AS:AS)</f>
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="Q16" s="1">
         <f>SUMIF(Jogos!AB:AB,B16,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B16,Jogos!AT:AT)</f>
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="R16" s="15">
         <f t="shared" si="0"/>
-        <v>1117.6470588235295</v>
+        <v>1103.2258064516129</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="5"/>
@@ -3342,11 +3350,11 @@
       </c>
       <c r="T16" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" si="8"/>
@@ -3359,7 +3367,7 @@
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>56</v>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B17)</f>
@@ -3378,7 +3386,7 @@
       </c>
       <c r="F17" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B17)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B17,Jogos!AF:AF)</f>
@@ -3398,7 +3406,7 @@
       </c>
       <c r="K17" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B17,Jogos!AQ:AQ)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B17,Jogos!AR:AR)</f>
@@ -3406,27 +3414,27 @@
       </c>
       <c r="M17" s="1">
         <f>SUMIF(Jogos!AB:AB,B17,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B17,Jogos!AN:AN)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="1">
         <f>SUMIF(Jogos!AB:AB,B17,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B17,Jogos!AO:AO)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O17" s="15">
         <f t="shared" si="4"/>
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="P17" s="1">
         <f>SUMIF(Jogos!AB:AB,B17,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B17,Jogos!AS:AS)</f>
-        <v>113</v>
+        <v>225</v>
       </c>
       <c r="Q17" s="1">
         <f>SUMIF(Jogos!AB:AB,B17,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B17,Jogos!AT:AT)</f>
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="R17" s="15">
         <f t="shared" si="0"/>
-        <v>1086.5384615384614</v>
+        <v>978.26086956521738</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" si="5"/>
@@ -3451,7 +3459,7 @@
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>57</v>
@@ -3543,7 +3551,7 @@
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>58</v>
@@ -3554,7 +3562,7 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1">
         <f>COUNTIF(Jogos!AB:AB,Dummy!B19)</f>
@@ -3562,7 +3570,7 @@
       </c>
       <c r="F19" s="1">
         <f>COUNTIF(Jogos!AL:AL,Dummy!B19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
         <f>SUMIF(Jogos!$AB:$AB,Dummy!$B19,Jogos!AF:AF)</f>
@@ -3582,7 +3590,7 @@
       </c>
       <c r="K19" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B19,Jogos!AQ:AQ)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="1">
         <f>SUMIF(Jogos!$AL:$AL,Dummy!$B19,Jogos!AR:AR)</f>
@@ -3590,31 +3598,31 @@
       </c>
       <c r="M19" s="1">
         <f>SUMIF(Jogos!AB:AB,B19,Jogos!AD:AD)+SUMIF(Jogos!AL:AL,B19,Jogos!AN:AN)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="1">
         <f>SUMIF(Jogos!AB:AB,B19,Jogos!AE:AE)+SUMIF(Jogos!AL:AL,B19,Jogos!AO:AO)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O19" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="P19" s="1">
         <f>SUMIF(Jogos!AB:AB,B19,Jogos!AI:AI)+SUMIF(Jogos!AL:AL,B19,Jogos!AS:AS)</f>
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="Q19" s="1">
         <f>SUMIF(Jogos!AB:AB,B19,Jogos!AJ:AJ)+SUMIF(Jogos!AL:AL,B19,Jogos!AT:AT)</f>
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="R19" s="15">
         <f t="shared" si="0"/>
-        <v>894.73684210526312</v>
+        <v>920</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" si="6"/>
@@ -3706,11 +3714,11 @@
       </c>
       <c r="S20" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U20" s="1">
         <f t="shared" si="7"/>
@@ -3835,7 +3843,7 @@
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f>RANK(E27,$E$27:$E$34)+SUM(S27:V27)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B27" s="1" t="str">
         <f>Z1</f>
@@ -3843,15 +3851,15 @@
       </c>
       <c r="C27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,2,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,5,FALSE)</f>
@@ -3863,7 +3871,7 @@
       </c>
       <c r="H27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,8,FALSE)</f>
@@ -3883,27 +3891,27 @@
       </c>
       <c r="M27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,12,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,13,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="36" t="str">
+        <v>1</v>
+      </c>
+      <c r="O27" s="36">
         <f>VLOOKUP($B27,$B$3:$R$20,14,FALSE)</f>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,15,FALSE)</f>
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="Q27" s="1">
         <f>VLOOKUP($B27,$B$3:$R$20,16,FALSE)</f>
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="R27" s="36">
         <f>VLOOKUP($B27,$B$3:$R$20,17,FALSE)</f>
-        <v>1117.6470588235295</v>
+        <v>1103.2258064516129</v>
       </c>
       <c r="S27" s="1">
         <f>SUMPRODUCT(($E$27:$E$34=E27)*($C$27:$C$34&gt;C27))</f>
@@ -3911,11 +3919,11 @@
       </c>
       <c r="T27" s="1">
         <f>SUMPRODUCT(($E$27:$E$34=E27)*($C$27:$C$34=C27)*($O$27:$O$34&gt;O27))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" s="1">
         <f>SUMPRODUCT(($E$27:$E$34=E27)*($C$27:$C$34=C27)*($O$27:$O$34=O27)*($R$27:$R$34&gt;R27))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V27" s="1">
         <f>SUMPRODUCT(($E$27:$E$34=E27)*($C$27:$C$34=C27)*($O$27:$O$34=O27)*($R$27:$R$34=R27)*($W$27:$W$34&lt;W27))</f>
@@ -3932,19 +3940,19 @@
       </c>
       <c r="B28" s="1" t="str">
         <f>VLOOKUP(Z3,$A$3:$R$20,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" ref="C28:C34" si="11">VLOOKUP($B28,$B$3:$R$20,2,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" ref="D28:D34" si="12">VLOOKUP($B28,$B$3:$R$20,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" ref="E28:E34" si="13">VLOOKUP($B28,$B$3:$R$20,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" ref="F28:F34" si="14">VLOOKUP($B28,$B$3:$R$20,5,FALSE)</f>
@@ -3952,7 +3960,7 @@
       </c>
       <c r="G28" s="1">
         <f t="shared" ref="G28:G34" si="15">VLOOKUP($B28,$B$3:$R$20,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" ref="H28:H34" si="16">VLOOKUP($B28,$B$3:$R$20,7,FALSE)</f>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="M28" s="1">
         <f t="shared" ref="M28:M34" si="21">VLOOKUP($B28,$B$3:$R$20,12,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" ref="N28:N34" si="22">VLOOKUP($B28,$B$3:$R$20,13,FALSE)</f>
@@ -3988,15 +3996,15 @@
       </c>
       <c r="P28" s="1">
         <f t="shared" ref="P28:P34" si="24">VLOOKUP($B28,$B$3:$R$20,15,FALSE)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" ref="Q28:Q34" si="25">VLOOKUP($B28,$B$3:$R$20,16,FALSE)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="R28" s="36">
         <f t="shared" ref="R28:R34" si="26">VLOOKUP($B28,$B$3:$R$20,17,FALSE)</f>
-        <v>1562.5</v>
+        <v>1339.2857142857142</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" ref="S28:S34" si="27">SUMPRODUCT(($E$27:$E$34=E28)*($C$27:$C$34&gt;C28))</f>
@@ -4021,7 +4029,7 @@
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" s="1" t="str">
         <f t="shared" ref="B29:B34" si="31">VLOOKUP(Z4,$A$3:$R$20,2,FALSE)</f>
@@ -4029,15 +4037,15 @@
       </c>
       <c r="C29" s="1">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" si="14"/>
@@ -4053,7 +4061,7 @@
       </c>
       <c r="I29" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="18"/>
@@ -4069,31 +4077,31 @@
       </c>
       <c r="M29" s="1">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="36" t="str">
+        <v>2</v>
+      </c>
+      <c r="O29" s="36">
         <f t="shared" si="23"/>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" si="24"/>
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" si="25"/>
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="R29" s="36">
         <f t="shared" si="26"/>
-        <v>1481.4814814814813</v>
+        <v>1375</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" si="28"/>
@@ -4101,7 +4109,7 @@
       </c>
       <c r="U29" s="1">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="1">
         <f t="shared" si="30"/>
@@ -4114,7 +4122,7 @@
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="1" t="str">
         <f t="shared" si="31"/>
@@ -4122,11 +4130,11 @@
       </c>
       <c r="C30" s="1">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="13"/>
@@ -4134,7 +4142,7 @@
       </c>
       <c r="F30" s="1">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="15"/>
@@ -4150,7 +4158,7 @@
       </c>
       <c r="J30" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="19"/>
@@ -4162,27 +4170,27 @@
       </c>
       <c r="M30" s="1">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="36" t="str">
+        <v>3</v>
+      </c>
+      <c r="O30" s="36">
         <f t="shared" si="23"/>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" si="24"/>
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="25"/>
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="R30" s="36">
         <f t="shared" si="26"/>
-        <v>1415.0943396226414</v>
+        <v>981.25</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" si="27"/>
@@ -4194,7 +4202,7 @@
       </c>
       <c r="U30" s="1">
         <f t="shared" si="29"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" s="1">
         <f t="shared" si="30"/>
@@ -4207,19 +4215,19 @@
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>China</v>
+        <v>Bulgária</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="13"/>
@@ -4227,15 +4235,15 @@
       </c>
       <c r="F31" s="1">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="17"/>
@@ -4243,7 +4251,7 @@
       </c>
       <c r="J31" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="19"/>
@@ -4255,27 +4263,27 @@
       </c>
       <c r="M31" s="1">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="36" t="str">
+        <v>4</v>
+      </c>
+      <c r="O31" s="36">
         <f t="shared" si="23"/>
-        <v>MAX</v>
+        <v>1250</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" si="24"/>
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" si="25"/>
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="R31" s="36">
         <f t="shared" si="26"/>
-        <v>1375</v>
+        <v>958.90410958904101</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" si="27"/>
@@ -4283,11 +4291,11 @@
       </c>
       <c r="T31" s="1">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="1">
         <f t="shared" si="29"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V31" s="1">
         <f t="shared" si="30"/>
@@ -4300,11 +4308,11 @@
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>Brasil</v>
+        <v>Japão</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="11"/>
@@ -4364,15 +4372,15 @@
       </c>
       <c r="Q32" s="1">
         <f t="shared" si="25"/>
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="R32" s="36">
         <f t="shared" si="26"/>
-        <v>1293.1034482758621</v>
+        <v>1562.5</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T32" s="1">
         <f t="shared" si="28"/>
@@ -4380,7 +4388,7 @@
       </c>
       <c r="U32" s="1">
         <f t="shared" si="29"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32" s="1">
         <f t="shared" si="30"/>
@@ -4465,11 +4473,11 @@
       </c>
       <c r="S33" s="1">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" si="28"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U33" s="1">
         <f t="shared" si="29"/>
@@ -4490,15 +4498,15 @@
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="13"/>
@@ -4506,11 +4514,11 @@
       </c>
       <c r="F34" s="1">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="16"/>
@@ -4518,7 +4526,7 @@
       </c>
       <c r="I34" s="1">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="18"/>
@@ -4526,7 +4534,7 @@
       </c>
       <c r="K34" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="20"/>
@@ -4534,35 +4542,35 @@
       </c>
       <c r="M34" s="1">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" s="36">
         <f t="shared" si="23"/>
-        <v>1500</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" si="24"/>
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" si="25"/>
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="R34" s="36">
         <f t="shared" si="26"/>
-        <v>1273.8095238095236</v>
+        <v>1086.0927152317881</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T34" s="1">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="1">
         <f t="shared" si="29"/>
@@ -4582,11 +4590,11 @@
       </c>
       <c r="B37" s="1" t="str">
         <f>VLOOKUP($A37,$A$27:$D$34,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="C37" s="1">
         <f>VLOOKUP($A37,$A$27:$D$34,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
@@ -4595,11 +4603,11 @@
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" ref="B38:B44" si="32">VLOOKUP($A38,$A$27:$D$34,2,FALSE)</f>
-        <v>Itália</v>
+        <v>Polônia</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" ref="C38:C44" si="33">VLOOKUP($A38,$A$27:$D$34,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -4608,11 +4616,11 @@
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>Alemanha</v>
+        <v>Itália</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
@@ -4621,11 +4629,11 @@
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>China</v>
+        <v>Alemanha</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
@@ -4634,11 +4642,11 @@
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>Brasil</v>
+        <v>Bulgária</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
@@ -4647,7 +4655,7 @@
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>Polônia</v>
+        <v>Japão</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" si="33"/>
@@ -4673,25 +4681,25 @@
       </c>
       <c r="B44" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="C44" s="1">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="S1:W1"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:L25"/>
     <mergeCell ref="M25:O25"/>
     <mergeCell ref="P25:R25"/>
     <mergeCell ref="S25:W25"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="S1:W1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4755,88 +4763,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="AU2" s="62" t="s">
+      <c r="B2" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="AU2" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="AV2" s="63"/>
-      <c r="AW2" s="64"/>
-      <c r="AX2" s="62" t="s">
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="69"/>
+      <c r="AX2" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="AY2" s="63"/>
-      <c r="AZ2" s="64"/>
-      <c r="BA2" s="62" t="s">
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="69"/>
+      <c r="BA2" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="BB2" s="63"/>
-      <c r="BC2" s="63"/>
-      <c r="BD2" s="63"/>
-      <c r="BE2" s="63"/>
-      <c r="BF2" s="64"/>
-      <c r="BG2" s="62" t="s">
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="68"/>
+      <c r="BD2" s="68"/>
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="69"/>
+      <c r="BG2" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="BH2" s="63"/>
-      <c r="BI2" s="64"/>
-      <c r="BJ2" s="62" t="s">
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="69"/>
+      <c r="BJ2" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="BK2" s="63"/>
-      <c r="BL2" s="64"/>
+      <c r="BK2" s="68"/>
+      <c r="BL2" s="69"/>
     </row>
     <row r="3" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
+      <c r="B3" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
       <c r="AU3" s="32" t="s">
         <v>43</v>
       </c>
@@ -4897,42 +4905,42 @@
         <v>2</v>
       </c>
       <c r="C4" s="24"/>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
       <c r="G4" s="20"/>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67" t="s">
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67" t="s">
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67" t="s">
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67" t="s">
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67" t="s">
+      <c r="U4" s="58"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
       <c r="AA4" s="4" t="s">
         <v>38</v>
       </c>
@@ -4995,19 +5003,19 @@
       </c>
       <c r="AV4" s="30" t="str">
         <f>VLOOKUP($AU4,Dummy!$A:$R,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="AW4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,6,FALSE)</f>
@@ -5015,7 +5023,7 @@
       </c>
       <c r="BA4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,8,FALSE)</f>
@@ -5039,7 +5047,7 @@
       </c>
       <c r="BG4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,14,FALSE)</f>
@@ -5051,15 +5059,15 @@
       </c>
       <c r="BJ4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BK4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,17,FALSE)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="BL4" s="29">
         <f>VLOOKUP($AU4,Dummy!$A:$R,18,FALSE)</f>
-        <v>1562.5</v>
+        <v>1339.2857142857142</v>
       </c>
     </row>
     <row r="5" spans="2:64" x14ac:dyDescent="0.25">
@@ -5210,19 +5218,19 @@
       </c>
       <c r="AV5" s="30" t="str">
         <f>VLOOKUP($AU5,Dummy!$A:$R,2,FALSE)</f>
-        <v>Itália</v>
+        <v>Polônia</v>
       </c>
       <c r="AW5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,6,FALSE)</f>
@@ -5234,7 +5242,7 @@
       </c>
       <c r="BB5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,9,FALSE)</f>
@@ -5254,27 +5262,27 @@
       </c>
       <c r="BG5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI5" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="BI5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="BJ5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,16,FALSE)</f>
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="BK5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,17,FALSE)</f>
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="BL5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,18,FALSE)</f>
-        <v>1481.4814814814813</v>
+        <v>1103.2258064516129</v>
       </c>
     </row>
     <row r="6" spans="2:64" x14ac:dyDescent="0.25">
@@ -5433,19 +5441,19 @@
       </c>
       <c r="AV6" s="30" t="str">
         <f>VLOOKUP($AU6,Dummy!$A:$R,2,FALSE)</f>
-        <v>Alemanha</v>
+        <v>Itália</v>
       </c>
       <c r="AW6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,6,FALSE)</f>
@@ -5461,7 +5469,7 @@
       </c>
       <c r="BC6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,10,FALSE)</f>
@@ -5477,27 +5485,27 @@
       </c>
       <c r="BG6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI6" s="29" t="str">
+        <v>2</v>
+      </c>
+      <c r="BI6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="BJ6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="BK6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,17,FALSE)</f>
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="BL6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,18,FALSE)</f>
-        <v>1415.0943396226414</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7" spans="2:64" x14ac:dyDescent="0.25">
@@ -5656,15 +5664,15 @@
       </c>
       <c r="AV7" s="30" t="str">
         <f>VLOOKUP($AU7,Dummy!$A:$R,2,FALSE)</f>
-        <v>China</v>
+        <v>Alemanha</v>
       </c>
       <c r="AW7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,5,FALSE)</f>
@@ -5672,7 +5680,7 @@
       </c>
       <c r="AZ7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,7,FALSE)</f>
@@ -5688,7 +5696,7 @@
       </c>
       <c r="BD7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,11,FALSE)</f>
@@ -5700,27 +5708,27 @@
       </c>
       <c r="BG7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI7" s="29" t="str">
+        <v>3</v>
+      </c>
+      <c r="BI7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="BJ7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,16,FALSE)</f>
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="BK7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,17,FALSE)</f>
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="BL7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,18,FALSE)</f>
-        <v>1375</v>
+        <v>981.25</v>
       </c>
     </row>
     <row r="8" spans="2:64" x14ac:dyDescent="0.25">
@@ -5730,37 +5738,53 @@
       <c r="C8" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="33">
+        <v>3</v>
+      </c>
       <c r="E8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="34"/>
+      <c r="F8" s="34">
+        <v>1</v>
+      </c>
       <c r="G8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="33"/>
+      <c r="H8" s="33">
+        <v>25</v>
+      </c>
       <c r="I8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="33"/>
+      <c r="J8" s="34">
+        <v>21</v>
+      </c>
+      <c r="K8" s="33">
+        <v>30</v>
+      </c>
       <c r="L8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="33"/>
+      <c r="M8" s="34">
+        <v>32</v>
+      </c>
+      <c r="N8" s="33">
+        <v>25</v>
+      </c>
       <c r="O8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="34"/>
+      <c r="P8" s="34">
+        <v>19</v>
+      </c>
       <c r="Q8" s="33">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="S8" s="34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T8" s="33">
         <v>15</v>
@@ -5773,34 +5797,34 @@
       </c>
       <c r="W8" s="12">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="X8" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y8" s="14">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AA8" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>Bulgária</v>
       </c>
       <c r="AC8" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" s="4">
         <f t="shared" si="7"/>
@@ -5808,7 +5832,7 @@
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="4">
         <f t="shared" si="9"/>
@@ -5816,27 +5840,27 @@
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="11"/>
-        <v>35</v>
-      </c>
-      <c r="AL8" s="4">
+        <v>112</v>
+      </c>
+      <c r="AL8" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>República Dominicana</v>
       </c>
       <c r="AM8" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" s="4">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP8" s="4">
         <f t="shared" si="16"/>
@@ -5844,7 +5868,7 @@
       </c>
       <c r="AQ8" s="4">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" s="4">
         <f t="shared" si="18"/>
@@ -5852,26 +5876,26 @@
       </c>
       <c r="AS8" s="4">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="AT8" s="4">
         <f t="shared" si="20"/>
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="AU8" s="31">
         <v>5</v>
       </c>
       <c r="AV8" s="30" t="str">
         <f>VLOOKUP($AU8,Dummy!$A:$R,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Bulgária</v>
       </c>
       <c r="AW8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,5,FALSE)</f>
@@ -5879,15 +5903,15 @@
       </c>
       <c r="AZ8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,9,FALSE)</f>
@@ -5895,7 +5919,7 @@
       </c>
       <c r="BD8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,11,FALSE)</f>
@@ -5907,27 +5931,27 @@
       </c>
       <c r="BG8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI8" s="29" t="str">
+        <v>4</v>
+      </c>
+      <c r="BI8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1250</v>
       </c>
       <c r="BJ8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="BK8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,17,FALSE)</f>
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="BL8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,18,FALSE)</f>
-        <v>1293.1034482758621</v>
+        <v>958.90410958904101</v>
       </c>
     </row>
     <row r="9" spans="2:64" x14ac:dyDescent="0.25">
@@ -5937,31 +5961,47 @@
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="33">
+        <v>1</v>
+      </c>
       <c r="E9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="34"/>
+      <c r="F9" s="34">
+        <v>3</v>
+      </c>
       <c r="G9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="33"/>
+      <c r="H9" s="33">
+        <v>18</v>
+      </c>
       <c r="I9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="33"/>
+      <c r="J9" s="34">
+        <v>25</v>
+      </c>
+      <c r="K9" s="33">
+        <v>25</v>
+      </c>
       <c r="L9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="34"/>
-      <c r="N9" s="33"/>
+      <c r="M9" s="34">
+        <v>22</v>
+      </c>
+      <c r="N9" s="33">
+        <v>15</v>
+      </c>
       <c r="O9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="34"/>
+      <c r="P9" s="34">
+        <v>25</v>
+      </c>
       <c r="Q9" s="33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R9" s="11" t="s">
         <v>6</v>
@@ -5976,34 +6016,34 @@
       <c r="V9" s="34"/>
       <c r="W9" s="12">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="X9" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y9" s="14">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="AA9" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB9" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>Holanda</v>
       </c>
       <c r="AC9" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE9" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="7"/>
@@ -6011,7 +6051,7 @@
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="9"/>
@@ -6019,27 +6059,27 @@
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" si="11"/>
-        <v>22</v>
-      </c>
-      <c r="AL9" s="4">
+        <v>81</v>
+      </c>
+      <c r="AL9" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>Canadá</v>
       </c>
       <c r="AM9" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="4">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP9" s="4">
         <f t="shared" si="16"/>
@@ -6047,7 +6087,7 @@
       </c>
       <c r="AQ9" s="4">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="4">
         <f t="shared" si="18"/>
@@ -6055,18 +6095,18 @@
       </c>
       <c r="AS9" s="4">
         <f t="shared" si="19"/>
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="AT9" s="4">
         <f t="shared" si="20"/>
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="AU9" s="31">
         <v>6</v>
       </c>
       <c r="AV9" s="30" t="str">
         <f>VLOOKUP($AU9,Dummy!$A:$R,2,FALSE)</f>
-        <v>Polônia</v>
+        <v>Japão</v>
       </c>
       <c r="AW9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,3,FALSE)</f>
@@ -6122,15 +6162,15 @@
       </c>
       <c r="BJ9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,16,FALSE)</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="BK9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,17,FALSE)</f>
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="BL9" s="29">
         <f>VLOOKUP($AU9,Dummy!$A:$R,18,FALSE)</f>
-        <v>1117.6470588235295</v>
+        <v>1562.5</v>
       </c>
     </row>
     <row r="10" spans="2:64" x14ac:dyDescent="0.25">
@@ -6464,15 +6504,15 @@
       </c>
       <c r="AV11" s="30" t="str">
         <f>VLOOKUP($AU11,Dummy!$A:$R,2,FALSE)</f>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="AW11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,5,FALSE)</f>
@@ -6480,11 +6520,11 @@
       </c>
       <c r="AZ11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,8,FALSE)</f>
@@ -6492,7 +6532,7 @@
       </c>
       <c r="BC11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,10,FALSE)</f>
@@ -6500,7 +6540,7 @@
       </c>
       <c r="BE11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,12,FALSE)</f>
@@ -6508,27 +6548,27 @@
       </c>
       <c r="BG11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="BJ11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,16,FALSE)</f>
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="BK11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,17,FALSE)</f>
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="BL11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,18,FALSE)</f>
-        <v>1273.8095238095236</v>
+        <v>1086.0927152317881</v>
       </c>
     </row>
     <row r="12" spans="2:64" x14ac:dyDescent="0.25">
@@ -6663,15 +6703,15 @@
       </c>
       <c r="AV12" s="30" t="str">
         <f>VLOOKUP($AU12,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Dominicana</v>
+        <v>Holanda</v>
       </c>
       <c r="AW12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,5,FALSE)</f>
@@ -6679,7 +6719,7 @@
       </c>
       <c r="AZ12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,7,FALSE)</f>
@@ -6687,11 +6727,11 @@
       </c>
       <c r="BB12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,10,FALSE)</f>
@@ -6703,7 +6743,7 @@
       </c>
       <c r="BF12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,13,FALSE)</f>
@@ -6711,23 +6751,23 @@
       </c>
       <c r="BH12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="BJ12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,16,FALSE)</f>
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="BK12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,17,FALSE)</f>
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="BL12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,18,FALSE)</f>
-        <v>1086.5384615384614</v>
+        <v>929.48717948717956</v>
       </c>
     </row>
     <row r="13" spans="2:64" x14ac:dyDescent="0.25">
@@ -6862,19 +6902,19 @@
       </c>
       <c r="AV13" s="30" t="str">
         <f>VLOOKUP($AU13,Dummy!$A:$R,2,FALSE)</f>
-        <v>Sérvia</v>
+        <v>Bélgica</v>
       </c>
       <c r="AW13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,6,FALSE)</f>
@@ -6886,7 +6926,7 @@
       </c>
       <c r="BB13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,9,FALSE)</f>
@@ -6894,7 +6934,7 @@
       </c>
       <c r="BD13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,11,FALSE)</f>
@@ -6902,31 +6942,31 @@
       </c>
       <c r="BF13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>750</v>
       </c>
       <c r="BJ13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,16,FALSE)</f>
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="BK13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,17,FALSE)</f>
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="BL13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,18,FALSE)</f>
-        <v>920.35398230088492</v>
+        <v>911.76470588235293</v>
       </c>
     </row>
     <row r="14" spans="2:64" x14ac:dyDescent="0.25">
@@ -7061,19 +7101,19 @@
       </c>
       <c r="AV14" s="30" t="str">
         <f>VLOOKUP($AU14,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bulgária</v>
+        <v>Canadá</v>
       </c>
       <c r="AW14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,6,FALSE)</f>
@@ -7089,15 +7129,15 @@
       </c>
       <c r="BC14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,12,FALSE)</f>
@@ -7105,27 +7145,27 @@
       </c>
       <c r="BG14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>800</v>
       </c>
       <c r="BJ14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,16,FALSE)</f>
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="BK14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,17,FALSE)</f>
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="BL14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,18,FALSE)</f>
-        <v>785.04672897196258</v>
+        <v>1038.6740331491712</v>
       </c>
     </row>
     <row r="15" spans="2:64" x14ac:dyDescent="0.25">
@@ -7260,19 +7300,19 @@
       </c>
       <c r="AV15" s="30" t="str">
         <f>VLOOKUP($AU15,Dummy!$A:$R,2,FALSE)</f>
-        <v>França</v>
+        <v>República Dominicana</v>
       </c>
       <c r="AW15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,6,FALSE)</f>
@@ -7288,7 +7328,7 @@
       </c>
       <c r="BC15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,10,FALSE)</f>
@@ -7304,27 +7344,27 @@
       </c>
       <c r="BG15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,13,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BH15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,15,FALSE)</f>
-        <v>333.33333333333331</v>
+        <v>800</v>
       </c>
       <c r="BJ15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,16,FALSE)</f>
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="BK15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,17,FALSE)</f>
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="BL15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,18,FALSE)</f>
-        <v>704.08163265306121</v>
+        <v>978.26086956521738</v>
       </c>
     </row>
     <row r="16" spans="2:64" x14ac:dyDescent="0.25">
@@ -7459,11 +7499,11 @@
       </c>
       <c r="AV16" s="30" t="str">
         <f>VLOOKUP($AU16,Dummy!$A:$R,2,FALSE)</f>
-        <v>Tailândia</v>
+        <v>Sérvia</v>
       </c>
       <c r="AW16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,4,FALSE)</f>
@@ -7491,7 +7531,7 @@
       </c>
       <c r="BD16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,11,FALSE)</f>
@@ -7499,11 +7539,11 @@
       </c>
       <c r="BF16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,14,FALSE)</f>
@@ -7511,54 +7551,54 @@
       </c>
       <c r="BI16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="BJ16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,16,FALSE)</f>
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="BK16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,17,FALSE)</f>
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="BL16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,18,FALSE)</f>
-        <v>894.73684210526312</v>
+        <v>920.35398230088492</v>
       </c>
     </row>
     <row r="17" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="59"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="59"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+      <c r="Y17" s="59"/>
       <c r="AU17" s="31">
         <v>14</v>
       </c>
       <c r="AV17" s="30" t="str">
         <f>VLOOKUP($AU17,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>França</v>
       </c>
       <c r="AW17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,3,FALSE)</f>
@@ -7594,15 +7634,15 @@
       </c>
       <c r="BE17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,14,FALSE)</f>
@@ -7610,19 +7650,19 @@
       </c>
       <c r="BI17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>333.33333333333331</v>
       </c>
       <c r="BJ17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,16,FALSE)</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="BK17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="BL17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,18,FALSE)</f>
-        <v>773.33333333333337</v>
+        <v>704.08163265306121</v>
       </c>
     </row>
     <row r="18" spans="2:64" x14ac:dyDescent="0.25">
@@ -7630,42 +7670,42 @@
         <v>2</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="67" t="s">
+      <c r="D18" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="67" t="s">
+      <c r="H18" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67" t="s">
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67" t="s">
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67" t="s">
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="67"/>
-      <c r="S18" s="67"/>
-      <c r="T18" s="67" t="s">
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="67"/>
-      <c r="V18" s="67"/>
-      <c r="W18" s="67" t="s">
+      <c r="U18" s="58"/>
+      <c r="V18" s="58"/>
+      <c r="W18" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="67"/>
+      <c r="X18" s="58"/>
+      <c r="Y18" s="58"/>
       <c r="AA18" s="4" t="s">
         <v>38</v>
       </c>
@@ -7728,7 +7768,7 @@
       </c>
       <c r="AV18" s="30" t="str">
         <f>VLOOKUP($AU18,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Tailândia</v>
       </c>
       <c r="AW18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,3,FALSE)</f>
@@ -7736,7 +7776,7 @@
       </c>
       <c r="AX18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,5,FALSE)</f>
@@ -7744,7 +7784,7 @@
       </c>
       <c r="AZ18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,7,FALSE)</f>
@@ -7764,7 +7804,7 @@
       </c>
       <c r="BE18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,12,FALSE)</f>
@@ -7772,27 +7812,27 @@
       </c>
       <c r="BG18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="BJ18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,16,FALSE)</f>
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="BK18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,17,FALSE)</f>
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="BL18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,18,FALSE)</f>
-        <v>727.27272727272725</v>
+        <v>920</v>
       </c>
     </row>
     <row r="19" spans="2:64" x14ac:dyDescent="0.25">
@@ -7943,7 +7983,7 @@
       </c>
       <c r="AV19" s="30" t="str">
         <f>VLOOKUP($AU19,Dummy!$A:$R,2,FALSE)</f>
-        <v>Coreia do Sul</v>
+        <v>República Tcheca</v>
       </c>
       <c r="AW19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,3,FALSE)</f>
@@ -7999,7 +8039,7 @@
       </c>
       <c r="BJ19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,16,FALSE)</f>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="BK19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,17,FALSE)</f>
@@ -8007,7 +8047,7 @@
       </c>
       <c r="BL19" s="29">
         <f>VLOOKUP($AU19,Dummy!$A:$R,18,FALSE)</f>
-        <v>706.66666666666663</v>
+        <v>773.33333333333337</v>
       </c>
     </row>
     <row r="20" spans="2:64" x14ac:dyDescent="0.25">
@@ -8158,7 +8198,7 @@
       </c>
       <c r="AV20" s="30" t="str">
         <f>VLOOKUP($AU20,Dummy!$A:$R,2,FALSE)</f>
-        <v>Estados Unidos</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AW20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,3,FALSE)</f>
@@ -8214,15 +8254,15 @@
       </c>
       <c r="BJ20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,16,FALSE)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,17,FALSE)</f>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BL20" s="29">
         <f>VLOOKUP($AU20,Dummy!$A:$R,18,FALSE)</f>
-        <v>675</v>
+        <v>706.66666666666663</v>
       </c>
     </row>
     <row r="21" spans="2:64" x14ac:dyDescent="0.25">
@@ -8373,7 +8413,7 @@
       </c>
       <c r="AV21" s="30" t="str">
         <f>VLOOKUP($AU21,Dummy!$A:$R,2,FALSE)</f>
-        <v>Holanda</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AW21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,3,FALSE)</f>
@@ -8381,7 +8421,7 @@
       </c>
       <c r="AX21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,5,FALSE)</f>
@@ -8389,7 +8429,7 @@
       </c>
       <c r="AZ21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,7,FALSE)</f>
@@ -8413,7 +8453,7 @@
       </c>
       <c r="BF21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,13,FALSE)</f>
@@ -8421,7 +8461,7 @@
       </c>
       <c r="BH21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,15,FALSE)</f>
@@ -8429,15 +8469,15 @@
       </c>
       <c r="BJ21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,16,FALSE)</f>
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="BK21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BL21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,18,FALSE)</f>
-        <v>640</v>
+        <v>696.77419354838707</v>
       </c>
     </row>
     <row r="22" spans="2:64" x14ac:dyDescent="0.25">
@@ -8447,69 +8487,93 @@
       <c r="C22" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="33"/>
+      <c r="D22" s="33">
+        <v>2</v>
+      </c>
       <c r="E22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="34"/>
+      <c r="F22" s="34">
+        <v>3</v>
+      </c>
       <c r="G22" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="33"/>
+      <c r="H22" s="33">
+        <v>25</v>
+      </c>
       <c r="I22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="33"/>
+      <c r="J22" s="34">
+        <v>22</v>
+      </c>
+      <c r="K22" s="33">
+        <v>10</v>
+      </c>
       <c r="L22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="33"/>
+      <c r="M22" s="34">
+        <v>25</v>
+      </c>
+      <c r="N22" s="33">
+        <v>25</v>
+      </c>
       <c r="O22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="33"/>
+      <c r="P22" s="34">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="33">
+        <v>13</v>
+      </c>
       <c r="R22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="34"/>
-      <c r="T22" s="33"/>
+      <c r="S22" s="34">
+        <v>25</v>
+      </c>
+      <c r="T22" s="33">
+        <v>9</v>
+      </c>
       <c r="U22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="V22" s="34"/>
+      <c r="V22" s="34">
+        <v>15</v>
+      </c>
       <c r="W22" s="9">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="X22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="4" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>Itália</v>
       </c>
       <c r="AC22" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE22" s="4">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="26"/>
@@ -8521,35 +8585,35 @@
       </c>
       <c r="AH22" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AJ22" s="4">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="4">
+        <v>82</v>
+      </c>
+      <c r="AL22" s="4" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>Alemanha</v>
       </c>
       <c r="AM22" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" s="4">
         <f t="shared" si="36"/>
@@ -8561,15 +8625,15 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT22" s="4">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AX22" s="53">
         <f>SUM(AX4:AX21)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:64" x14ac:dyDescent="0.25">
@@ -8579,29 +8643,45 @@
       <c r="C23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="33"/>
+      <c r="D23" s="33">
+        <v>0</v>
+      </c>
       <c r="E23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="34"/>
+      <c r="F23" s="34">
+        <v>3</v>
+      </c>
       <c r="G23" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H23" s="33"/>
+      <c r="H23" s="33">
+        <v>18</v>
+      </c>
       <c r="I23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="33"/>
+      <c r="J23" s="34">
+        <v>25</v>
+      </c>
+      <c r="K23" s="33">
+        <v>17</v>
+      </c>
       <c r="L23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M23" s="34"/>
-      <c r="N23" s="33"/>
+      <c r="M23" s="34">
+        <v>25</v>
+      </c>
+      <c r="N23" s="33">
+        <v>19</v>
+      </c>
       <c r="O23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P23" s="34"/>
+      <c r="P23" s="34">
+        <v>25</v>
+      </c>
       <c r="Q23" s="33"/>
       <c r="R23" s="11" t="s">
         <v>6</v>
@@ -8614,30 +8694,30 @@
       <c r="V23" s="34"/>
       <c r="W23" s="9">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="X23" s="11" t="s">
         <v>6</v>
       </c>
       <c r="Y23" s="10">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="4" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>Brasil</v>
       </c>
       <c r="AC23" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE23" s="4">
         <f t="shared" si="25"/>
@@ -8645,7 +8725,7 @@
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" s="4">
         <f t="shared" si="27"/>
@@ -8657,19 +8737,19 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ23" s="4">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="4">
+        <v>54</v>
+      </c>
+      <c r="AL23" s="4" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AM23" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="33"/>
@@ -8677,7 +8757,7 @@
       </c>
       <c r="AO23" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="35"/>
@@ -8689,20 +8769,20 @@
       </c>
       <c r="AR23" s="4">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT23" s="4">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="AU23" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU23" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="AV23" s="58"/>
+      <c r="AV23" s="66"/>
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
@@ -9609,74 +9689,74 @@
       </c>
     </row>
     <row r="31" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="65" t="s">
+      <c r="B31" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="65"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="59"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="59"/>
+      <c r="P31" s="59"/>
+      <c r="Q31" s="59"/>
+      <c r="R31" s="59"/>
+      <c r="S31" s="59"/>
+      <c r="T31" s="59"/>
+      <c r="U31" s="59"/>
+      <c r="V31" s="59"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="59"/>
+      <c r="Y31" s="59"/>
     </row>
     <row r="32" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="24"/>
-      <c r="D32" s="66" t="s">
+      <c r="D32" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="67" t="s">
+      <c r="H32" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67" t="s">
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="67"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67" t="s">
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="67" t="s">
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="67"/>
-      <c r="S32" s="67"/>
-      <c r="T32" s="67" t="s">
+      <c r="R32" s="58"/>
+      <c r="S32" s="58"/>
+      <c r="T32" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U32" s="67"/>
-      <c r="V32" s="67"/>
-      <c r="W32" s="67" t="s">
+      <c r="U32" s="58"/>
+      <c r="V32" s="58"/>
+      <c r="W32" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X32" s="67"/>
-      <c r="Y32" s="67"/>
+      <c r="X32" s="58"/>
+      <c r="Y32" s="58"/>
       <c r="AA32" s="4" t="s">
         <v>38</v>
       </c>
@@ -10178,34 +10258,54 @@
       <c r="C36" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="33"/>
+      <c r="D36" s="33">
+        <v>3</v>
+      </c>
       <c r="E36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="34"/>
+      <c r="F36" s="34">
+        <v>1</v>
+      </c>
       <c r="G36" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="33"/>
+      <c r="H36" s="33">
+        <v>25</v>
+      </c>
       <c r="I36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J36" s="34"/>
-      <c r="K36" s="33"/>
+      <c r="J36" s="34">
+        <v>22</v>
+      </c>
+      <c r="K36" s="33">
+        <v>25</v>
+      </c>
       <c r="L36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M36" s="34"/>
-      <c r="N36" s="33"/>
+      <c r="M36" s="34">
+        <v>23</v>
+      </c>
+      <c r="N36" s="33">
+        <v>24</v>
+      </c>
       <c r="O36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="33"/>
+      <c r="P36" s="34">
+        <v>26</v>
+      </c>
+      <c r="Q36" s="33">
+        <v>25</v>
+      </c>
       <c r="R36" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S36" s="34"/>
+      <c r="S36" s="34">
+        <v>22</v>
+      </c>
       <c r="T36" s="33"/>
       <c r="U36" s="11" t="s">
         <v>6</v>
@@ -10213,34 +10313,34 @@
       <c r="V36" s="34"/>
       <c r="W36" s="12">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="X36" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y36" s="14">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AB36" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB36" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>Bélgica</v>
       </c>
       <c r="AC36" s="4">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE36" s="4">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="47"/>
@@ -10248,7 +10348,7 @@
       </c>
       <c r="AG36" s="4">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH36" s="4">
         <f t="shared" si="49"/>
@@ -10256,27 +10356,27 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AJ36" s="4">
         <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AL36" s="4">
+        <v>93</v>
+      </c>
+      <c r="AL36" s="4" t="str">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>Tailândia</v>
       </c>
       <c r="AM36" s="4">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36" s="4">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="56"/>
@@ -10284,7 +10384,7 @@
       </c>
       <c r="AQ36" s="4">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR36" s="4">
         <f t="shared" si="58"/>
@@ -10292,11 +10392,11 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AT36" s="4">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.25">
@@ -10306,34 +10406,54 @@
       <c r="C37" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="33"/>
+      <c r="D37" s="33">
+        <v>1</v>
+      </c>
       <c r="E37" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="34"/>
+      <c r="F37" s="34">
+        <v>3</v>
+      </c>
       <c r="G37" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="33"/>
+      <c r="H37" s="33">
+        <v>22</v>
+      </c>
       <c r="I37" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J37" s="34"/>
-      <c r="K37" s="33"/>
+      <c r="J37" s="34">
+        <v>25</v>
+      </c>
+      <c r="K37" s="33">
+        <v>25</v>
+      </c>
       <c r="L37" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M37" s="34"/>
-      <c r="N37" s="33"/>
+      <c r="M37" s="34">
+        <v>20</v>
+      </c>
+      <c r="N37" s="33">
+        <v>19</v>
+      </c>
       <c r="O37" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="33"/>
+      <c r="P37" s="34">
+        <v>25</v>
+      </c>
+      <c r="Q37" s="33">
+        <v>21</v>
+      </c>
       <c r="R37" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S37" s="34"/>
+      <c r="S37" s="34">
+        <v>25</v>
+      </c>
       <c r="T37" s="33"/>
       <c r="U37" s="11" t="s">
         <v>6</v>
@@ -10341,34 +10461,34 @@
       <c r="V37" s="34"/>
       <c r="W37" s="12">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="X37" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y37" s="14">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AB37" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB37" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>Polônia</v>
       </c>
       <c r="AC37" s="4">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE37" s="4">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="47"/>
@@ -10376,7 +10496,7 @@
       </c>
       <c r="AG37" s="4">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" s="4">
         <f t="shared" si="49"/>
@@ -10384,27 +10504,27 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ37" s="4">
         <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AL37" s="4">
+        <v>87</v>
+      </c>
+      <c r="AL37" s="4" t="str">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>China</v>
       </c>
       <c r="AM37" s="4">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" s="4">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="56"/>
@@ -10412,7 +10532,7 @@
       </c>
       <c r="AQ37" s="4">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37" s="4">
         <f t="shared" si="58"/>
@@ -10420,11 +10540,11 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT37" s="4">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="2:64" x14ac:dyDescent="0.25">
@@ -11324,88 +11444,88 @@
       </c>
     </row>
     <row r="46" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
-      <c r="L46" s="69"/>
-      <c r="M46" s="69"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="69"/>
-      <c r="P46" s="69"/>
-      <c r="Q46" s="69"/>
-      <c r="R46" s="69"/>
-      <c r="S46" s="69"/>
-      <c r="T46" s="69"/>
-      <c r="U46" s="69"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="69"/>
-      <c r="X46" s="69"/>
-      <c r="Y46" s="69"/>
-      <c r="AU46" s="59" t="s">
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="60"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="60"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="60"/>
+      <c r="T46" s="60"/>
+      <c r="U46" s="60"/>
+      <c r="V46" s="60"/>
+      <c r="W46" s="60"/>
+      <c r="X46" s="60"/>
+      <c r="Y46" s="60"/>
+      <c r="AU46" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="AV46" s="60"/>
-      <c r="AW46" s="61"/>
-      <c r="AX46" s="59" t="s">
+      <c r="AV46" s="64"/>
+      <c r="AW46" s="65"/>
+      <c r="AX46" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="AY46" s="60"/>
-      <c r="AZ46" s="61"/>
-      <c r="BA46" s="59" t="s">
+      <c r="AY46" s="64"/>
+      <c r="AZ46" s="65"/>
+      <c r="BA46" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="BB46" s="60"/>
-      <c r="BC46" s="60"/>
-      <c r="BD46" s="60"/>
-      <c r="BE46" s="60"/>
-      <c r="BF46" s="61"/>
-      <c r="BG46" s="59" t="s">
+      <c r="BB46" s="64"/>
+      <c r="BC46" s="64"/>
+      <c r="BD46" s="64"/>
+      <c r="BE46" s="64"/>
+      <c r="BF46" s="65"/>
+      <c r="BG46" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="BH46" s="60"/>
-      <c r="BI46" s="61"/>
-      <c r="BJ46" s="59" t="s">
+      <c r="BH46" s="64"/>
+      <c r="BI46" s="65"/>
+      <c r="BJ46" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="BK46" s="60"/>
-      <c r="BL46" s="61"/>
+      <c r="BK46" s="64"/>
+      <c r="BL46" s="65"/>
     </row>
     <row r="47" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
-      <c r="N47" s="65"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="65"/>
-      <c r="Q47" s="65"/>
-      <c r="R47" s="65"/>
-      <c r="S47" s="65"/>
-      <c r="T47" s="65"/>
-      <c r="U47" s="65"/>
-      <c r="V47" s="65"/>
-      <c r="W47" s="65"/>
-      <c r="X47" s="65"/>
-      <c r="Y47" s="65"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="59"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="59"/>
+      <c r="M47" s="59"/>
+      <c r="N47" s="59"/>
+      <c r="O47" s="59"/>
+      <c r="P47" s="59"/>
+      <c r="Q47" s="59"/>
+      <c r="R47" s="59"/>
+      <c r="S47" s="59"/>
+      <c r="T47" s="59"/>
+      <c r="U47" s="59"/>
+      <c r="V47" s="59"/>
+      <c r="W47" s="59"/>
+      <c r="X47" s="59"/>
+      <c r="Y47" s="59"/>
       <c r="AU47" s="32" t="s">
         <v>43</v>
       </c>
@@ -11466,42 +11586,42 @@
         <v>2</v>
       </c>
       <c r="C48" s="24"/>
-      <c r="D48" s="66" t="s">
+      <c r="D48" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
       <c r="G48" s="20"/>
-      <c r="H48" s="67" t="s">
+      <c r="H48" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67" t="s">
+      <c r="I48" s="58"/>
+      <c r="J48" s="58"/>
+      <c r="K48" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="67"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="67" t="s">
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O48" s="67"/>
-      <c r="P48" s="67"/>
-      <c r="Q48" s="67" t="s">
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="67"/>
-      <c r="S48" s="67"/>
-      <c r="T48" s="67" t="s">
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+      <c r="T48" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U48" s="67"/>
-      <c r="V48" s="67"/>
-      <c r="W48" s="67" t="s">
+      <c r="U48" s="58"/>
+      <c r="V48" s="58"/>
+      <c r="W48" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X48" s="67"/>
-      <c r="Y48" s="67"/>
+      <c r="X48" s="58"/>
+      <c r="Y48" s="58"/>
       <c r="AA48" s="4" t="s">
         <v>38</v>
       </c>
@@ -11564,19 +11684,19 @@
       </c>
       <c r="AV48" s="30" t="str">
         <f>VLOOKUP($AU48,Dummy!$A:$R,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="AW48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,6,FALSE)</f>
@@ -11584,7 +11704,7 @@
       </c>
       <c r="BA48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,8,FALSE)</f>
@@ -11608,7 +11728,7 @@
       </c>
       <c r="BG48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,14,FALSE)</f>
@@ -11620,15 +11740,15 @@
       </c>
       <c r="BJ48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BK48" s="28">
         <f>VLOOKUP($AU48,Dummy!$A:$R,17,FALSE)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="BL48" s="29">
         <f>VLOOKUP($AU48,Dummy!$A:$R,18,FALSE)</f>
-        <v>1562.5</v>
+        <v>1339.2857142857142</v>
       </c>
     </row>
     <row r="49" spans="2:64" x14ac:dyDescent="0.25">
@@ -11763,19 +11883,19 @@
       </c>
       <c r="AV49" s="30" t="str">
         <f>VLOOKUP($AU49,Dummy!$A:$R,2,FALSE)</f>
-        <v>Itália</v>
+        <v>Polônia</v>
       </c>
       <c r="AW49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,6,FALSE)</f>
@@ -11787,7 +11907,7 @@
       </c>
       <c r="BB49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,9,FALSE)</f>
@@ -11807,27 +11927,27 @@
       </c>
       <c r="BG49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI49" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="BI49" s="29">
         <f>VLOOKUP($AU49,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="BJ49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,16,FALSE)</f>
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="BK49" s="28">
         <f>VLOOKUP($AU49,Dummy!$A:$R,17,FALSE)</f>
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="BL49" s="29">
         <f>VLOOKUP($AU49,Dummy!$A:$R,18,FALSE)</f>
-        <v>1481.4814814814813</v>
+        <v>1103.2258064516129</v>
       </c>
     </row>
     <row r="50" spans="2:64" x14ac:dyDescent="0.25">
@@ -11962,19 +12082,19 @@
       </c>
       <c r="AV50" s="30" t="str">
         <f>VLOOKUP($AU50,Dummy!$A:$R,2,FALSE)</f>
-        <v>Alemanha</v>
+        <v>Itália</v>
       </c>
       <c r="AW50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,6,FALSE)</f>
@@ -11990,7 +12110,7 @@
       </c>
       <c r="BC50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,10,FALSE)</f>
@@ -12006,27 +12126,27 @@
       </c>
       <c r="BG50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI50" s="29" t="str">
+        <v>2</v>
+      </c>
+      <c r="BI50" s="29">
         <f>VLOOKUP($AU50,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="BJ50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="BK50" s="28">
         <f>VLOOKUP($AU50,Dummy!$A:$R,17,FALSE)</f>
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="BL50" s="29">
         <f>VLOOKUP($AU50,Dummy!$A:$R,18,FALSE)</f>
-        <v>1415.0943396226414</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="51" spans="2:64" x14ac:dyDescent="0.25">
@@ -12161,15 +12281,15 @@
       </c>
       <c r="AV51" s="30" t="str">
         <f>VLOOKUP($AU51,Dummy!$A:$R,2,FALSE)</f>
-        <v>China</v>
+        <v>Alemanha</v>
       </c>
       <c r="AW51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,5,FALSE)</f>
@@ -12177,7 +12297,7 @@
       </c>
       <c r="AZ51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,7,FALSE)</f>
@@ -12193,7 +12313,7 @@
       </c>
       <c r="BD51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,11,FALSE)</f>
@@ -12205,27 +12325,27 @@
       </c>
       <c r="BG51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI51" s="29" t="str">
+        <v>3</v>
+      </c>
+      <c r="BI51" s="29">
         <f>VLOOKUP($AU51,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="BJ51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,16,FALSE)</f>
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="BK51" s="28">
         <f>VLOOKUP($AU51,Dummy!$A:$R,17,FALSE)</f>
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="BL51" s="29">
         <f>VLOOKUP($AU51,Dummy!$A:$R,18,FALSE)</f>
-        <v>1375</v>
+        <v>981.25</v>
       </c>
     </row>
     <row r="52" spans="2:64" x14ac:dyDescent="0.25">
@@ -12360,15 +12480,15 @@
       </c>
       <c r="AV52" s="30" t="str">
         <f>VLOOKUP($AU52,Dummy!$A:$R,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Bulgária</v>
       </c>
       <c r="AW52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,5,FALSE)</f>
@@ -12376,15 +12496,15 @@
       </c>
       <c r="AZ52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,9,FALSE)</f>
@@ -12392,7 +12512,7 @@
       </c>
       <c r="BD52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,11,FALSE)</f>
@@ -12404,27 +12524,27 @@
       </c>
       <c r="BG52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI52" s="29" t="str">
+        <v>4</v>
+      </c>
+      <c r="BI52" s="29">
         <f>VLOOKUP($AU52,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1250</v>
       </c>
       <c r="BJ52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="BK52" s="28">
         <f>VLOOKUP($AU52,Dummy!$A:$R,17,FALSE)</f>
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="BL52" s="29">
         <f>VLOOKUP($AU52,Dummy!$A:$R,18,FALSE)</f>
-        <v>1293.1034482758621</v>
+        <v>958.90410958904101</v>
       </c>
     </row>
     <row r="53" spans="2:64" x14ac:dyDescent="0.25">
@@ -12559,7 +12679,7 @@
       </c>
       <c r="AV53" s="30" t="str">
         <f>VLOOKUP($AU53,Dummy!$A:$R,2,FALSE)</f>
-        <v>Polônia</v>
+        <v>Japão</v>
       </c>
       <c r="AW53" s="28">
         <f>VLOOKUP($AU53,Dummy!$A:$R,3,FALSE)</f>
@@ -12615,15 +12735,15 @@
       </c>
       <c r="BJ53" s="28">
         <f>VLOOKUP($AU53,Dummy!$A:$R,16,FALSE)</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="BK53" s="28">
         <f>VLOOKUP($AU53,Dummy!$A:$R,17,FALSE)</f>
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="BL53" s="29">
         <f>VLOOKUP($AU53,Dummy!$A:$R,18,FALSE)</f>
-        <v>1117.6470588235295</v>
+        <v>1562.5</v>
       </c>
     </row>
     <row r="54" spans="2:64" x14ac:dyDescent="0.25">
@@ -12957,15 +13077,15 @@
       </c>
       <c r="AV55" s="30" t="str">
         <f>VLOOKUP($AU55,Dummy!$A:$R,2,FALSE)</f>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="AW55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,5,FALSE)</f>
@@ -12973,11 +13093,11 @@
       </c>
       <c r="AZ55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,8,FALSE)</f>
@@ -12985,7 +13105,7 @@
       </c>
       <c r="BC55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,10,FALSE)</f>
@@ -12993,7 +13113,7 @@
       </c>
       <c r="BE55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,12,FALSE)</f>
@@ -13001,27 +13121,27 @@
       </c>
       <c r="BG55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="29">
         <f>VLOOKUP($AU55,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="BJ55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,16,FALSE)</f>
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="BK55" s="28">
         <f>VLOOKUP($AU55,Dummy!$A:$R,17,FALSE)</f>
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="BL55" s="29">
         <f>VLOOKUP($AU55,Dummy!$A:$R,18,FALSE)</f>
-        <v>1273.8095238095236</v>
+        <v>1086.0927152317881</v>
       </c>
     </row>
     <row r="56" spans="2:64" x14ac:dyDescent="0.25">
@@ -13156,15 +13276,15 @@
       </c>
       <c r="AV56" s="30" t="str">
         <f>VLOOKUP($AU56,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Dominicana</v>
+        <v>Holanda</v>
       </c>
       <c r="AW56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,5,FALSE)</f>
@@ -13172,7 +13292,7 @@
       </c>
       <c r="AZ56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,7,FALSE)</f>
@@ -13180,11 +13300,11 @@
       </c>
       <c r="BB56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,10,FALSE)</f>
@@ -13196,7 +13316,7 @@
       </c>
       <c r="BF56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,13,FALSE)</f>
@@ -13204,23 +13324,23 @@
       </c>
       <c r="BH56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI56" s="29">
         <f>VLOOKUP($AU56,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="BJ56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,16,FALSE)</f>
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="BK56" s="28">
         <f>VLOOKUP($AU56,Dummy!$A:$R,17,FALSE)</f>
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="BL56" s="29">
         <f>VLOOKUP($AU56,Dummy!$A:$R,18,FALSE)</f>
-        <v>1086.5384615384614</v>
+        <v>929.48717948717956</v>
       </c>
     </row>
     <row r="57" spans="2:64" x14ac:dyDescent="0.25">
@@ -13355,19 +13475,19 @@
       </c>
       <c r="AV57" s="30" t="str">
         <f>VLOOKUP($AU57,Dummy!$A:$R,2,FALSE)</f>
-        <v>Sérvia</v>
+        <v>Bélgica</v>
       </c>
       <c r="AW57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,6,FALSE)</f>
@@ -13379,7 +13499,7 @@
       </c>
       <c r="BB57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,9,FALSE)</f>
@@ -13387,7 +13507,7 @@
       </c>
       <c r="BD57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,11,FALSE)</f>
@@ -13395,31 +13515,31 @@
       </c>
       <c r="BF57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI57" s="29">
         <f>VLOOKUP($AU57,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>750</v>
       </c>
       <c r="BJ57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,16,FALSE)</f>
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="BK57" s="28">
         <f>VLOOKUP($AU57,Dummy!$A:$R,17,FALSE)</f>
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="BL57" s="29">
         <f>VLOOKUP($AU57,Dummy!$A:$R,18,FALSE)</f>
-        <v>920.35398230088492</v>
+        <v>911.76470588235293</v>
       </c>
     </row>
     <row r="58" spans="2:64" x14ac:dyDescent="0.25">
@@ -13554,19 +13674,19 @@
       </c>
       <c r="AV58" s="30" t="str">
         <f>VLOOKUP($AU58,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bulgária</v>
+        <v>Canadá</v>
       </c>
       <c r="AW58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,6,FALSE)</f>
@@ -13582,15 +13702,15 @@
       </c>
       <c r="BC58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,12,FALSE)</f>
@@ -13598,27 +13718,27 @@
       </c>
       <c r="BG58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI58" s="29">
         <f>VLOOKUP($AU58,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>800</v>
       </c>
       <c r="BJ58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,16,FALSE)</f>
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="BK58" s="28">
         <f>VLOOKUP($AU58,Dummy!$A:$R,17,FALSE)</f>
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="BL58" s="29">
         <f>VLOOKUP($AU58,Dummy!$A:$R,18,FALSE)</f>
-        <v>785.04672897196258</v>
+        <v>1038.6740331491712</v>
       </c>
     </row>
     <row r="59" spans="2:64" x14ac:dyDescent="0.25">
@@ -13753,19 +13873,19 @@
       </c>
       <c r="AV59" s="30" t="str">
         <f>VLOOKUP($AU59,Dummy!$A:$R,2,FALSE)</f>
-        <v>França</v>
+        <v>República Dominicana</v>
       </c>
       <c r="AW59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,6,FALSE)</f>
@@ -13781,7 +13901,7 @@
       </c>
       <c r="BC59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,10,FALSE)</f>
@@ -13797,27 +13917,27 @@
       </c>
       <c r="BG59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,13,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BH59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI59" s="29">
         <f>VLOOKUP($AU59,Dummy!$A:$R,15,FALSE)</f>
-        <v>333.33333333333331</v>
+        <v>800</v>
       </c>
       <c r="BJ59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,16,FALSE)</f>
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="BK59" s="28">
         <f>VLOOKUP($AU59,Dummy!$A:$R,17,FALSE)</f>
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="BL59" s="29">
         <f>VLOOKUP($AU59,Dummy!$A:$R,18,FALSE)</f>
-        <v>704.08163265306121</v>
+        <v>978.26086956521738</v>
       </c>
     </row>
     <row r="60" spans="2:64" x14ac:dyDescent="0.25">
@@ -13952,11 +14072,11 @@
       </c>
       <c r="AV60" s="30" t="str">
         <f>VLOOKUP($AU60,Dummy!$A:$R,2,FALSE)</f>
-        <v>Tailândia</v>
+        <v>Sérvia</v>
       </c>
       <c r="AW60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,4,FALSE)</f>
@@ -13984,7 +14104,7 @@
       </c>
       <c r="BD60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,11,FALSE)</f>
@@ -13992,11 +14112,11 @@
       </c>
       <c r="BF60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,14,FALSE)</f>
@@ -14004,54 +14124,54 @@
       </c>
       <c r="BI60" s="29">
         <f>VLOOKUP($AU60,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="BJ60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,16,FALSE)</f>
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="BK60" s="28">
         <f>VLOOKUP($AU60,Dummy!$A:$R,17,FALSE)</f>
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="BL60" s="29">
         <f>VLOOKUP($AU60,Dummy!$A:$R,18,FALSE)</f>
-        <v>894.73684210526312</v>
+        <v>920.35398230088492</v>
       </c>
     </row>
     <row r="61" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B61" s="65" t="s">
+      <c r="B61" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="65"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
-      <c r="J61" s="65"/>
-      <c r="K61" s="65"/>
-      <c r="L61" s="65"/>
-      <c r="M61" s="65"/>
-      <c r="N61" s="65"/>
-      <c r="O61" s="65"/>
-      <c r="P61" s="65"/>
-      <c r="Q61" s="65"/>
-      <c r="R61" s="65"/>
-      <c r="S61" s="65"/>
-      <c r="T61" s="65"/>
-      <c r="U61" s="65"/>
-      <c r="V61" s="65"/>
-      <c r="W61" s="65"/>
-      <c r="X61" s="65"/>
-      <c r="Y61" s="65"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="59"/>
+      <c r="W61" s="59"/>
+      <c r="X61" s="59"/>
+      <c r="Y61" s="59"/>
       <c r="AU61" s="31">
         <v>14</v>
       </c>
       <c r="AV61" s="30" t="str">
         <f>VLOOKUP($AU61,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>França</v>
       </c>
       <c r="AW61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,3,FALSE)</f>
@@ -14087,15 +14207,15 @@
       </c>
       <c r="BE61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,14,FALSE)</f>
@@ -14103,19 +14223,19 @@
       </c>
       <c r="BI61" s="29">
         <f>VLOOKUP($AU61,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>333.33333333333331</v>
       </c>
       <c r="BJ61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,16,FALSE)</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="BK61" s="28">
         <f>VLOOKUP($AU61,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="BL61" s="29">
         <f>VLOOKUP($AU61,Dummy!$A:$R,18,FALSE)</f>
-        <v>773.33333333333337</v>
+        <v>704.08163265306121</v>
       </c>
     </row>
     <row r="62" spans="2:64" x14ac:dyDescent="0.25">
@@ -14123,42 +14243,42 @@
         <v>2</v>
       </c>
       <c r="C62" s="24"/>
-      <c r="D62" s="67" t="s">
+      <c r="D62" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
       <c r="G62" s="20"/>
-      <c r="H62" s="67" t="s">
+      <c r="H62" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="67"/>
-      <c r="J62" s="67"/>
-      <c r="K62" s="67" t="s">
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="67"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="67" t="s">
+      <c r="L62" s="58"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O62" s="67"/>
-      <c r="P62" s="67"/>
-      <c r="Q62" s="67" t="s">
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="67"/>
-      <c r="S62" s="67"/>
-      <c r="T62" s="67" t="s">
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U62" s="67"/>
-      <c r="V62" s="67"/>
-      <c r="W62" s="67" t="s">
+      <c r="U62" s="58"/>
+      <c r="V62" s="58"/>
+      <c r="W62" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X62" s="67"/>
-      <c r="Y62" s="67"/>
+      <c r="X62" s="58"/>
+      <c r="Y62" s="58"/>
       <c r="AA62" s="4" t="s">
         <v>38</v>
       </c>
@@ -14221,7 +14341,7 @@
       </c>
       <c r="AV62" s="30" t="str">
         <f>VLOOKUP($AU62,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Tailândia</v>
       </c>
       <c r="AW62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,3,FALSE)</f>
@@ -14229,7 +14349,7 @@
       </c>
       <c r="AX62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,5,FALSE)</f>
@@ -14237,7 +14357,7 @@
       </c>
       <c r="AZ62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,7,FALSE)</f>
@@ -14257,7 +14377,7 @@
       </c>
       <c r="BE62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,12,FALSE)</f>
@@ -14265,27 +14385,27 @@
       </c>
       <c r="BG62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI62" s="29">
         <f>VLOOKUP($AU62,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="BJ62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,16,FALSE)</f>
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="BK62" s="28">
         <f>VLOOKUP($AU62,Dummy!$A:$R,17,FALSE)</f>
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="BL62" s="29">
         <f>VLOOKUP($AU62,Dummy!$A:$R,18,FALSE)</f>
-        <v>727.27272727272725</v>
+        <v>920</v>
       </c>
     </row>
     <row r="63" spans="2:64" x14ac:dyDescent="0.25">
@@ -14420,7 +14540,7 @@
       </c>
       <c r="AV63" s="30" t="str">
         <f>VLOOKUP($AU63,Dummy!$A:$R,2,FALSE)</f>
-        <v>Coreia do Sul</v>
+        <v>República Tcheca</v>
       </c>
       <c r="AW63" s="28">
         <f>VLOOKUP($AU63,Dummy!$A:$R,3,FALSE)</f>
@@ -14476,7 +14596,7 @@
       </c>
       <c r="BJ63" s="28">
         <f>VLOOKUP($AU63,Dummy!$A:$R,16,FALSE)</f>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="BK63" s="28">
         <f>VLOOKUP($AU63,Dummy!$A:$R,17,FALSE)</f>
@@ -14484,7 +14604,7 @@
       </c>
       <c r="BL63" s="29">
         <f>VLOOKUP($AU63,Dummy!$A:$R,18,FALSE)</f>
-        <v>706.66666666666663</v>
+        <v>773.33333333333337</v>
       </c>
     </row>
     <row r="64" spans="2:64" x14ac:dyDescent="0.25">
@@ -14619,7 +14739,7 @@
       </c>
       <c r="AV64" s="30" t="str">
         <f>VLOOKUP($AU64,Dummy!$A:$R,2,FALSE)</f>
-        <v>Estados Unidos</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AW64" s="28">
         <f>VLOOKUP($AU64,Dummy!$A:$R,3,FALSE)</f>
@@ -14675,15 +14795,15 @@
       </c>
       <c r="BJ64" s="28">
         <f>VLOOKUP($AU64,Dummy!$A:$R,16,FALSE)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK64" s="28">
         <f>VLOOKUP($AU64,Dummy!$A:$R,17,FALSE)</f>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BL64" s="29">
         <f>VLOOKUP($AU64,Dummy!$A:$R,18,FALSE)</f>
-        <v>675</v>
+        <v>706.66666666666663</v>
       </c>
     </row>
     <row r="65" spans="2:64" x14ac:dyDescent="0.25">
@@ -14818,7 +14938,7 @@
       </c>
       <c r="AV65" s="30" t="str">
         <f>VLOOKUP($AU65,Dummy!$A:$R,2,FALSE)</f>
-        <v>Holanda</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AW65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,3,FALSE)</f>
@@ -14826,7 +14946,7 @@
       </c>
       <c r="AX65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,5,FALSE)</f>
@@ -14834,7 +14954,7 @@
       </c>
       <c r="AZ65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,7,FALSE)</f>
@@ -14858,7 +14978,7 @@
       </c>
       <c r="BF65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,13,FALSE)</f>
@@ -14866,7 +14986,7 @@
       </c>
       <c r="BH65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI65" s="29">
         <f>VLOOKUP($AU65,Dummy!$A:$R,15,FALSE)</f>
@@ -14874,15 +14994,15 @@
       </c>
       <c r="BJ65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,16,FALSE)</f>
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="BK65" s="28">
         <f>VLOOKUP($AU65,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BL65" s="29">
         <f>VLOOKUP($AU65,Dummy!$A:$R,18,FALSE)</f>
-        <v>640</v>
+        <v>696.77419354838707</v>
       </c>
     </row>
     <row r="66" spans="2:64" x14ac:dyDescent="0.25">
@@ -15014,7 +15134,7 @@
       </c>
       <c r="AX66" s="53">
         <f>SUM(AX48:AX65)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="2:64" x14ac:dyDescent="0.25">
@@ -15144,10 +15264,10 @@
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="AU67" s="58" t="s">
+      <c r="AU67" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="AV67" s="58"/>
+      <c r="AV67" s="66"/>
     </row>
     <row r="68" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B68" s="18">
@@ -16054,74 +16174,74 @@
       </c>
     </row>
     <row r="75" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="65"/>
-      <c r="D75" s="65"/>
-      <c r="E75" s="65"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="65"/>
-      <c r="H75" s="65"/>
-      <c r="I75" s="65"/>
-      <c r="J75" s="65"/>
-      <c r="K75" s="65"/>
-      <c r="L75" s="65"/>
-      <c r="M75" s="65"/>
-      <c r="N75" s="65"/>
-      <c r="O75" s="65"/>
-      <c r="P75" s="65"/>
-      <c r="Q75" s="65"/>
-      <c r="R75" s="65"/>
-      <c r="S75" s="65"/>
-      <c r="T75" s="65"/>
-      <c r="U75" s="65"/>
-      <c r="V75" s="65"/>
-      <c r="W75" s="65"/>
-      <c r="X75" s="65"/>
-      <c r="Y75" s="65"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="59"/>
+      <c r="K75" s="59"/>
+      <c r="L75" s="59"/>
+      <c r="M75" s="59"/>
+      <c r="N75" s="59"/>
+      <c r="O75" s="59"/>
+      <c r="P75" s="59"/>
+      <c r="Q75" s="59"/>
+      <c r="R75" s="59"/>
+      <c r="S75" s="59"/>
+      <c r="T75" s="59"/>
+      <c r="U75" s="59"/>
+      <c r="V75" s="59"/>
+      <c r="W75" s="59"/>
+      <c r="X75" s="59"/>
+      <c r="Y75" s="59"/>
     </row>
     <row r="76" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C76" s="24"/>
-      <c r="D76" s="66" t="s">
+      <c r="D76" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
+      <c r="E76" s="62"/>
+      <c r="F76" s="62"/>
       <c r="G76" s="20"/>
-      <c r="H76" s="67" t="s">
+      <c r="H76" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="67"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67" t="s">
+      <c r="I76" s="58"/>
+      <c r="J76" s="58"/>
+      <c r="K76" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L76" s="67"/>
-      <c r="M76" s="67"/>
-      <c r="N76" s="67" t="s">
+      <c r="L76" s="58"/>
+      <c r="M76" s="58"/>
+      <c r="N76" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O76" s="67"/>
-      <c r="P76" s="67"/>
-      <c r="Q76" s="67" t="s">
+      <c r="O76" s="58"/>
+      <c r="P76" s="58"/>
+      <c r="Q76" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R76" s="67"/>
-      <c r="S76" s="67"/>
-      <c r="T76" s="67" t="s">
+      <c r="R76" s="58"/>
+      <c r="S76" s="58"/>
+      <c r="T76" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U76" s="67"/>
-      <c r="V76" s="67"/>
-      <c r="W76" s="67" t="s">
+      <c r="U76" s="58"/>
+      <c r="V76" s="58"/>
+      <c r="W76" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X76" s="67"/>
-      <c r="Y76" s="67"/>
+      <c r="X76" s="58"/>
+      <c r="Y76" s="58"/>
       <c r="AA76" s="4" t="s">
         <v>38</v>
       </c>
@@ -17717,88 +17837,88 @@
       </c>
     </row>
     <row r="90" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B90" s="69" t="s">
+      <c r="B90" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="69"/>
-      <c r="E90" s="69"/>
-      <c r="F90" s="69"/>
-      <c r="G90" s="69"/>
-      <c r="H90" s="69"/>
-      <c r="I90" s="69"/>
-      <c r="J90" s="69"/>
-      <c r="K90" s="69"/>
-      <c r="L90" s="69"/>
-      <c r="M90" s="69"/>
-      <c r="N90" s="69"/>
-      <c r="O90" s="69"/>
-      <c r="P90" s="69"/>
-      <c r="Q90" s="69"/>
-      <c r="R90" s="69"/>
-      <c r="S90" s="69"/>
-      <c r="T90" s="69"/>
-      <c r="U90" s="69"/>
-      <c r="V90" s="69"/>
-      <c r="W90" s="69"/>
-      <c r="X90" s="69"/>
-      <c r="Y90" s="69"/>
-      <c r="AU90" s="59" t="s">
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="60"/>
+      <c r="I90" s="60"/>
+      <c r="J90" s="60"/>
+      <c r="K90" s="60"/>
+      <c r="L90" s="60"/>
+      <c r="M90" s="60"/>
+      <c r="N90" s="60"/>
+      <c r="O90" s="60"/>
+      <c r="P90" s="60"/>
+      <c r="Q90" s="60"/>
+      <c r="R90" s="60"/>
+      <c r="S90" s="60"/>
+      <c r="T90" s="60"/>
+      <c r="U90" s="60"/>
+      <c r="V90" s="60"/>
+      <c r="W90" s="60"/>
+      <c r="X90" s="60"/>
+      <c r="Y90" s="60"/>
+      <c r="AU90" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="AV90" s="60"/>
-      <c r="AW90" s="61"/>
-      <c r="AX90" s="59" t="s">
+      <c r="AV90" s="64"/>
+      <c r="AW90" s="65"/>
+      <c r="AX90" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="AY90" s="60"/>
-      <c r="AZ90" s="61"/>
-      <c r="BA90" s="59" t="s">
+      <c r="AY90" s="64"/>
+      <c r="AZ90" s="65"/>
+      <c r="BA90" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="BB90" s="60"/>
-      <c r="BC90" s="60"/>
-      <c r="BD90" s="60"/>
-      <c r="BE90" s="60"/>
-      <c r="BF90" s="61"/>
-      <c r="BG90" s="59" t="s">
+      <c r="BB90" s="64"/>
+      <c r="BC90" s="64"/>
+      <c r="BD90" s="64"/>
+      <c r="BE90" s="64"/>
+      <c r="BF90" s="65"/>
+      <c r="BG90" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="BH90" s="60"/>
-      <c r="BI90" s="61"/>
-      <c r="BJ90" s="59" t="s">
+      <c r="BH90" s="64"/>
+      <c r="BI90" s="65"/>
+      <c r="BJ90" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="BK90" s="60"/>
-      <c r="BL90" s="61"/>
+      <c r="BK90" s="64"/>
+      <c r="BL90" s="65"/>
     </row>
     <row r="91" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B91" s="65" t="s">
+      <c r="B91" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="65"/>
-      <c r="D91" s="65"/>
-      <c r="E91" s="65"/>
-      <c r="F91" s="65"/>
-      <c r="G91" s="65"/>
-      <c r="H91" s="65"/>
-      <c r="I91" s="65"/>
-      <c r="J91" s="65"/>
-      <c r="K91" s="65"/>
-      <c r="L91" s="65"/>
-      <c r="M91" s="65"/>
-      <c r="N91" s="65"/>
-      <c r="O91" s="65"/>
-      <c r="P91" s="65"/>
-      <c r="Q91" s="65"/>
-      <c r="R91" s="65"/>
-      <c r="S91" s="65"/>
-      <c r="T91" s="65"/>
-      <c r="U91" s="65"/>
-      <c r="V91" s="65"/>
-      <c r="W91" s="65"/>
-      <c r="X91" s="65"/>
-      <c r="Y91" s="65"/>
+      <c r="C91" s="59"/>
+      <c r="D91" s="59"/>
+      <c r="E91" s="59"/>
+      <c r="F91" s="59"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="59"/>
+      <c r="J91" s="59"/>
+      <c r="K91" s="59"/>
+      <c r="L91" s="59"/>
+      <c r="M91" s="59"/>
+      <c r="N91" s="59"/>
+      <c r="O91" s="59"/>
+      <c r="P91" s="59"/>
+      <c r="Q91" s="59"/>
+      <c r="R91" s="59"/>
+      <c r="S91" s="59"/>
+      <c r="T91" s="59"/>
+      <c r="U91" s="59"/>
+      <c r="V91" s="59"/>
+      <c r="W91" s="59"/>
+      <c r="X91" s="59"/>
+      <c r="Y91" s="59"/>
       <c r="AU91" s="32" t="s">
         <v>43</v>
       </c>
@@ -17859,42 +17979,42 @@
         <v>2</v>
       </c>
       <c r="C92" s="24"/>
-      <c r="D92" s="66" t="s">
+      <c r="D92" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E92" s="66"/>
-      <c r="F92" s="66"/>
+      <c r="E92" s="62"/>
+      <c r="F92" s="62"/>
       <c r="G92" s="20"/>
-      <c r="H92" s="67" t="s">
+      <c r="H92" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I92" s="67"/>
-      <c r="J92" s="67"/>
-      <c r="K92" s="67" t="s">
+      <c r="I92" s="58"/>
+      <c r="J92" s="58"/>
+      <c r="K92" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L92" s="67"/>
-      <c r="M92" s="67"/>
-      <c r="N92" s="67" t="s">
+      <c r="L92" s="58"/>
+      <c r="M92" s="58"/>
+      <c r="N92" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O92" s="67"/>
-      <c r="P92" s="67"/>
-      <c r="Q92" s="67" t="s">
+      <c r="O92" s="58"/>
+      <c r="P92" s="58"/>
+      <c r="Q92" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R92" s="67"/>
-      <c r="S92" s="67"/>
-      <c r="T92" s="67" t="s">
+      <c r="R92" s="58"/>
+      <c r="S92" s="58"/>
+      <c r="T92" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U92" s="67"/>
-      <c r="V92" s="67"/>
-      <c r="W92" s="67" t="s">
+      <c r="U92" s="58"/>
+      <c r="V92" s="58"/>
+      <c r="W92" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X92" s="67"/>
-      <c r="Y92" s="67"/>
+      <c r="X92" s="58"/>
+      <c r="Y92" s="58"/>
       <c r="AA92" s="4" t="s">
         <v>38</v>
       </c>
@@ -17957,19 +18077,19 @@
       </c>
       <c r="AV92" s="30" t="str">
         <f>VLOOKUP($AU92,Dummy!$A:$R,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="AW92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,6,FALSE)</f>
@@ -17977,7 +18097,7 @@
       </c>
       <c r="BA92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,8,FALSE)</f>
@@ -18001,7 +18121,7 @@
       </c>
       <c r="BG92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,14,FALSE)</f>
@@ -18013,15 +18133,15 @@
       </c>
       <c r="BJ92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BK92" s="28">
         <f>VLOOKUP($AU92,Dummy!$A:$R,17,FALSE)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="BL92" s="29">
         <f>VLOOKUP($AU92,Dummy!$A:$R,18,FALSE)</f>
-        <v>1562.5</v>
+        <v>1339.2857142857142</v>
       </c>
     </row>
     <row r="93" spans="2:64" x14ac:dyDescent="0.25">
@@ -18156,19 +18276,19 @@
       </c>
       <c r="AV93" s="30" t="str">
         <f>VLOOKUP($AU93,Dummy!$A:$R,2,FALSE)</f>
-        <v>Itália</v>
+        <v>Polônia</v>
       </c>
       <c r="AW93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,6,FALSE)</f>
@@ -18180,7 +18300,7 @@
       </c>
       <c r="BB93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,9,FALSE)</f>
@@ -18200,27 +18320,27 @@
       </c>
       <c r="BG93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI93" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="BI93" s="29">
         <f>VLOOKUP($AU93,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="BJ93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,16,FALSE)</f>
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="BK93" s="28">
         <f>VLOOKUP($AU93,Dummy!$A:$R,17,FALSE)</f>
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="BL93" s="29">
         <f>VLOOKUP($AU93,Dummy!$A:$R,18,FALSE)</f>
-        <v>1481.4814814814813</v>
+        <v>1103.2258064516129</v>
       </c>
     </row>
     <row r="94" spans="2:64" x14ac:dyDescent="0.25">
@@ -18355,19 +18475,19 @@
       </c>
       <c r="AV94" s="30" t="str">
         <f>VLOOKUP($AU94,Dummy!$A:$R,2,FALSE)</f>
-        <v>Alemanha</v>
+        <v>Itália</v>
       </c>
       <c r="AW94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,6,FALSE)</f>
@@ -18383,7 +18503,7 @@
       </c>
       <c r="BC94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,10,FALSE)</f>
@@ -18399,27 +18519,27 @@
       </c>
       <c r="BG94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI94" s="29" t="str">
+        <v>2</v>
+      </c>
+      <c r="BI94" s="29">
         <f>VLOOKUP($AU94,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="BJ94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="BK94" s="28">
         <f>VLOOKUP($AU94,Dummy!$A:$R,17,FALSE)</f>
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="BL94" s="29">
         <f>VLOOKUP($AU94,Dummy!$A:$R,18,FALSE)</f>
-        <v>1415.0943396226414</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="95" spans="2:64" x14ac:dyDescent="0.25">
@@ -18554,15 +18674,15 @@
       </c>
       <c r="AV95" s="30" t="str">
         <f>VLOOKUP($AU95,Dummy!$A:$R,2,FALSE)</f>
-        <v>China</v>
+        <v>Alemanha</v>
       </c>
       <c r="AW95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,5,FALSE)</f>
@@ -18570,7 +18690,7 @@
       </c>
       <c r="AZ95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,7,FALSE)</f>
@@ -18586,7 +18706,7 @@
       </c>
       <c r="BD95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,11,FALSE)</f>
@@ -18598,27 +18718,27 @@
       </c>
       <c r="BG95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI95" s="29" t="str">
+        <v>3</v>
+      </c>
+      <c r="BI95" s="29">
         <f>VLOOKUP($AU95,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="BJ95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,16,FALSE)</f>
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="BK95" s="28">
         <f>VLOOKUP($AU95,Dummy!$A:$R,17,FALSE)</f>
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="BL95" s="29">
         <f>VLOOKUP($AU95,Dummy!$A:$R,18,FALSE)</f>
-        <v>1375</v>
+        <v>981.25</v>
       </c>
     </row>
     <row r="96" spans="2:64" x14ac:dyDescent="0.25">
@@ -18753,15 +18873,15 @@
       </c>
       <c r="AV96" s="30" t="str">
         <f>VLOOKUP($AU96,Dummy!$A:$R,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Bulgária</v>
       </c>
       <c r="AW96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,5,FALSE)</f>
@@ -18769,15 +18889,15 @@
       </c>
       <c r="AZ96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,9,FALSE)</f>
@@ -18785,7 +18905,7 @@
       </c>
       <c r="BD96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,11,FALSE)</f>
@@ -18797,27 +18917,27 @@
       </c>
       <c r="BG96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI96" s="29" t="str">
+        <v>4</v>
+      </c>
+      <c r="BI96" s="29">
         <f>VLOOKUP($AU96,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1250</v>
       </c>
       <c r="BJ96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="BK96" s="28">
         <f>VLOOKUP($AU96,Dummy!$A:$R,17,FALSE)</f>
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="BL96" s="29">
         <f>VLOOKUP($AU96,Dummy!$A:$R,18,FALSE)</f>
-        <v>1293.1034482758621</v>
+        <v>958.90410958904101</v>
       </c>
     </row>
     <row r="97" spans="2:64" x14ac:dyDescent="0.25">
@@ -18952,7 +19072,7 @@
       </c>
       <c r="AV97" s="30" t="str">
         <f>VLOOKUP($AU97,Dummy!$A:$R,2,FALSE)</f>
-        <v>Polônia</v>
+        <v>Japão</v>
       </c>
       <c r="AW97" s="28">
         <f>VLOOKUP($AU97,Dummy!$A:$R,3,FALSE)</f>
@@ -19008,15 +19128,15 @@
       </c>
       <c r="BJ97" s="28">
         <f>VLOOKUP($AU97,Dummy!$A:$R,16,FALSE)</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="BK97" s="28">
         <f>VLOOKUP($AU97,Dummy!$A:$R,17,FALSE)</f>
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="BL97" s="29">
         <f>VLOOKUP($AU97,Dummy!$A:$R,18,FALSE)</f>
-        <v>1117.6470588235295</v>
+        <v>1562.5</v>
       </c>
     </row>
     <row r="98" spans="2:64" x14ac:dyDescent="0.25">
@@ -19350,15 +19470,15 @@
       </c>
       <c r="AV99" s="30" t="str">
         <f>VLOOKUP($AU99,Dummy!$A:$R,2,FALSE)</f>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="AW99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,5,FALSE)</f>
@@ -19366,11 +19486,11 @@
       </c>
       <c r="AZ99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,8,FALSE)</f>
@@ -19378,7 +19498,7 @@
       </c>
       <c r="BC99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,10,FALSE)</f>
@@ -19386,7 +19506,7 @@
       </c>
       <c r="BE99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,12,FALSE)</f>
@@ -19394,27 +19514,27 @@
       </c>
       <c r="BG99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI99" s="29">
         <f>VLOOKUP($AU99,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="BJ99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,16,FALSE)</f>
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="BK99" s="28">
         <f>VLOOKUP($AU99,Dummy!$A:$R,17,FALSE)</f>
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="BL99" s="29">
         <f>VLOOKUP($AU99,Dummy!$A:$R,18,FALSE)</f>
-        <v>1273.8095238095236</v>
+        <v>1086.0927152317881</v>
       </c>
     </row>
     <row r="100" spans="2:64" x14ac:dyDescent="0.25">
@@ -19549,15 +19669,15 @@
       </c>
       <c r="AV100" s="30" t="str">
         <f>VLOOKUP($AU100,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Dominicana</v>
+        <v>Holanda</v>
       </c>
       <c r="AW100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,5,FALSE)</f>
@@ -19565,7 +19685,7 @@
       </c>
       <c r="AZ100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,7,FALSE)</f>
@@ -19573,11 +19693,11 @@
       </c>
       <c r="BB100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,10,FALSE)</f>
@@ -19589,7 +19709,7 @@
       </c>
       <c r="BF100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,13,FALSE)</f>
@@ -19597,23 +19717,23 @@
       </c>
       <c r="BH100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI100" s="29">
         <f>VLOOKUP($AU100,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="BJ100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,16,FALSE)</f>
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="BK100" s="28">
         <f>VLOOKUP($AU100,Dummy!$A:$R,17,FALSE)</f>
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="BL100" s="29">
         <f>VLOOKUP($AU100,Dummy!$A:$R,18,FALSE)</f>
-        <v>1086.5384615384614</v>
+        <v>929.48717948717956</v>
       </c>
     </row>
     <row r="101" spans="2:64" x14ac:dyDescent="0.25">
@@ -19748,19 +19868,19 @@
       </c>
       <c r="AV101" s="30" t="str">
         <f>VLOOKUP($AU101,Dummy!$A:$R,2,FALSE)</f>
-        <v>Sérvia</v>
+        <v>Bélgica</v>
       </c>
       <c r="AW101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,6,FALSE)</f>
@@ -19772,7 +19892,7 @@
       </c>
       <c r="BB101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,9,FALSE)</f>
@@ -19780,7 +19900,7 @@
       </c>
       <c r="BD101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,11,FALSE)</f>
@@ -19788,31 +19908,31 @@
       </c>
       <c r="BF101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI101" s="29">
         <f>VLOOKUP($AU101,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>750</v>
       </c>
       <c r="BJ101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,16,FALSE)</f>
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="BK101" s="28">
         <f>VLOOKUP($AU101,Dummy!$A:$R,17,FALSE)</f>
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="BL101" s="29">
         <f>VLOOKUP($AU101,Dummy!$A:$R,18,FALSE)</f>
-        <v>920.35398230088492</v>
+        <v>911.76470588235293</v>
       </c>
     </row>
     <row r="102" spans="2:64" x14ac:dyDescent="0.25">
@@ -19947,19 +20067,19 @@
       </c>
       <c r="AV102" s="30" t="str">
         <f>VLOOKUP($AU102,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bulgária</v>
+        <v>Canadá</v>
       </c>
       <c r="AW102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,6,FALSE)</f>
@@ -19975,15 +20095,15 @@
       </c>
       <c r="BC102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,12,FALSE)</f>
@@ -19991,27 +20111,27 @@
       </c>
       <c r="BG102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI102" s="29">
         <f>VLOOKUP($AU102,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>800</v>
       </c>
       <c r="BJ102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,16,FALSE)</f>
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="BK102" s="28">
         <f>VLOOKUP($AU102,Dummy!$A:$R,17,FALSE)</f>
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="BL102" s="29">
         <f>VLOOKUP($AU102,Dummy!$A:$R,18,FALSE)</f>
-        <v>785.04672897196258</v>
+        <v>1038.6740331491712</v>
       </c>
     </row>
     <row r="103" spans="2:64" x14ac:dyDescent="0.25">
@@ -20146,19 +20266,19 @@
       </c>
       <c r="AV103" s="30" t="str">
         <f>VLOOKUP($AU103,Dummy!$A:$R,2,FALSE)</f>
-        <v>França</v>
+        <v>República Dominicana</v>
       </c>
       <c r="AW103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,6,FALSE)</f>
@@ -20174,7 +20294,7 @@
       </c>
       <c r="BC103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,10,FALSE)</f>
@@ -20190,27 +20310,27 @@
       </c>
       <c r="BG103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,13,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BH103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI103" s="29">
         <f>VLOOKUP($AU103,Dummy!$A:$R,15,FALSE)</f>
-        <v>333.33333333333331</v>
+        <v>800</v>
       </c>
       <c r="BJ103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,16,FALSE)</f>
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="BK103" s="28">
         <f>VLOOKUP($AU103,Dummy!$A:$R,17,FALSE)</f>
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="BL103" s="29">
         <f>VLOOKUP($AU103,Dummy!$A:$R,18,FALSE)</f>
-        <v>704.08163265306121</v>
+        <v>978.26086956521738</v>
       </c>
     </row>
     <row r="104" spans="2:64" x14ac:dyDescent="0.25">
@@ -20345,11 +20465,11 @@
       </c>
       <c r="AV104" s="30" t="str">
         <f>VLOOKUP($AU104,Dummy!$A:$R,2,FALSE)</f>
-        <v>Tailândia</v>
+        <v>Sérvia</v>
       </c>
       <c r="AW104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,4,FALSE)</f>
@@ -20377,7 +20497,7 @@
       </c>
       <c r="BD104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,11,FALSE)</f>
@@ -20385,11 +20505,11 @@
       </c>
       <c r="BF104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,14,FALSE)</f>
@@ -20397,54 +20517,54 @@
       </c>
       <c r="BI104" s="29">
         <f>VLOOKUP($AU104,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="BJ104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,16,FALSE)</f>
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="BK104" s="28">
         <f>VLOOKUP($AU104,Dummy!$A:$R,17,FALSE)</f>
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="BL104" s="29">
         <f>VLOOKUP($AU104,Dummy!$A:$R,18,FALSE)</f>
-        <v>894.73684210526312</v>
+        <v>920.35398230088492</v>
       </c>
     </row>
     <row r="105" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B105" s="65" t="s">
+      <c r="B105" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="C105" s="65"/>
-      <c r="D105" s="65"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="65"/>
-      <c r="H105" s="65"/>
-      <c r="I105" s="65"/>
-      <c r="J105" s="65"/>
-      <c r="K105" s="65"/>
-      <c r="L105" s="65"/>
-      <c r="M105" s="65"/>
-      <c r="N105" s="65"/>
-      <c r="O105" s="65"/>
-      <c r="P105" s="65"/>
-      <c r="Q105" s="65"/>
-      <c r="R105" s="65"/>
-      <c r="S105" s="65"/>
-      <c r="T105" s="65"/>
-      <c r="U105" s="65"/>
-      <c r="V105" s="65"/>
-      <c r="W105" s="65"/>
-      <c r="X105" s="65"/>
-      <c r="Y105" s="65"/>
+      <c r="C105" s="59"/>
+      <c r="D105" s="59"/>
+      <c r="E105" s="61"/>
+      <c r="F105" s="59"/>
+      <c r="G105" s="59"/>
+      <c r="H105" s="59"/>
+      <c r="I105" s="59"/>
+      <c r="J105" s="59"/>
+      <c r="K105" s="59"/>
+      <c r="L105" s="59"/>
+      <c r="M105" s="59"/>
+      <c r="N105" s="59"/>
+      <c r="O105" s="59"/>
+      <c r="P105" s="59"/>
+      <c r="Q105" s="59"/>
+      <c r="R105" s="59"/>
+      <c r="S105" s="59"/>
+      <c r="T105" s="59"/>
+      <c r="U105" s="59"/>
+      <c r="V105" s="59"/>
+      <c r="W105" s="59"/>
+      <c r="X105" s="59"/>
+      <c r="Y105" s="59"/>
       <c r="AU105" s="31">
         <v>14</v>
       </c>
       <c r="AV105" s="30" t="str">
         <f>VLOOKUP($AU105,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>França</v>
       </c>
       <c r="AW105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,3,FALSE)</f>
@@ -20480,15 +20600,15 @@
       </c>
       <c r="BE105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,14,FALSE)</f>
@@ -20496,19 +20616,19 @@
       </c>
       <c r="BI105" s="29">
         <f>VLOOKUP($AU105,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>333.33333333333331</v>
       </c>
       <c r="BJ105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,16,FALSE)</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="BK105" s="28">
         <f>VLOOKUP($AU105,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="BL105" s="29">
         <f>VLOOKUP($AU105,Dummy!$A:$R,18,FALSE)</f>
-        <v>773.33333333333337</v>
+        <v>704.08163265306121</v>
       </c>
     </row>
     <row r="106" spans="2:64" x14ac:dyDescent="0.25">
@@ -20516,42 +20636,42 @@
         <v>2</v>
       </c>
       <c r="C106" s="24"/>
-      <c r="D106" s="67" t="s">
+      <c r="D106" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="58"/>
       <c r="G106" s="20"/>
-      <c r="H106" s="67" t="s">
+      <c r="H106" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I106" s="67"/>
-      <c r="J106" s="67"/>
-      <c r="K106" s="67" t="s">
+      <c r="I106" s="58"/>
+      <c r="J106" s="58"/>
+      <c r="K106" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L106" s="67"/>
-      <c r="M106" s="67"/>
-      <c r="N106" s="67" t="s">
+      <c r="L106" s="58"/>
+      <c r="M106" s="58"/>
+      <c r="N106" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O106" s="67"/>
-      <c r="P106" s="67"/>
-      <c r="Q106" s="67" t="s">
+      <c r="O106" s="58"/>
+      <c r="P106" s="58"/>
+      <c r="Q106" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R106" s="67"/>
-      <c r="S106" s="67"/>
-      <c r="T106" s="67" t="s">
+      <c r="R106" s="58"/>
+      <c r="S106" s="58"/>
+      <c r="T106" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U106" s="67"/>
-      <c r="V106" s="67"/>
-      <c r="W106" s="67" t="s">
+      <c r="U106" s="58"/>
+      <c r="V106" s="58"/>
+      <c r="W106" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X106" s="67"/>
-      <c r="Y106" s="67"/>
+      <c r="X106" s="58"/>
+      <c r="Y106" s="58"/>
       <c r="AA106" s="4" t="s">
         <v>38</v>
       </c>
@@ -20614,7 +20734,7 @@
       </c>
       <c r="AV106" s="30" t="str">
         <f>VLOOKUP($AU106,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Tailândia</v>
       </c>
       <c r="AW106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,3,FALSE)</f>
@@ -20622,7 +20742,7 @@
       </c>
       <c r="AX106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,5,FALSE)</f>
@@ -20630,7 +20750,7 @@
       </c>
       <c r="AZ106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,7,FALSE)</f>
@@ -20650,7 +20770,7 @@
       </c>
       <c r="BE106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,12,FALSE)</f>
@@ -20658,27 +20778,27 @@
       </c>
       <c r="BG106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI106" s="29">
         <f>VLOOKUP($AU106,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="BJ106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,16,FALSE)</f>
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="BK106" s="28">
         <f>VLOOKUP($AU106,Dummy!$A:$R,17,FALSE)</f>
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="BL106" s="29">
         <f>VLOOKUP($AU106,Dummy!$A:$R,18,FALSE)</f>
-        <v>727.27272727272725</v>
+        <v>920</v>
       </c>
     </row>
     <row r="107" spans="2:64" x14ac:dyDescent="0.25">
@@ -20813,7 +20933,7 @@
       </c>
       <c r="AV107" s="30" t="str">
         <f>VLOOKUP($AU107,Dummy!$A:$R,2,FALSE)</f>
-        <v>Coreia do Sul</v>
+        <v>República Tcheca</v>
       </c>
       <c r="AW107" s="28">
         <f>VLOOKUP($AU107,Dummy!$A:$R,3,FALSE)</f>
@@ -20869,7 +20989,7 @@
       </c>
       <c r="BJ107" s="28">
         <f>VLOOKUP($AU107,Dummy!$A:$R,16,FALSE)</f>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="BK107" s="28">
         <f>VLOOKUP($AU107,Dummy!$A:$R,17,FALSE)</f>
@@ -20877,7 +20997,7 @@
       </c>
       <c r="BL107" s="29">
         <f>VLOOKUP($AU107,Dummy!$A:$R,18,FALSE)</f>
-        <v>706.66666666666663</v>
+        <v>773.33333333333337</v>
       </c>
     </row>
     <row r="108" spans="2:64" x14ac:dyDescent="0.25">
@@ -21012,7 +21132,7 @@
       </c>
       <c r="AV108" s="30" t="str">
         <f>VLOOKUP($AU108,Dummy!$A:$R,2,FALSE)</f>
-        <v>Estados Unidos</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AW108" s="28">
         <f>VLOOKUP($AU108,Dummy!$A:$R,3,FALSE)</f>
@@ -21068,15 +21188,15 @@
       </c>
       <c r="BJ108" s="28">
         <f>VLOOKUP($AU108,Dummy!$A:$R,16,FALSE)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK108" s="28">
         <f>VLOOKUP($AU108,Dummy!$A:$R,17,FALSE)</f>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BL108" s="29">
         <f>VLOOKUP($AU108,Dummy!$A:$R,18,FALSE)</f>
-        <v>675</v>
+        <v>706.66666666666663</v>
       </c>
     </row>
     <row r="109" spans="2:64" x14ac:dyDescent="0.25">
@@ -21211,7 +21331,7 @@
       </c>
       <c r="AV109" s="30" t="str">
         <f>VLOOKUP($AU109,Dummy!$A:$R,2,FALSE)</f>
-        <v>Holanda</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AW109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,3,FALSE)</f>
@@ -21219,7 +21339,7 @@
       </c>
       <c r="AX109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,5,FALSE)</f>
@@ -21227,7 +21347,7 @@
       </c>
       <c r="AZ109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,7,FALSE)</f>
@@ -21251,7 +21371,7 @@
       </c>
       <c r="BF109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,13,FALSE)</f>
@@ -21259,7 +21379,7 @@
       </c>
       <c r="BH109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI109" s="29">
         <f>VLOOKUP($AU109,Dummy!$A:$R,15,FALSE)</f>
@@ -21267,15 +21387,15 @@
       </c>
       <c r="BJ109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,16,FALSE)</f>
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="BK109" s="28">
         <f>VLOOKUP($AU109,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BL109" s="29">
         <f>VLOOKUP($AU109,Dummy!$A:$R,18,FALSE)</f>
-        <v>640</v>
+        <v>696.77419354838707</v>
       </c>
     </row>
     <row r="110" spans="2:64" x14ac:dyDescent="0.25">
@@ -21407,7 +21527,7 @@
       </c>
       <c r="AX110" s="53">
         <f>SUM(AX92:AX109)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="2:64" x14ac:dyDescent="0.25">
@@ -21537,10 +21657,10 @@
         <f t="shared" si="165"/>
         <v>0</v>
       </c>
-      <c r="AU111" s="58" t="s">
+      <c r="AU111" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="AV111" s="58"/>
+      <c r="AV111" s="66"/>
     </row>
     <row r="112" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
@@ -22447,74 +22567,74 @@
       </c>
     </row>
     <row r="119" spans="2:48" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B119" s="65" t="s">
+      <c r="B119" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="C119" s="65"/>
-      <c r="D119" s="65"/>
-      <c r="E119" s="65"/>
-      <c r="F119" s="65"/>
-      <c r="G119" s="65"/>
-      <c r="H119" s="65"/>
-      <c r="I119" s="65"/>
-      <c r="J119" s="65"/>
-      <c r="K119" s="65"/>
-      <c r="L119" s="65"/>
-      <c r="M119" s="65"/>
-      <c r="N119" s="65"/>
-      <c r="O119" s="65"/>
-      <c r="P119" s="65"/>
-      <c r="Q119" s="65"/>
-      <c r="R119" s="65"/>
-      <c r="S119" s="65"/>
-      <c r="T119" s="65"/>
-      <c r="U119" s="65"/>
-      <c r="V119" s="65"/>
-      <c r="W119" s="65"/>
-      <c r="X119" s="65"/>
-      <c r="Y119" s="65"/>
+      <c r="C119" s="59"/>
+      <c r="D119" s="59"/>
+      <c r="E119" s="59"/>
+      <c r="F119" s="59"/>
+      <c r="G119" s="59"/>
+      <c r="H119" s="59"/>
+      <c r="I119" s="59"/>
+      <c r="J119" s="59"/>
+      <c r="K119" s="59"/>
+      <c r="L119" s="59"/>
+      <c r="M119" s="59"/>
+      <c r="N119" s="59"/>
+      <c r="O119" s="59"/>
+      <c r="P119" s="59"/>
+      <c r="Q119" s="59"/>
+      <c r="R119" s="59"/>
+      <c r="S119" s="59"/>
+      <c r="T119" s="59"/>
+      <c r="U119" s="59"/>
+      <c r="V119" s="59"/>
+      <c r="W119" s="59"/>
+      <c r="X119" s="59"/>
+      <c r="Y119" s="59"/>
     </row>
     <row r="120" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B120" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="24"/>
-      <c r="D120" s="66" t="s">
+      <c r="D120" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E120" s="66"/>
-      <c r="F120" s="66"/>
+      <c r="E120" s="62"/>
+      <c r="F120" s="62"/>
       <c r="G120" s="20"/>
-      <c r="H120" s="67" t="s">
+      <c r="H120" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I120" s="67"/>
-      <c r="J120" s="67"/>
-      <c r="K120" s="67" t="s">
+      <c r="I120" s="58"/>
+      <c r="J120" s="58"/>
+      <c r="K120" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L120" s="67"/>
-      <c r="M120" s="67"/>
-      <c r="N120" s="67" t="s">
+      <c r="L120" s="58"/>
+      <c r="M120" s="58"/>
+      <c r="N120" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O120" s="67"/>
-      <c r="P120" s="67"/>
-      <c r="Q120" s="67" t="s">
+      <c r="O120" s="58"/>
+      <c r="P120" s="58"/>
+      <c r="Q120" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R120" s="67"/>
-      <c r="S120" s="67"/>
-      <c r="T120" s="67" t="s">
+      <c r="R120" s="58"/>
+      <c r="S120" s="58"/>
+      <c r="T120" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U120" s="67"/>
-      <c r="V120" s="67"/>
-      <c r="W120" s="67" t="s">
+      <c r="U120" s="58"/>
+      <c r="V120" s="58"/>
+      <c r="W120" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X120" s="67"/>
-      <c r="Y120" s="67"/>
+      <c r="X120" s="58"/>
+      <c r="Y120" s="58"/>
       <c r="AA120" s="4" t="s">
         <v>38</v>
       </c>
@@ -24112,18 +24232,71 @@
   </sheetData>
   <sheetProtection password="CC01" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="93">
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B2:Y2"/>
-    <mergeCell ref="B17:Y17"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="AU111:AV111"/>
+    <mergeCell ref="AU90:AW90"/>
+    <mergeCell ref="AX90:AZ90"/>
+    <mergeCell ref="BA90:BF90"/>
+    <mergeCell ref="BG90:BI90"/>
+    <mergeCell ref="BJ90:BL90"/>
+    <mergeCell ref="AU23:AV23"/>
+    <mergeCell ref="AU67:AV67"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AU46:AW46"/>
+    <mergeCell ref="AX46:AZ46"/>
+    <mergeCell ref="BA46:BF46"/>
+    <mergeCell ref="BG46:BI46"/>
+    <mergeCell ref="BJ46:BL46"/>
+    <mergeCell ref="B119:Y119"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="N120:P120"/>
+    <mergeCell ref="Q120:S120"/>
+    <mergeCell ref="T120:V120"/>
+    <mergeCell ref="W120:Y120"/>
+    <mergeCell ref="B105:Y105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="N106:P106"/>
+    <mergeCell ref="Q106:S106"/>
+    <mergeCell ref="T106:V106"/>
+    <mergeCell ref="W106:Y106"/>
+    <mergeCell ref="W76:Y76"/>
+    <mergeCell ref="B90:Y90"/>
+    <mergeCell ref="B91:Y91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="H92:J92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="N92:P92"/>
+    <mergeCell ref="Q92:S92"/>
+    <mergeCell ref="T92:V92"/>
+    <mergeCell ref="W92:Y92"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="Q76:S76"/>
+    <mergeCell ref="T76:V76"/>
+    <mergeCell ref="W48:Y48"/>
+    <mergeCell ref="B61:Y61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="T62:V62"/>
+    <mergeCell ref="W62:Y62"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="T48:V48"/>
     <mergeCell ref="B75:Y75"/>
     <mergeCell ref="B46:Y46"/>
     <mergeCell ref="B47:Y47"/>
@@ -24140,379 +24313,326 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="K18:M18"/>
     <mergeCell ref="N18:P18"/>
-    <mergeCell ref="W48:Y48"/>
-    <mergeCell ref="B61:Y61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="T62:V62"/>
-    <mergeCell ref="W62:Y62"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="T48:V48"/>
-    <mergeCell ref="W76:Y76"/>
-    <mergeCell ref="B90:Y90"/>
-    <mergeCell ref="B91:Y91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="H92:J92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="N92:P92"/>
-    <mergeCell ref="Q92:S92"/>
-    <mergeCell ref="T92:V92"/>
-    <mergeCell ref="W92:Y92"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="H76:J76"/>
-    <mergeCell ref="K76:M76"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="Q76:S76"/>
-    <mergeCell ref="T76:V76"/>
-    <mergeCell ref="B105:Y105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="H106:J106"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="N106:P106"/>
-    <mergeCell ref="Q106:S106"/>
-    <mergeCell ref="T106:V106"/>
-    <mergeCell ref="W106:Y106"/>
-    <mergeCell ref="B119:Y119"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="H120:J120"/>
-    <mergeCell ref="K120:M120"/>
-    <mergeCell ref="N120:P120"/>
-    <mergeCell ref="Q120:S120"/>
-    <mergeCell ref="T120:V120"/>
-    <mergeCell ref="W120:Y120"/>
-    <mergeCell ref="BJ90:BL90"/>
-    <mergeCell ref="AU23:AV23"/>
-    <mergeCell ref="AU67:AV67"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BJ2:BL2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AU46:AW46"/>
-    <mergeCell ref="AX46:AZ46"/>
-    <mergeCell ref="BA46:BF46"/>
-    <mergeCell ref="BG46:BI46"/>
-    <mergeCell ref="BJ46:BL46"/>
-    <mergeCell ref="AU111:AV111"/>
-    <mergeCell ref="AU90:AW90"/>
-    <mergeCell ref="AX90:AZ90"/>
-    <mergeCell ref="BA90:BF90"/>
-    <mergeCell ref="BG90:BI90"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B2:Y2"/>
+    <mergeCell ref="B17:Y17"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="T5:V16">
-    <cfRule type="expression" dxfId="78" priority="75">
+    <cfRule type="expression" dxfId="80" priority="75">
       <formula>$AA5&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:S16">
-    <cfRule type="expression" dxfId="77" priority="74">
+    <cfRule type="expression" dxfId="79" priority="74">
       <formula>$AA5&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:P16">
-    <cfRule type="expression" dxfId="76" priority="73">
+    <cfRule type="expression" dxfId="78" priority="73">
       <formula>$AA5&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:M16">
-    <cfRule type="expression" dxfId="75" priority="72">
+    <cfRule type="expression" dxfId="77" priority="72">
       <formula>$AA5&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:J16">
-    <cfRule type="expression" dxfId="74" priority="71">
+    <cfRule type="expression" dxfId="76" priority="71">
       <formula>$AA5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:Y16">
-    <cfRule type="expression" dxfId="73" priority="70">
+    <cfRule type="expression" dxfId="75" priority="70">
       <formula>$AA5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:V44">
-    <cfRule type="expression" dxfId="72" priority="69">
+    <cfRule type="expression" dxfId="74" priority="69">
       <formula>$AA33&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33:S44">
-    <cfRule type="expression" dxfId="71" priority="68">
+    <cfRule type="expression" dxfId="73" priority="68">
       <formula>$AA33&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:P44">
-    <cfRule type="expression" dxfId="70" priority="67">
+    <cfRule type="expression" dxfId="72" priority="67">
       <formula>$AA33&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33:M44">
-    <cfRule type="expression" dxfId="69" priority="66">
+    <cfRule type="expression" dxfId="71" priority="66">
       <formula>$AA33&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:J44">
-    <cfRule type="expression" dxfId="68" priority="65">
+    <cfRule type="expression" dxfId="70" priority="65">
       <formula>$AA33=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33:Y44">
-    <cfRule type="expression" dxfId="67" priority="64">
+    <cfRule type="expression" dxfId="69" priority="64">
       <formula>$AA33=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:V30">
-    <cfRule type="expression" dxfId="66" priority="63">
+    <cfRule type="expression" dxfId="68" priority="63">
       <formula>$AA19&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q19:S30">
-    <cfRule type="expression" dxfId="65" priority="62">
+    <cfRule type="expression" dxfId="67" priority="62">
       <formula>$AA19&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:P30">
-    <cfRule type="expression" dxfId="64" priority="61">
+    <cfRule type="expression" dxfId="66" priority="61">
       <formula>$AA19&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:M30">
-    <cfRule type="expression" dxfId="63" priority="60">
+    <cfRule type="expression" dxfId="65" priority="60">
       <formula>$AA19&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:J30">
-    <cfRule type="expression" dxfId="62" priority="59">
+    <cfRule type="expression" dxfId="64" priority="59">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y30">
-    <cfRule type="expression" dxfId="61" priority="58">
+    <cfRule type="expression" dxfId="63" priority="58">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T49:V60">
-    <cfRule type="expression" dxfId="60" priority="57">
+    <cfRule type="expression" dxfId="62" priority="57">
       <formula>$AA49&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q49:S60">
-    <cfRule type="expression" dxfId="59" priority="56">
+    <cfRule type="expression" dxfId="61" priority="56">
       <formula>$AA49&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49:P60">
-    <cfRule type="expression" dxfId="58" priority="55">
+    <cfRule type="expression" dxfId="60" priority="55">
       <formula>$AA49&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49:M60">
-    <cfRule type="expression" dxfId="57" priority="54">
+    <cfRule type="expression" dxfId="59" priority="54">
       <formula>$AA49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:J60">
-    <cfRule type="expression" dxfId="56" priority="53">
+    <cfRule type="expression" dxfId="58" priority="53">
       <formula>$AA49=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W49:Y60">
-    <cfRule type="expression" dxfId="55" priority="52">
+    <cfRule type="expression" dxfId="57" priority="52">
       <formula>$AA49=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T77:V88">
-    <cfRule type="expression" dxfId="54" priority="51">
+    <cfRule type="expression" dxfId="56" priority="51">
       <formula>$AA77&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q77:S88">
-    <cfRule type="expression" dxfId="53" priority="50">
+    <cfRule type="expression" dxfId="55" priority="50">
       <formula>$AA77&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N77:P88">
-    <cfRule type="expression" dxfId="52" priority="49">
+    <cfRule type="expression" dxfId="54" priority="49">
       <formula>$AA77&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77:M88">
-    <cfRule type="expression" dxfId="51" priority="48">
+    <cfRule type="expression" dxfId="53" priority="48">
       <formula>$AA77&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77:J88">
-    <cfRule type="expression" dxfId="50" priority="47">
+    <cfRule type="expression" dxfId="52" priority="47">
       <formula>$AA77=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W77:Y88">
-    <cfRule type="expression" dxfId="49" priority="46">
+    <cfRule type="expression" dxfId="51" priority="46">
       <formula>$AA77=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T63:V74">
-    <cfRule type="expression" dxfId="48" priority="45">
+    <cfRule type="expression" dxfId="50" priority="45">
       <formula>$AA63&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63:S74">
-    <cfRule type="expression" dxfId="47" priority="44">
+    <cfRule type="expression" dxfId="49" priority="44">
       <formula>$AA63&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N63:P74">
-    <cfRule type="expression" dxfId="46" priority="43">
+    <cfRule type="expression" dxfId="48" priority="43">
       <formula>$AA63&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:M74">
-    <cfRule type="expression" dxfId="45" priority="42">
+    <cfRule type="expression" dxfId="47" priority="42">
       <formula>$AA63&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H63:J74">
-    <cfRule type="expression" dxfId="44" priority="41">
+    <cfRule type="expression" dxfId="46" priority="41">
       <formula>$AA63=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63:Y74">
-    <cfRule type="expression" dxfId="43" priority="40">
+    <cfRule type="expression" dxfId="45" priority="40">
       <formula>$AA63=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T93:V104">
-    <cfRule type="expression" dxfId="42" priority="39">
+    <cfRule type="expression" dxfId="44" priority="39">
       <formula>$AA93&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q93:S104">
-    <cfRule type="expression" dxfId="41" priority="38">
+    <cfRule type="expression" dxfId="43" priority="38">
       <formula>$AA93&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N93:P104">
-    <cfRule type="expression" dxfId="40" priority="37">
+    <cfRule type="expression" dxfId="42" priority="37">
       <formula>$AA93&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:M104">
-    <cfRule type="expression" dxfId="39" priority="36">
+    <cfRule type="expression" dxfId="41" priority="36">
       <formula>$AA93&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H93:J104">
-    <cfRule type="expression" dxfId="38" priority="35">
+    <cfRule type="expression" dxfId="40" priority="35">
       <formula>$AA93=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W93:Y104">
-    <cfRule type="expression" dxfId="37" priority="34">
+    <cfRule type="expression" dxfId="39" priority="34">
       <formula>$AA93=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T121:V132">
-    <cfRule type="expression" dxfId="36" priority="33">
+    <cfRule type="expression" dxfId="38" priority="33">
       <formula>$AA121&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q121:S132">
-    <cfRule type="expression" dxfId="35" priority="32">
+    <cfRule type="expression" dxfId="37" priority="32">
       <formula>$AA121&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N121:P132">
-    <cfRule type="expression" dxfId="34" priority="31">
+    <cfRule type="expression" dxfId="36" priority="31">
       <formula>$AA121&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K121:M132">
-    <cfRule type="expression" dxfId="33" priority="30">
+    <cfRule type="expression" dxfId="35" priority="30">
       <formula>$AA121&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H121:J132">
-    <cfRule type="expression" dxfId="32" priority="29">
+    <cfRule type="expression" dxfId="34" priority="29">
       <formula>$AA121=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W121:Y132">
-    <cfRule type="expression" dxfId="31" priority="28">
+    <cfRule type="expression" dxfId="33" priority="28">
       <formula>$AA121=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T107:V118">
-    <cfRule type="expression" dxfId="30" priority="27">
+    <cfRule type="expression" dxfId="32" priority="27">
       <formula>$AA107&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q107:S118">
-    <cfRule type="expression" dxfId="29" priority="26">
+    <cfRule type="expression" dxfId="31" priority="26">
       <formula>$AA107&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N107:P118">
-    <cfRule type="expression" dxfId="28" priority="25">
+    <cfRule type="expression" dxfId="30" priority="25">
       <formula>$AA107&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:M118">
-    <cfRule type="expression" dxfId="27" priority="24">
+    <cfRule type="expression" dxfId="29" priority="24">
       <formula>$AA107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H107:J118">
-    <cfRule type="expression" dxfId="26" priority="23">
+    <cfRule type="expression" dxfId="28" priority="23">
       <formula>$AA107=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W107:Y118">
-    <cfRule type="expression" dxfId="25" priority="22">
+    <cfRule type="expression" dxfId="27" priority="22">
       <formula>$AA107=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM2:XFD21 AY22:XFD22 AW23:XFD25 BM46:XFD69 BM90:XFD113 A1:XFD1 A26:XFD45 A2:AT21 A22:AW22 A23:AT25 A70:XFD89 A46:AT69 A114:XFD1048576 A90:AT113">
-    <cfRule type="cellIs" dxfId="24" priority="21" operator="equal">
+  <conditionalFormatting sqref="BM2:XFD21 AY22:XFD22 AW23:XFD25 BM46:XFD69 BM90:XFD113 A1:XFD1 A26:XFD45 A22:AW22 A23:AT25 A70:XFD89 A46:AT69 A114:XFD1048576 A90:AT113 A2:AT21">
+    <cfRule type="cellIs" dxfId="26" priority="21" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y19">
-    <cfRule type="expression" dxfId="23" priority="20">
+    <cfRule type="expression" dxfId="25" priority="20">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y30">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="24" priority="19">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:BL3 AV4:BL21">
-    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU66:AW66 AY66:BL66 AW67:BL69">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU46:BL47 AV48:BL65">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU110:AW110 AY110:BL110 AW111:BL113">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU90:BL91 AV92:BL109">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24602,24 +24722,25 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="19"/>
+    <col min="2" max="2" width="8.7109375" style="19" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" style="27" customWidth="1"/>
     <col min="4" max="4" width="3.7109375" style="43" customWidth="1"/>
-    <col min="5" max="5" width="2.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="4" customWidth="1"/>
     <col min="6" max="6" width="3.7109375" style="6" customWidth="1"/>
     <col min="7" max="7" width="23.7109375" style="23" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" style="4" customWidth="1"/>
-    <col min="10" max="11" width="4.7109375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="2.7109375" style="4" customWidth="1"/>
-    <col min="13" max="14" width="4.7109375" style="4" customWidth="1"/>
-    <col min="15" max="15" width="2.7109375" style="4" customWidth="1"/>
-    <col min="16" max="17" width="4.7109375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" style="4" customWidth="1"/>
-    <col min="19" max="20" width="4.7109375" style="4" customWidth="1"/>
-    <col min="21" max="21" width="2.7109375" style="4" customWidth="1"/>
-    <col min="22" max="23" width="4.7109375" style="4" customWidth="1"/>
-    <col min="24" max="24" width="2.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="4" customWidth="1"/>
+    <col min="10" max="11" width="3.7109375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="1.7109375" style="4" customWidth="1"/>
+    <col min="13" max="14" width="3.7109375" style="4" customWidth="1"/>
+    <col min="15" max="15" width="1.7109375" style="4" customWidth="1"/>
+    <col min="16" max="17" width="3.7109375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="1.7109375" style="4" customWidth="1"/>
+    <col min="19" max="20" width="3.7109375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" style="4" customWidth="1"/>
+    <col min="22" max="22" width="3.7109375" style="4" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" style="4" customWidth="1"/>
+    <col min="24" max="24" width="1.7109375" style="4" customWidth="1"/>
     <col min="25" max="25" width="4.7109375" style="4" customWidth="1"/>
     <col min="26" max="26" width="9.140625" style="4" customWidth="1"/>
     <col min="27" max="27" width="6.28515625" style="4" hidden="1" customWidth="1"/>
@@ -24649,100 +24770,100 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="AU2" s="71" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="AU2" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="AV2" s="71"/>
-      <c r="AW2" s="71"/>
-      <c r="AX2" s="71" t="s">
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="69"/>
+      <c r="AX2" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="AY2" s="71"/>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="69"/>
+      <c r="BA2" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71"/>
-      <c r="BD2" s="71"/>
-      <c r="BE2" s="71"/>
-      <c r="BF2" s="71"/>
-      <c r="BG2" s="71" t="s">
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="68"/>
+      <c r="BD2" s="68"/>
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="69"/>
+      <c r="BG2" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="BH2" s="71"/>
-      <c r="BI2" s="71"/>
-      <c r="BJ2" s="71" t="s">
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="69"/>
+      <c r="BJ2" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="BK2" s="71"/>
-      <c r="BL2" s="71"/>
+      <c r="BK2" s="68"/>
+      <c r="BL2" s="69"/>
     </row>
     <row r="3" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
       <c r="G3" s="20"/>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67" t="s">
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67" t="s">
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67" t="s">
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67" t="s">
+      <c r="U3" s="58"/>
+      <c r="V3" s="58"/>
+      <c r="W3" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
       <c r="AA3" s="4" t="s">
         <v>38</v>
       </c>
@@ -24989,19 +25110,19 @@
       </c>
       <c r="AV4" s="30" t="str">
         <f>VLOOKUP($AU4,Dummy!$A:$R,2,FALSE)</f>
-        <v>Japão</v>
+        <v>Brasil</v>
       </c>
       <c r="AW4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,6,FALSE)</f>
@@ -25009,7 +25130,7 @@
       </c>
       <c r="BA4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,8,FALSE)</f>
@@ -25033,7 +25154,7 @@
       </c>
       <c r="BG4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,14,FALSE)</f>
@@ -25045,15 +25166,15 @@
       </c>
       <c r="BJ4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BK4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,17,FALSE)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="BL4" s="29">
         <f>VLOOKUP($AU4,Dummy!$A:$R,18,FALSE)</f>
-        <v>1562.5</v>
+        <v>1339.2857142857142</v>
       </c>
     </row>
     <row r="5" spans="2:64" x14ac:dyDescent="0.25">
@@ -25190,19 +25311,19 @@
       </c>
       <c r="AV5" s="30" t="str">
         <f>VLOOKUP($AU5,Dummy!$A:$R,2,FALSE)</f>
-        <v>Itália</v>
+        <v>Polônia</v>
       </c>
       <c r="AW5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,6,FALSE)</f>
@@ -25214,7 +25335,7 @@
       </c>
       <c r="BB5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,9,FALSE)</f>
@@ -25234,27 +25355,27 @@
       </c>
       <c r="BG5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI5" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="BI5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>6000</v>
       </c>
       <c r="BJ5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,16,FALSE)</f>
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="BK5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,17,FALSE)</f>
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="BL5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,18,FALSE)</f>
-        <v>1481.4814814814813</v>
+        <v>1103.2258064516129</v>
       </c>
     </row>
     <row r="6" spans="2:64" x14ac:dyDescent="0.25">
@@ -25391,19 +25512,19 @@
       </c>
       <c r="AV6" s="30" t="str">
         <f>VLOOKUP($AU6,Dummy!$A:$R,2,FALSE)</f>
-        <v>Alemanha</v>
+        <v>Itália</v>
       </c>
       <c r="AW6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,6,FALSE)</f>
@@ -25419,7 +25540,7 @@
       </c>
       <c r="BC6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,10,FALSE)</f>
@@ -25435,27 +25556,27 @@
       </c>
       <c r="BG6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI6" s="29" t="str">
+        <v>2</v>
+      </c>
+      <c r="BI6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>3000</v>
       </c>
       <c r="BJ6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="BK6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,17,FALSE)</f>
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="BL6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,18,FALSE)</f>
-        <v>1415.0943396226414</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7" spans="2:64" x14ac:dyDescent="0.25">
@@ -25592,15 +25713,15 @@
       </c>
       <c r="AV7" s="30" t="str">
         <f>VLOOKUP($AU7,Dummy!$A:$R,2,FALSE)</f>
-        <v>China</v>
+        <v>Alemanha</v>
       </c>
       <c r="AW7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,5,FALSE)</f>
@@ -25608,7 +25729,7 @@
       </c>
       <c r="AZ7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,7,FALSE)</f>
@@ -25624,7 +25745,7 @@
       </c>
       <c r="BD7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,11,FALSE)</f>
@@ -25636,27 +25757,27 @@
       </c>
       <c r="BG7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI7" s="29" t="str">
+        <v>3</v>
+      </c>
+      <c r="BI7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1666.6666666666667</v>
       </c>
       <c r="BJ7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,16,FALSE)</f>
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="BK7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,17,FALSE)</f>
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="BL7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,18,FALSE)</f>
-        <v>1375</v>
+        <v>981.25</v>
       </c>
     </row>
     <row r="8" spans="2:64" x14ac:dyDescent="0.25">
@@ -25665,15 +25786,15 @@
       </c>
       <c r="AV8" s="30" t="str">
         <f>VLOOKUP($AU8,Dummy!$A:$R,2,FALSE)</f>
-        <v>Brasil</v>
+        <v>Bulgária</v>
       </c>
       <c r="AW8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,3,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,5,FALSE)</f>
@@ -25681,15 +25802,15 @@
       </c>
       <c r="AZ8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,7,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,9,FALSE)</f>
@@ -25697,7 +25818,7 @@
       </c>
       <c r="BD8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,11,FALSE)</f>
@@ -25709,27 +25830,27 @@
       </c>
       <c r="BG8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,14,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BI8" s="29" t="str">
+        <v>4</v>
+      </c>
+      <c r="BI8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,15,FALSE)</f>
-        <v>MAX</v>
+        <v>1250</v>
       </c>
       <c r="BJ8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,16,FALSE)</f>
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="BK8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,17,FALSE)</f>
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="BL8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,18,FALSE)</f>
-        <v>1293.1034482758621</v>
+        <v>958.90410958904101</v>
       </c>
     </row>
     <row r="9" spans="2:64" x14ac:dyDescent="0.25">
@@ -25738,7 +25859,7 @@
       </c>
       <c r="AV9" s="30" t="str">
         <f>VLOOKUP($AU9,Dummy!$A:$R,2,FALSE)</f>
-        <v>Polônia</v>
+        <v>Japão</v>
       </c>
       <c r="AW9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,3,FALSE)</f>
@@ -25794,44 +25915,44 @@
       </c>
       <c r="BJ9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,16,FALSE)</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="BK9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,17,FALSE)</f>
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="BL9" s="29">
         <f>VLOOKUP($AU9,Dummy!$A:$R,18,FALSE)</f>
-        <v>1117.6470588235295</v>
+        <v>1562.5</v>
       </c>
     </row>
     <row r="10" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
       <c r="AU10" s="31">
         <v>7</v>
       </c>
@@ -25907,42 +26028,42 @@
     <row r="11" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="67" t="s">
+      <c r="H11" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67" t="s">
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67" t="s">
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
-      <c r="Q11" s="67" t="s">
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="67"/>
-      <c r="S11" s="67"/>
-      <c r="T11" s="67" t="s">
+      <c r="R11" s="58"/>
+      <c r="S11" s="58"/>
+      <c r="T11" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U11" s="67"/>
-      <c r="V11" s="67"/>
-      <c r="W11" s="67" t="s">
+      <c r="U11" s="58"/>
+      <c r="V11" s="58"/>
+      <c r="W11" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="67"/>
+      <c r="X11" s="58"/>
+      <c r="Y11" s="58"/>
       <c r="AA11" s="4" t="s">
         <v>38</v>
       </c>
@@ -26005,15 +26126,15 @@
       </c>
       <c r="AV11" s="30" t="str">
         <f>VLOOKUP($AU11,Dummy!$A:$R,2,FALSE)</f>
-        <v>Canadá</v>
+        <v>China</v>
       </c>
       <c r="AW11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,5,FALSE)</f>
@@ -26021,11 +26142,11 @@
       </c>
       <c r="AZ11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,8,FALSE)</f>
@@ -26033,7 +26154,7 @@
       </c>
       <c r="BC11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,10,FALSE)</f>
@@ -26041,7 +26162,7 @@
       </c>
       <c r="BE11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,12,FALSE)</f>
@@ -26049,27 +26170,27 @@
       </c>
       <c r="BG11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,13,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="BJ11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,16,FALSE)</f>
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="BK11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,17,FALSE)</f>
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="BL11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,18,FALSE)</f>
-        <v>1273.8095238095236</v>
+        <v>1086.0927152317881</v>
       </c>
     </row>
     <row r="12" spans="2:64" x14ac:dyDescent="0.25">
@@ -26206,15 +26327,15 @@
       </c>
       <c r="AV12" s="30" t="str">
         <f>VLOOKUP($AU12,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Dominicana</v>
+        <v>Holanda</v>
       </c>
       <c r="AW12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,5,FALSE)</f>
@@ -26222,7 +26343,7 @@
       </c>
       <c r="AZ12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,6,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,7,FALSE)</f>
@@ -26230,11 +26351,11 @@
       </c>
       <c r="BB12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,9,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,10,FALSE)</f>
@@ -26246,7 +26367,7 @@
       </c>
       <c r="BF12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,13,FALSE)</f>
@@ -26254,23 +26375,23 @@
       </c>
       <c r="BH12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,14,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,15,FALSE)</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="BJ12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,16,FALSE)</f>
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="BK12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,17,FALSE)</f>
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="BL12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,18,FALSE)</f>
-        <v>1086.5384615384614</v>
+        <v>929.48717948717956</v>
       </c>
     </row>
     <row r="13" spans="2:64" x14ac:dyDescent="0.25">
@@ -26407,19 +26528,19 @@
       </c>
       <c r="AV13" s="30" t="str">
         <f>VLOOKUP($AU13,Dummy!$A:$R,2,FALSE)</f>
-        <v>Sérvia</v>
+        <v>Bélgica</v>
       </c>
       <c r="AW13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,6,FALSE)</f>
@@ -26431,7 +26552,7 @@
       </c>
       <c r="BB13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,9,FALSE)</f>
@@ -26439,7 +26560,7 @@
       </c>
       <c r="BD13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,11,FALSE)</f>
@@ -26447,31 +26568,31 @@
       </c>
       <c r="BF13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,12,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>750</v>
       </c>
       <c r="BJ13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,16,FALSE)</f>
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="BK13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,17,FALSE)</f>
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="BL13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,18,FALSE)</f>
-        <v>920.35398230088492</v>
+        <v>911.76470588235293</v>
       </c>
     </row>
     <row r="14" spans="2:64" x14ac:dyDescent="0.25">
@@ -26480,19 +26601,19 @@
       </c>
       <c r="AV14" s="30" t="str">
         <f>VLOOKUP($AU14,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bulgária</v>
+        <v>Canadá</v>
       </c>
       <c r="AW14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,6,FALSE)</f>
@@ -26508,15 +26629,15 @@
       </c>
       <c r="BC14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,10,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,12,FALSE)</f>
@@ -26524,27 +26645,27 @@
       </c>
       <c r="BG14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,13,FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,15,FALSE)</f>
-        <v>666.66666666666663</v>
+        <v>800</v>
       </c>
       <c r="BJ14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,16,FALSE)</f>
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="BK14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,17,FALSE)</f>
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="BL14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,18,FALSE)</f>
-        <v>785.04672897196258</v>
+        <v>1038.6740331491712</v>
       </c>
     </row>
     <row r="15" spans="2:64" x14ac:dyDescent="0.25">
@@ -26553,19 +26674,19 @@
       </c>
       <c r="AV15" s="30" t="str">
         <f>VLOOKUP($AU15,Dummy!$A:$R,2,FALSE)</f>
-        <v>França</v>
+        <v>República Dominicana</v>
       </c>
       <c r="AW15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,6,FALSE)</f>
@@ -26581,7 +26702,7 @@
       </c>
       <c r="BC15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,9,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,10,FALSE)</f>
@@ -26597,66 +26718,66 @@
       </c>
       <c r="BG15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,13,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BH15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,15,FALSE)</f>
-        <v>333.33333333333331</v>
+        <v>800</v>
       </c>
       <c r="BJ15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,16,FALSE)</f>
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="BK15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,17,FALSE)</f>
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="BL15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,18,FALSE)</f>
-        <v>704.08163265306121</v>
+        <v>978.26086956521738</v>
       </c>
     </row>
     <row r="16" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="69"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="69"/>
-      <c r="X16" s="69"/>
-      <c r="Y16" s="69"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="60"/>
       <c r="AU16" s="31">
         <v>13</v>
       </c>
       <c r="AV16" s="30" t="str">
         <f>VLOOKUP($AU16,Dummy!$A:$R,2,FALSE)</f>
-        <v>Tailândia</v>
+        <v>Sérvia</v>
       </c>
       <c r="AW16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,4,FALSE)</f>
@@ -26684,7 +26805,7 @@
       </c>
       <c r="BD16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,10,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,11,FALSE)</f>
@@ -26692,11 +26813,11 @@
       </c>
       <c r="BF16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,14,FALSE)</f>
@@ -26704,60 +26825,60 @@
       </c>
       <c r="BI16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="BJ16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,16,FALSE)</f>
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="BK16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,17,FALSE)</f>
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="BL16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,18,FALSE)</f>
-        <v>894.73684210526312</v>
+        <v>920.35398230088492</v>
       </c>
     </row>
     <row r="17" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B17" s="16"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="66" t="s">
+      <c r="D17" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
       <c r="G17" s="20"/>
-      <c r="H17" s="67" t="s">
+      <c r="H17" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67" t="s">
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67" t="s">
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O17" s="67"/>
-      <c r="P17" s="67"/>
-      <c r="Q17" s="67" t="s">
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R17" s="67"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="67" t="s">
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U17" s="67"/>
-      <c r="V17" s="67"/>
-      <c r="W17" s="67" t="s">
+      <c r="U17" s="58"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
+      <c r="X17" s="58"/>
+      <c r="Y17" s="58"/>
       <c r="AA17" s="4" t="s">
         <v>38</v>
       </c>
@@ -26820,7 +26941,7 @@
       </c>
       <c r="AV17" s="30" t="str">
         <f>VLOOKUP($AU17,Dummy!$A:$R,2,FALSE)</f>
-        <v>República Tcheca</v>
+        <v>França</v>
       </c>
       <c r="AW17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,3,FALSE)</f>
@@ -26856,15 +26977,15 @@
       </c>
       <c r="BE17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,14,FALSE)</f>
@@ -26872,19 +26993,19 @@
       </c>
       <c r="BI17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>333.33333333333331</v>
       </c>
       <c r="BJ17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,16,FALSE)</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="BK17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="BL17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,18,FALSE)</f>
-        <v>773.33333333333337</v>
+        <v>704.08163265306121</v>
       </c>
     </row>
     <row r="18" spans="2:64" x14ac:dyDescent="0.25">
@@ -27021,7 +27142,7 @@
       </c>
       <c r="AV18" s="30" t="str">
         <f>VLOOKUP($AU18,Dummy!$A:$R,2,FALSE)</f>
-        <v>Bélgica</v>
+        <v>Tailândia</v>
       </c>
       <c r="AW18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,3,FALSE)</f>
@@ -27029,7 +27150,7 @@
       </c>
       <c r="AX18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,5,FALSE)</f>
@@ -27037,7 +27158,7 @@
       </c>
       <c r="AZ18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,7,FALSE)</f>
@@ -27057,7 +27178,7 @@
       </c>
       <c r="BE18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,11,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,12,FALSE)</f>
@@ -27065,27 +27186,27 @@
       </c>
       <c r="BG18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,13,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,15,FALSE)</f>
-        <v>0</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="BJ18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,16,FALSE)</f>
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="BK18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,17,FALSE)</f>
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="BL18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,18,FALSE)</f>
-        <v>727.27272727272725</v>
+        <v>920</v>
       </c>
     </row>
     <row r="19" spans="2:64" x14ac:dyDescent="0.25">
@@ -27094,7 +27215,7 @@
       </c>
       <c r="AV19" s="30" t="str">
         <f>VLOOKUP($AU19,Dummy!$A:$R,2,FALSE)</f>
-        <v>Coreia do Sul</v>
+        <v>República Tcheca</v>
       </c>
       <c r="AW19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,3,FALSE)</f>
@@ -27150,7 +27271,7 @@
       </c>
       <c r="BJ19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,16,FALSE)</f>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="BK19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,17,FALSE)</f>
@@ -27158,7 +27279,7 @@
       </c>
       <c r="BL19" s="29">
         <f>VLOOKUP($AU19,Dummy!$A:$R,18,FALSE)</f>
-        <v>706.66666666666663</v>
+        <v>773.33333333333337</v>
       </c>
     </row>
     <row r="20" spans="2:64" x14ac:dyDescent="0.25">
@@ -27167,7 +27288,7 @@
       </c>
       <c r="AV20" s="30" t="str">
         <f>VLOOKUP($AU20,Dummy!$A:$R,2,FALSE)</f>
-        <v>Estados Unidos</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="AW20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,3,FALSE)</f>
@@ -27223,15 +27344,15 @@
       </c>
       <c r="BJ20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,16,FALSE)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,17,FALSE)</f>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BL20" s="29">
         <f>VLOOKUP($AU20,Dummy!$A:$R,18,FALSE)</f>
-        <v>675</v>
+        <v>706.66666666666663</v>
       </c>
     </row>
     <row r="21" spans="2:64" x14ac:dyDescent="0.25">
@@ -27240,7 +27361,7 @@
       </c>
       <c r="AV21" s="30" t="str">
         <f>VLOOKUP($AU21,Dummy!$A:$R,2,FALSE)</f>
-        <v>Holanda</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AW21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,3,FALSE)</f>
@@ -27248,7 +27369,7 @@
       </c>
       <c r="AX21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,5,FALSE)</f>
@@ -27256,7 +27377,7 @@
       </c>
       <c r="AZ21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,6,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,7,FALSE)</f>
@@ -27280,7 +27401,7 @@
       </c>
       <c r="BF21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,12,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,13,FALSE)</f>
@@ -27288,7 +27409,7 @@
       </c>
       <c r="BH21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,14,FALSE)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,15,FALSE)</f>
@@ -27296,88 +27417,88 @@
       </c>
       <c r="BJ21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,16,FALSE)</f>
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="BK21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,17,FALSE)</f>
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="BL21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,18,FALSE)</f>
-        <v>640</v>
+        <v>696.77419354838707</v>
       </c>
     </row>
     <row r="22" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="69"/>
-      <c r="X22" s="69"/>
-      <c r="Y22" s="69"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
       <c r="AX22" s="53">
         <f>SUM(AX4:AX21)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B23" s="16"/>
       <c r="C23" s="24"/>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="67" t="s">
+      <c r="H23" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67" t="s">
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67" t="s">
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67"/>
-      <c r="Q23" s="67" t="s">
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="R23" s="67"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="67" t="s">
+      <c r="R23" s="58"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="U23" s="67"/>
-      <c r="V23" s="67"/>
-      <c r="W23" s="67" t="s">
+      <c r="U23" s="58"/>
+      <c r="V23" s="58"/>
+      <c r="W23" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="67"/>
-      <c r="Y23" s="67"/>
+      <c r="X23" s="58"/>
+      <c r="Y23" s="58"/>
       <c r="AA23" s="4" t="s">
         <v>38</v>
       </c>
@@ -27435,10 +27556,10 @@
       <c r="AT23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU23" s="58" t="s">
+      <c r="AU23" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="AV23" s="58"/>
+      <c r="AV23" s="66"/>
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B24" s="17" t="s">
@@ -27633,21 +27754,15 @@
   </sheetData>
   <sheetProtection password="CC01" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="39">
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="B10:Y10"/>
-    <mergeCell ref="B16:Y16"/>
-    <mergeCell ref="B2:Y2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="AU23:AV23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="T23:V23"/>
     <mergeCell ref="B22:Y22"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="H11:J11"/>
@@ -27663,58 +27778,69 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="T17:V17"/>
     <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="AU23:AV23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="B10:Y10"/>
+    <mergeCell ref="B16:Y16"/>
+    <mergeCell ref="B2:Y2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <conditionalFormatting sqref="T4:V7 T12:V13 T18:V18 T24:V24">
-    <cfRule type="expression" dxfId="10" priority="62">
+    <cfRule type="expression" dxfId="12" priority="64">
       <formula>$AA4&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:S7 Q12:S13 Q18:S18 Q24:S24">
-    <cfRule type="expression" dxfId="9" priority="61">
+    <cfRule type="expression" dxfId="11" priority="63">
       <formula>$AA4&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:P7 N12:P13 N18:P18 N24:P24">
-    <cfRule type="expression" dxfId="8" priority="60">
+    <cfRule type="expression" dxfId="10" priority="62">
       <formula>$AA4&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:M7 K12:M13 K18:M18 K24:M24">
-    <cfRule type="expression" dxfId="7" priority="59">
+    <cfRule type="expression" dxfId="9" priority="61">
       <formula>$AA4&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:J7 W4:Y7 H12:J13 W12:Y13 H18:J18 W18:Y18 H24:J24 W24:Y24">
-    <cfRule type="expression" dxfId="6" priority="58">
+    <cfRule type="expression" dxfId="8" priority="60">
       <formula>$AA4=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38 BM16:XFD16 Z38:AT38 BM21:XFD22 BM2:XFD10 BM12:XFD13 BM18:XFD18 BM24:XFD38 AU2:BL21 A16:AT18 A21:AT26 A1:XFD1 A2:AT13 A43:XFD1048576 A28:AT37 A27:B27 D27:AT27">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+  <conditionalFormatting sqref="A38 BM16:XFD16 Z38:AT38 BM21:XFD22 BM2:XFD10 BM12:XFD13 BM18:XFD18 BM24:XFD38 AU3:BL21 A16:AT18 A21:AT26 A1:XFD1 A2:AT13 A43:XFD1048576 A28:AT37 A27:B27 D27:AT27">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM11:XFD11">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"Brasil"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM17:XFD17">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Brasil"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM23:XFD23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM17:XFD17">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Brasil"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BM23:XFD23">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="AU2:BL2">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27724,7 +27850,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{846C8833-E3D2-4ED5-A15E-097CE8650A3F}">
+          <x14:cfRule type="expression" priority="3" id="{846C8833-E3D2-4ED5-A15E-097CE8650A3F}">
             <xm:f>OR(AND($AU4=Dummy!$Z$3,$AX$22=216),AND($AU4=Dummy!$Z$4,$AX$22=216),AND($AU4=Dummy!$Z$5,$AX$22=216),AND($AU4=Dummy!$Z$6,$AX$22=216),AND($AU4=Dummy!$Z$7,$AX$22=216),AND($AU4=Dummy!$Z$8,$AX$22=216),AND($AU4=Dummy!$Z$9,$AX$22=216),)</xm:f>
             <x14:dxf>
               <fill>
@@ -27734,7 +27860,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="2" id="{8397423E-44A1-4671-96AF-62E1881D16AF}">
+          <x14:cfRule type="expression" priority="4" id="{8397423E-44A1-4671-96AF-62E1881D16AF}">
             <xm:f>$AV4=Dummy!$Z$1</xm:f>
             <x14:dxf>
               <fill>
@@ -27753,23 +27879,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0c08e4af4d80db6585ac36ba965bb3a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e7db2db65f9cb533b4933096bc9b657" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -28002,32 +28111,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0F6A83-8A20-4128-AC08-526BDD0F4F5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5079BA11-B2F9-4F45-9320-B0ECAAE97A1E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1A4F3B6-8EF3-43FC-AA6E-56F4B11E76F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28044,4 +28145,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5079BA11-B2F9-4F45-9320-B0ECAAE97A1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0F6A83-8A20-4128-AC08-526BDD0F4F5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/VNL Feminina 2025.xlsx
+++ b/VNL Feminina 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mjunior\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD7A676-9529-4D4E-A1E2-48F68772FA66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{193B2670-6E0D-4629-8A7F-D6F0F42BF775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="CC01" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="1" activeTab="2" xr2:uid="{701403F6-3112-456D-B33A-FC5595D41656}"/>
@@ -282,9 +282,6 @@
     <t>SEDE</t>
   </si>
   <si>
-    <t>Pódio</t>
-  </si>
-  <si>
     <t>🥇</t>
   </si>
   <si>
@@ -323,6 +320,9 @@
   <si>
     <t>@maurilyn</t>
   </si>
+  <si>
+    <t>Classificação</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +332,7 @@
     <numFmt numFmtId="164" formatCode="#,##0,000"/>
     <numFmt numFmtId="165" formatCode="[$-416]d\-mmm;@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,8 +448,21 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,6 +556,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,7 +679,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -841,6 +860,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -863,15 +897,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -879,6 +904,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -890,22 +918,66 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,7 +985,18 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="102">
+  <dxfs count="103">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1004,12 +1087,6 @@
           <bgColor rgb="FFFF9B9B"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2446,7 +2523,7 @@
         <v>2</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" ref="Z4:Z9" si="9">IF(Y4&gt;=$A$16,Y4+$AA$3,Y4)</f>
+        <f t="shared" ref="Z4:Z20" si="9">IF(Y4&gt;=$A$16,Y4+$AA$3,Y4)</f>
         <v>2</v>
       </c>
     </row>
@@ -3036,6 +3113,13 @@
       <c r="W10" s="1">
         <v>7</v>
       </c>
+      <c r="Y10" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3128,6 +3212,13 @@
       <c r="W11" s="1">
         <v>8</v>
       </c>
+      <c r="Y11" s="1">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3220,6 +3311,13 @@
       <c r="W12" s="1">
         <v>9</v>
       </c>
+      <c r="Y12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3312,6 +3410,13 @@
       <c r="W13" s="1">
         <v>10</v>
       </c>
+      <c r="Y13" s="1">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3403,6 +3508,13 @@
       </c>
       <c r="W14" s="1">
         <v>11</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>12</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" si="9"/>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -3496,6 +3608,13 @@
       <c r="W15" s="1">
         <v>12</v>
       </c>
+      <c r="Y15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" si="9"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3588,8 +3707,15 @@
       <c r="W16" s="1">
         <v>13</v>
       </c>
+      <c r="Y16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z16" s="1">
+        <f t="shared" si="9"/>
+        <v>15</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3680,8 +3806,15 @@
       <c r="W17" s="1">
         <v>14</v>
       </c>
+      <c r="Y17" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z17" s="1">
+        <f t="shared" si="9"/>
+        <v>16</v>
+      </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3772,8 +3905,15 @@
       <c r="W18" s="1">
         <v>15</v>
       </c>
+      <c r="Y18" s="1">
+        <v>16</v>
+      </c>
+      <c r="Z18" s="1">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -3864,8 +4004,15 @@
       <c r="W19" s="1">
         <v>16</v>
       </c>
+      <c r="Y19" s="1">
+        <v>17</v>
+      </c>
+      <c r="Z19" s="1">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3956,13 +4103,16 @@
       <c r="W20" s="1">
         <v>17</v>
       </c>
+      <c r="Y20" s="1">
+        <v>18</v>
+      </c>
     </row>
-    <row r="23" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D25" s="58" t="s">
         <v>14</v>
       </c>
@@ -3994,7 +4144,7 @@
       <c r="V25" s="58"/>
       <c r="W25" s="58"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
@@ -4065,7 +4215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f>RANK(E27,$E$27:$E$34)+SUM(S27:V27)</f>
         <v>4</v>
@@ -4158,7 +4308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" ref="A28:A34" si="10">RANK(E28,$E$27:$E$34)+SUM(S28:V28)</f>
         <v>1</v>
@@ -4251,7 +4401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="10"/>
         <v>2</v>
@@ -4344,7 +4494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="10"/>
         <v>3</v>
@@ -4437,7 +4587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -4530,7 +4680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="10"/>
         <v>6</v>
@@ -4915,16 +5065,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="S1:W1"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:L25"/>
     <mergeCell ref="M25:O25"/>
     <mergeCell ref="P25:R25"/>
     <mergeCell ref="S25:W25"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="S1:W1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4988,88 +5138,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="AU2" s="71" t="s">
+      <c r="B2" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="AU2" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="73"/>
-      <c r="AX2" s="71" t="s">
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="76"/>
+      <c r="AX2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AY2" s="72"/>
-      <c r="AZ2" s="73"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AY2" s="75"/>
+      <c r="AZ2" s="76"/>
+      <c r="BA2" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="BB2" s="72"/>
-      <c r="BC2" s="72"/>
-      <c r="BD2" s="72"/>
-      <c r="BE2" s="72"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="71" t="s">
+      <c r="BB2" s="75"/>
+      <c r="BC2" s="75"/>
+      <c r="BD2" s="75"/>
+      <c r="BE2" s="75"/>
+      <c r="BF2" s="76"/>
+      <c r="BG2" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="BH2" s="72"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="71" t="s">
+      <c r="BH2" s="75"/>
+      <c r="BI2" s="76"/>
+      <c r="BJ2" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="72"/>
-      <c r="BL2" s="73"/>
+      <c r="BK2" s="75"/>
+      <c r="BL2" s="76"/>
     </row>
     <row r="3" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
+      <c r="B3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
       <c r="AU3" s="32" t="s">
         <v>43</v>
       </c>
@@ -5130,42 +5280,42 @@
         <v>2</v>
       </c>
       <c r="C4" s="24"/>
-      <c r="D4" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
+      <c r="D4" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
       <c r="G4" s="20"/>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76" t="s">
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76" t="s">
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76" t="s">
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76" t="s">
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76" t="s">
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="59"/>
       <c r="AA4" s="4" t="s">
         <v>38</v>
       </c>
@@ -7928,32 +8078,32 @@
       </c>
     </row>
     <row r="17" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
-      <c r="S17" s="74"/>
-      <c r="T17" s="74"/>
-      <c r="U17" s="74"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74"/>
-      <c r="X17" s="74"/>
-      <c r="Y17" s="74"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
       <c r="AU17" s="31">
         <v>14</v>
       </c>
@@ -8031,42 +8181,42 @@
         <v>2</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
+      <c r="D18" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76" t="s">
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76" t="s">
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="76"/>
-      <c r="P18" s="76"/>
-      <c r="Q18" s="76" t="s">
+      <c r="O18" s="59"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="76"/>
-      <c r="S18" s="76"/>
-      <c r="T18" s="76" t="s">
+      <c r="R18" s="59"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="76"/>
-      <c r="V18" s="76"/>
-      <c r="W18" s="76" t="s">
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="76"/>
-      <c r="Y18" s="76"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="59"/>
       <c r="AA18" s="4" t="s">
         <v>38</v>
       </c>
@@ -9140,10 +9290,10 @@
         <f t="shared" si="39"/>
         <v>75</v>
       </c>
-      <c r="AU23" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV23" s="67"/>
+      <c r="AU23" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV23" s="73"/>
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
@@ -9290,7 +9440,7 @@
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:64" x14ac:dyDescent="0.25">
@@ -9446,7 +9596,7 @@
       </c>
       <c r="AU25" s="55"/>
       <c r="AV25" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:64" x14ac:dyDescent="0.25">
@@ -9602,7 +9752,7 @@
       </c>
       <c r="AU26" s="57"/>
       <c r="AV26" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="2:64" x14ac:dyDescent="0.25">
@@ -10194,78 +10344,78 @@
       </c>
     </row>
     <row r="31" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="AU31" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV31" s="66"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="60"/>
+      <c r="V31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="60"/>
+      <c r="Y31" s="60"/>
+      <c r="AU31" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV31" s="78"/>
     </row>
     <row r="32" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="24"/>
-      <c r="D32" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
+      <c r="D32" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="76" t="s">
+      <c r="H32" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76" t="s">
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="76" t="s">
+      <c r="L32" s="59"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O32" s="76"/>
-      <c r="P32" s="76"/>
-      <c r="Q32" s="76" t="s">
+      <c r="O32" s="59"/>
+      <c r="P32" s="59"/>
+      <c r="Q32" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="76"/>
-      <c r="S32" s="76"/>
-      <c r="T32" s="76" t="s">
+      <c r="R32" s="59"/>
+      <c r="S32" s="59"/>
+      <c r="T32" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U32" s="76"/>
-      <c r="V32" s="76"/>
-      <c r="W32" s="76" t="s">
+      <c r="U32" s="59"/>
+      <c r="V32" s="59"/>
+      <c r="W32" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X32" s="76"/>
-      <c r="Y32" s="76"/>
+      <c r="X32" s="59"/>
+      <c r="Y32" s="59"/>
       <c r="AA32" s="4" t="s">
         <v>38</v>
       </c>
@@ -10323,10 +10473,10 @@
       <c r="AT32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU32" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV32" s="60"/>
+      <c r="AU32" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV32" s="65"/>
     </row>
     <row r="33" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B33" s="17">
@@ -10475,10 +10625,10 @@
         <f t="shared" ref="AT33:AT44" si="60">IF(D33&lt;F33,SUM(J33,M33,P33,S33,V33),SUM(H33,K33,N33,Q33,T33))</f>
         <v>98</v>
       </c>
-      <c r="AU33" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV33" s="62"/>
+      <c r="AU33" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV33" s="67"/>
     </row>
     <row r="34" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B34" s="17">
@@ -10623,10 +10773,10 @@
         <f t="shared" si="60"/>
         <v>76</v>
       </c>
-      <c r="AU34" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV34" s="62"/>
+      <c r="AU34" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV34" s="67"/>
     </row>
     <row r="35" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B35" s="17">
@@ -10771,10 +10921,10 @@
         <f t="shared" si="60"/>
         <v>77</v>
       </c>
-      <c r="AU35" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV35" s="62"/>
+      <c r="AU35" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV35" s="67"/>
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B36" s="17">
@@ -10923,10 +11073,10 @@
         <f t="shared" si="60"/>
         <v>99</v>
       </c>
-      <c r="AU36" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV36" s="64"/>
+      <c r="AU36" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV36" s="69"/>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B37" s="17">
@@ -12109,88 +12259,88 @@
       </c>
     </row>
     <row r="46" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="78" t="s">
+      <c r="B46" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
-      <c r="M46" s="78"/>
-      <c r="N46" s="78"/>
-      <c r="O46" s="78"/>
-      <c r="P46" s="78"/>
-      <c r="Q46" s="78"/>
-      <c r="R46" s="78"/>
-      <c r="S46" s="78"/>
-      <c r="T46" s="78"/>
-      <c r="U46" s="78"/>
-      <c r="V46" s="78"/>
-      <c r="W46" s="78"/>
-      <c r="X46" s="78"/>
-      <c r="Y46" s="78"/>
-      <c r="AU46" s="68" t="s">
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="61"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="61"/>
+      <c r="T46" s="61"/>
+      <c r="U46" s="61"/>
+      <c r="V46" s="61"/>
+      <c r="W46" s="61"/>
+      <c r="X46" s="61"/>
+      <c r="Y46" s="61"/>
+      <c r="AU46" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="AV46" s="69"/>
-      <c r="AW46" s="70"/>
-      <c r="AX46" s="68" t="s">
+      <c r="AV46" s="71"/>
+      <c r="AW46" s="72"/>
+      <c r="AX46" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AY46" s="69"/>
-      <c r="AZ46" s="70"/>
-      <c r="BA46" s="68" t="s">
+      <c r="AY46" s="71"/>
+      <c r="AZ46" s="72"/>
+      <c r="BA46" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="BB46" s="69"/>
-      <c r="BC46" s="69"/>
-      <c r="BD46" s="69"/>
-      <c r="BE46" s="69"/>
-      <c r="BF46" s="70"/>
-      <c r="BG46" s="68" t="s">
+      <c r="BB46" s="71"/>
+      <c r="BC46" s="71"/>
+      <c r="BD46" s="71"/>
+      <c r="BE46" s="71"/>
+      <c r="BF46" s="72"/>
+      <c r="BG46" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="BH46" s="69"/>
-      <c r="BI46" s="70"/>
-      <c r="BJ46" s="68" t="s">
+      <c r="BH46" s="71"/>
+      <c r="BI46" s="72"/>
+      <c r="BJ46" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="BK46" s="69"/>
-      <c r="BL46" s="70"/>
+      <c r="BK46" s="71"/>
+      <c r="BL46" s="72"/>
     </row>
     <row r="47" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="74" t="s">
+      <c r="B47" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="74"/>
-      <c r="J47" s="74"/>
-      <c r="K47" s="74"/>
-      <c r="L47" s="74"/>
-      <c r="M47" s="74"/>
-      <c r="N47" s="74"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="74"/>
-      <c r="Q47" s="74"/>
-      <c r="R47" s="74"/>
-      <c r="S47" s="74"/>
-      <c r="T47" s="74"/>
-      <c r="U47" s="74"/>
-      <c r="V47" s="74"/>
-      <c r="W47" s="74"/>
-      <c r="X47" s="74"/>
-      <c r="Y47" s="74"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="60"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="60"/>
+      <c r="O47" s="60"/>
+      <c r="P47" s="60"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="60"/>
+      <c r="S47" s="60"/>
+      <c r="T47" s="60"/>
+      <c r="U47" s="60"/>
+      <c r="V47" s="60"/>
+      <c r="W47" s="60"/>
+      <c r="X47" s="60"/>
+      <c r="Y47" s="60"/>
       <c r="AU47" s="32" t="s">
         <v>43</v>
       </c>
@@ -12251,42 +12401,42 @@
         <v>2</v>
       </c>
       <c r="C48" s="24"/>
-      <c r="D48" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
+      <c r="D48" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
       <c r="G48" s="20"/>
-      <c r="H48" s="76" t="s">
+      <c r="H48" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I48" s="76"/>
-      <c r="J48" s="76"/>
-      <c r="K48" s="76" t="s">
+      <c r="I48" s="59"/>
+      <c r="J48" s="59"/>
+      <c r="K48" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="76"/>
-      <c r="M48" s="76"/>
-      <c r="N48" s="76" t="s">
+      <c r="L48" s="59"/>
+      <c r="M48" s="59"/>
+      <c r="N48" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O48" s="76"/>
-      <c r="P48" s="76"/>
-      <c r="Q48" s="76" t="s">
+      <c r="O48" s="59"/>
+      <c r="P48" s="59"/>
+      <c r="Q48" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="76"/>
-      <c r="S48" s="76"/>
-      <c r="T48" s="76" t="s">
+      <c r="R48" s="59"/>
+      <c r="S48" s="59"/>
+      <c r="T48" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U48" s="76"/>
-      <c r="V48" s="76"/>
-      <c r="W48" s="76" t="s">
+      <c r="U48" s="59"/>
+      <c r="V48" s="59"/>
+      <c r="W48" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X48" s="76"/>
-      <c r="Y48" s="76"/>
+      <c r="X48" s="59"/>
+      <c r="Y48" s="59"/>
       <c r="AA48" s="4" t="s">
         <v>38</v>
       </c>
@@ -15033,32 +15183,32 @@
       </c>
     </row>
     <row r="61" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B61" s="74" t="s">
+      <c r="B61" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="77"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="74"/>
-      <c r="I61" s="74"/>
-      <c r="J61" s="74"/>
-      <c r="K61" s="74"/>
-      <c r="L61" s="74"/>
-      <c r="M61" s="74"/>
-      <c r="N61" s="74"/>
-      <c r="O61" s="74"/>
-      <c r="P61" s="74"/>
-      <c r="Q61" s="74"/>
-      <c r="R61" s="74"/>
-      <c r="S61" s="74"/>
-      <c r="T61" s="74"/>
-      <c r="U61" s="74"/>
-      <c r="V61" s="74"/>
-      <c r="W61" s="74"/>
-      <c r="X61" s="74"/>
-      <c r="Y61" s="74"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
+      <c r="J61" s="60"/>
+      <c r="K61" s="60"/>
+      <c r="L61" s="60"/>
+      <c r="M61" s="60"/>
+      <c r="N61" s="60"/>
+      <c r="O61" s="60"/>
+      <c r="P61" s="60"/>
+      <c r="Q61" s="60"/>
+      <c r="R61" s="60"/>
+      <c r="S61" s="60"/>
+      <c r="T61" s="60"/>
+      <c r="U61" s="60"/>
+      <c r="V61" s="60"/>
+      <c r="W61" s="60"/>
+      <c r="X61" s="60"/>
+      <c r="Y61" s="60"/>
       <c r="AU61" s="31">
         <v>14</v>
       </c>
@@ -15136,42 +15286,42 @@
         <v>2</v>
       </c>
       <c r="C62" s="24"/>
-      <c r="D62" s="76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="76"/>
-      <c r="F62" s="76"/>
+      <c r="D62" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="59"/>
+      <c r="F62" s="59"/>
       <c r="G62" s="20"/>
-      <c r="H62" s="76" t="s">
+      <c r="H62" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="76"/>
-      <c r="J62" s="76"/>
-      <c r="K62" s="76" t="s">
+      <c r="I62" s="59"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="76"/>
-      <c r="M62" s="76"/>
-      <c r="N62" s="76" t="s">
+      <c r="L62" s="59"/>
+      <c r="M62" s="59"/>
+      <c r="N62" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O62" s="76"/>
-      <c r="P62" s="76"/>
-      <c r="Q62" s="76" t="s">
+      <c r="O62" s="59"/>
+      <c r="P62" s="59"/>
+      <c r="Q62" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="76"/>
-      <c r="S62" s="76"/>
-      <c r="T62" s="76" t="s">
+      <c r="R62" s="59"/>
+      <c r="S62" s="59"/>
+      <c r="T62" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U62" s="76"/>
-      <c r="V62" s="76"/>
-      <c r="W62" s="76" t="s">
+      <c r="U62" s="59"/>
+      <c r="V62" s="59"/>
+      <c r="W62" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X62" s="76"/>
-      <c r="Y62" s="76"/>
+      <c r="X62" s="59"/>
+      <c r="Y62" s="59"/>
       <c r="AA62" s="4" t="s">
         <v>38</v>
       </c>
@@ -16261,10 +16411,10 @@
         <f t="shared" si="102"/>
         <v>112</v>
       </c>
-      <c r="AU67" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV67" s="67"/>
+      <c r="AU67" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV67" s="73"/>
     </row>
     <row r="68" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B68" s="18">
@@ -16411,7 +16561,7 @@
       </c>
       <c r="AU68" s="54"/>
       <c r="AV68" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="2:64" x14ac:dyDescent="0.25">
@@ -16567,7 +16717,7 @@
       </c>
       <c r="AU69" s="55"/>
       <c r="AV69" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="2:64" x14ac:dyDescent="0.25">
@@ -16715,7 +16865,7 @@
       </c>
       <c r="AU70" s="57"/>
       <c r="AV70" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="2:64" x14ac:dyDescent="0.25">
@@ -17307,78 +17457,78 @@
       </c>
     </row>
     <row r="75" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="74" t="s">
+      <c r="B75" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="74"/>
-      <c r="K75" s="74"/>
-      <c r="L75" s="74"/>
-      <c r="M75" s="74"/>
-      <c r="N75" s="74"/>
-      <c r="O75" s="74"/>
-      <c r="P75" s="74"/>
-      <c r="Q75" s="74"/>
-      <c r="R75" s="74"/>
-      <c r="S75" s="74"/>
-      <c r="T75" s="74"/>
-      <c r="U75" s="74"/>
-      <c r="V75" s="74"/>
-      <c r="W75" s="74"/>
-      <c r="X75" s="74"/>
-      <c r="Y75" s="74"/>
-      <c r="AU75" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV75" s="66"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="60"/>
+      <c r="L75" s="60"/>
+      <c r="M75" s="60"/>
+      <c r="N75" s="60"/>
+      <c r="O75" s="60"/>
+      <c r="P75" s="60"/>
+      <c r="Q75" s="60"/>
+      <c r="R75" s="60"/>
+      <c r="S75" s="60"/>
+      <c r="T75" s="60"/>
+      <c r="U75" s="60"/>
+      <c r="V75" s="60"/>
+      <c r="W75" s="60"/>
+      <c r="X75" s="60"/>
+      <c r="Y75" s="60"/>
+      <c r="AU75" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV75" s="78"/>
     </row>
     <row r="76" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C76" s="24"/>
-      <c r="D76" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="75"/>
-      <c r="F76" s="75"/>
+      <c r="D76" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
       <c r="G76" s="20"/>
-      <c r="H76" s="76" t="s">
+      <c r="H76" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="76"/>
-      <c r="J76" s="76"/>
-      <c r="K76" s="76" t="s">
+      <c r="I76" s="59"/>
+      <c r="J76" s="59"/>
+      <c r="K76" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L76" s="76"/>
-      <c r="M76" s="76"/>
-      <c r="N76" s="76" t="s">
+      <c r="L76" s="59"/>
+      <c r="M76" s="59"/>
+      <c r="N76" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O76" s="76"/>
-      <c r="P76" s="76"/>
-      <c r="Q76" s="76" t="s">
+      <c r="O76" s="59"/>
+      <c r="P76" s="59"/>
+      <c r="Q76" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R76" s="76"/>
-      <c r="S76" s="76"/>
-      <c r="T76" s="76" t="s">
+      <c r="R76" s="59"/>
+      <c r="S76" s="59"/>
+      <c r="T76" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U76" s="76"/>
-      <c r="V76" s="76"/>
-      <c r="W76" s="76" t="s">
+      <c r="U76" s="59"/>
+      <c r="V76" s="59"/>
+      <c r="W76" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X76" s="76"/>
-      <c r="Y76" s="76"/>
+      <c r="X76" s="59"/>
+      <c r="Y76" s="59"/>
       <c r="AA76" s="4" t="s">
         <v>38</v>
       </c>
@@ -17436,10 +17586,10 @@
       <c r="AT76" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU76" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV76" s="60"/>
+      <c r="AU76" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV76" s="65"/>
     </row>
     <row r="77" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B77" s="17">
@@ -17592,10 +17742,10 @@
         <f t="shared" ref="AT77:AT88" si="123">IF(D77&lt;F77,SUM(J77,M77,P77,S77,V77),SUM(H77,K77,N77,Q77,T77))</f>
         <v>112</v>
       </c>
-      <c r="AU77" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV77" s="62"/>
+      <c r="AU77" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV77" s="67"/>
     </row>
     <row r="78" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B78" s="17">
@@ -17748,10 +17898,10 @@
         <f t="shared" si="123"/>
         <v>99</v>
       </c>
-      <c r="AU78" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV78" s="62"/>
+      <c r="AU78" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV78" s="67"/>
     </row>
     <row r="79" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
@@ -17904,10 +18054,10 @@
         <f t="shared" si="123"/>
         <v>109</v>
       </c>
-      <c r="AU79" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV79" s="62"/>
+      <c r="AU79" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV79" s="67"/>
     </row>
     <row r="80" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B80" s="17">
@@ -18056,10 +18206,10 @@
         <f t="shared" si="123"/>
         <v>95</v>
       </c>
-      <c r="AU80" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV80" s="64"/>
+      <c r="AU80" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV80" s="69"/>
     </row>
     <row r="81" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
@@ -19246,88 +19396,88 @@
       </c>
     </row>
     <row r="90" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B90" s="78" t="s">
+      <c r="B90" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="C90" s="78"/>
-      <c r="D90" s="78"/>
-      <c r="E90" s="78"/>
-      <c r="F90" s="78"/>
-      <c r="G90" s="78"/>
-      <c r="H90" s="78"/>
-      <c r="I90" s="78"/>
-      <c r="J90" s="78"/>
-      <c r="K90" s="78"/>
-      <c r="L90" s="78"/>
-      <c r="M90" s="78"/>
-      <c r="N90" s="78"/>
-      <c r="O90" s="78"/>
-      <c r="P90" s="78"/>
-      <c r="Q90" s="78"/>
-      <c r="R90" s="78"/>
-      <c r="S90" s="78"/>
-      <c r="T90" s="78"/>
-      <c r="U90" s="78"/>
-      <c r="V90" s="78"/>
-      <c r="W90" s="78"/>
-      <c r="X90" s="78"/>
-      <c r="Y90" s="78"/>
-      <c r="AU90" s="68" t="s">
+      <c r="C90" s="61"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="61"/>
+      <c r="I90" s="61"/>
+      <c r="J90" s="61"/>
+      <c r="K90" s="61"/>
+      <c r="L90" s="61"/>
+      <c r="M90" s="61"/>
+      <c r="N90" s="61"/>
+      <c r="O90" s="61"/>
+      <c r="P90" s="61"/>
+      <c r="Q90" s="61"/>
+      <c r="R90" s="61"/>
+      <c r="S90" s="61"/>
+      <c r="T90" s="61"/>
+      <c r="U90" s="61"/>
+      <c r="V90" s="61"/>
+      <c r="W90" s="61"/>
+      <c r="X90" s="61"/>
+      <c r="Y90" s="61"/>
+      <c r="AU90" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="AV90" s="69"/>
-      <c r="AW90" s="70"/>
-      <c r="AX90" s="68" t="s">
+      <c r="AV90" s="71"/>
+      <c r="AW90" s="72"/>
+      <c r="AX90" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AY90" s="69"/>
-      <c r="AZ90" s="70"/>
-      <c r="BA90" s="68" t="s">
+      <c r="AY90" s="71"/>
+      <c r="AZ90" s="72"/>
+      <c r="BA90" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="BB90" s="69"/>
-      <c r="BC90" s="69"/>
-      <c r="BD90" s="69"/>
-      <c r="BE90" s="69"/>
-      <c r="BF90" s="70"/>
-      <c r="BG90" s="68" t="s">
+      <c r="BB90" s="71"/>
+      <c r="BC90" s="71"/>
+      <c r="BD90" s="71"/>
+      <c r="BE90" s="71"/>
+      <c r="BF90" s="72"/>
+      <c r="BG90" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="BH90" s="69"/>
-      <c r="BI90" s="70"/>
-      <c r="BJ90" s="68" t="s">
+      <c r="BH90" s="71"/>
+      <c r="BI90" s="72"/>
+      <c r="BJ90" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="BK90" s="69"/>
-      <c r="BL90" s="70"/>
+      <c r="BK90" s="71"/>
+      <c r="BL90" s="72"/>
     </row>
     <row r="91" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B91" s="74" t="s">
+      <c r="B91" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="C91" s="74"/>
-      <c r="D91" s="74"/>
-      <c r="E91" s="74"/>
-      <c r="F91" s="74"/>
-      <c r="G91" s="74"/>
-      <c r="H91" s="74"/>
-      <c r="I91" s="74"/>
-      <c r="J91" s="74"/>
-      <c r="K91" s="74"/>
-      <c r="L91" s="74"/>
-      <c r="M91" s="74"/>
-      <c r="N91" s="74"/>
-      <c r="O91" s="74"/>
-      <c r="P91" s="74"/>
-      <c r="Q91" s="74"/>
-      <c r="R91" s="74"/>
-      <c r="S91" s="74"/>
-      <c r="T91" s="74"/>
-      <c r="U91" s="74"/>
-      <c r="V91" s="74"/>
-      <c r="W91" s="74"/>
-      <c r="X91" s="74"/>
-      <c r="Y91" s="74"/>
+      <c r="C91" s="60"/>
+      <c r="D91" s="60"/>
+      <c r="E91" s="60"/>
+      <c r="F91" s="60"/>
+      <c r="G91" s="60"/>
+      <c r="H91" s="60"/>
+      <c r="I91" s="60"/>
+      <c r="J91" s="60"/>
+      <c r="K91" s="60"/>
+      <c r="L91" s="60"/>
+      <c r="M91" s="60"/>
+      <c r="N91" s="60"/>
+      <c r="O91" s="60"/>
+      <c r="P91" s="60"/>
+      <c r="Q91" s="60"/>
+      <c r="R91" s="60"/>
+      <c r="S91" s="60"/>
+      <c r="T91" s="60"/>
+      <c r="U91" s="60"/>
+      <c r="V91" s="60"/>
+      <c r="W91" s="60"/>
+      <c r="X91" s="60"/>
+      <c r="Y91" s="60"/>
       <c r="AU91" s="32" t="s">
         <v>43</v>
       </c>
@@ -19388,42 +19538,42 @@
         <v>2</v>
       </c>
       <c r="C92" s="24"/>
-      <c r="D92" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E92" s="75"/>
-      <c r="F92" s="75"/>
+      <c r="D92" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
       <c r="G92" s="20"/>
-      <c r="H92" s="76" t="s">
+      <c r="H92" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I92" s="76"/>
-      <c r="J92" s="76"/>
-      <c r="K92" s="76" t="s">
+      <c r="I92" s="59"/>
+      <c r="J92" s="59"/>
+      <c r="K92" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L92" s="76"/>
-      <c r="M92" s="76"/>
-      <c r="N92" s="76" t="s">
+      <c r="L92" s="59"/>
+      <c r="M92" s="59"/>
+      <c r="N92" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O92" s="76"/>
-      <c r="P92" s="76"/>
-      <c r="Q92" s="76" t="s">
+      <c r="O92" s="59"/>
+      <c r="P92" s="59"/>
+      <c r="Q92" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R92" s="76"/>
-      <c r="S92" s="76"/>
-      <c r="T92" s="76" t="s">
+      <c r="R92" s="59"/>
+      <c r="S92" s="59"/>
+      <c r="T92" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U92" s="76"/>
-      <c r="V92" s="76"/>
-      <c r="W92" s="76" t="s">
+      <c r="U92" s="59"/>
+      <c r="V92" s="59"/>
+      <c r="W92" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X92" s="76"/>
-      <c r="Y92" s="76"/>
+      <c r="X92" s="59"/>
+      <c r="Y92" s="59"/>
       <c r="AA92" s="4" t="s">
         <v>38</v>
       </c>
@@ -22166,32 +22316,32 @@
       </c>
     </row>
     <row r="105" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B105" s="74" t="s">
+      <c r="B105" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C105" s="74"/>
-      <c r="D105" s="74"/>
-      <c r="E105" s="77"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="74"/>
-      <c r="H105" s="74"/>
-      <c r="I105" s="74"/>
-      <c r="J105" s="74"/>
-      <c r="K105" s="74"/>
-      <c r="L105" s="74"/>
-      <c r="M105" s="74"/>
-      <c r="N105" s="74"/>
-      <c r="O105" s="74"/>
-      <c r="P105" s="74"/>
-      <c r="Q105" s="74"/>
-      <c r="R105" s="74"/>
-      <c r="S105" s="74"/>
-      <c r="T105" s="74"/>
-      <c r="U105" s="74"/>
-      <c r="V105" s="74"/>
-      <c r="W105" s="74"/>
-      <c r="X105" s="74"/>
-      <c r="Y105" s="74"/>
+      <c r="C105" s="60"/>
+      <c r="D105" s="60"/>
+      <c r="E105" s="62"/>
+      <c r="F105" s="60"/>
+      <c r="G105" s="60"/>
+      <c r="H105" s="60"/>
+      <c r="I105" s="60"/>
+      <c r="J105" s="60"/>
+      <c r="K105" s="60"/>
+      <c r="L105" s="60"/>
+      <c r="M105" s="60"/>
+      <c r="N105" s="60"/>
+      <c r="O105" s="60"/>
+      <c r="P105" s="60"/>
+      <c r="Q105" s="60"/>
+      <c r="R105" s="60"/>
+      <c r="S105" s="60"/>
+      <c r="T105" s="60"/>
+      <c r="U105" s="60"/>
+      <c r="V105" s="60"/>
+      <c r="W105" s="60"/>
+      <c r="X105" s="60"/>
+      <c r="Y105" s="60"/>
       <c r="AU105" s="31">
         <v>14</v>
       </c>
@@ -22269,42 +22419,42 @@
         <v>2</v>
       </c>
       <c r="C106" s="24"/>
-      <c r="D106" s="76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E106" s="76"/>
-      <c r="F106" s="76"/>
+      <c r="D106" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E106" s="59"/>
+      <c r="F106" s="59"/>
       <c r="G106" s="20"/>
-      <c r="H106" s="76" t="s">
+      <c r="H106" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I106" s="76"/>
-      <c r="J106" s="76"/>
-      <c r="K106" s="76" t="s">
+      <c r="I106" s="59"/>
+      <c r="J106" s="59"/>
+      <c r="K106" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L106" s="76"/>
-      <c r="M106" s="76"/>
-      <c r="N106" s="76" t="s">
+      <c r="L106" s="59"/>
+      <c r="M106" s="59"/>
+      <c r="N106" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O106" s="76"/>
-      <c r="P106" s="76"/>
-      <c r="Q106" s="76" t="s">
+      <c r="O106" s="59"/>
+      <c r="P106" s="59"/>
+      <c r="Q106" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R106" s="76"/>
-      <c r="S106" s="76"/>
-      <c r="T106" s="76" t="s">
+      <c r="R106" s="59"/>
+      <c r="S106" s="59"/>
+      <c r="T106" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U106" s="76"/>
-      <c r="V106" s="76"/>
-      <c r="W106" s="76" t="s">
+      <c r="U106" s="59"/>
+      <c r="V106" s="59"/>
+      <c r="W106" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X106" s="76"/>
-      <c r="Y106" s="76"/>
+      <c r="X106" s="59"/>
+      <c r="Y106" s="59"/>
       <c r="AA106" s="4" t="s">
         <v>38</v>
       </c>
@@ -23394,10 +23544,10 @@
         <f t="shared" si="165"/>
         <v>98</v>
       </c>
-      <c r="AU111" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV111" s="67"/>
+      <c r="AU111" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV111" s="73"/>
     </row>
     <row r="112" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
@@ -23544,7 +23694,7 @@
       </c>
       <c r="AU112" s="54"/>
       <c r="AV112" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" spans="2:48" x14ac:dyDescent="0.25">
@@ -23696,7 +23846,7 @@
       </c>
       <c r="AU113" s="55"/>
       <c r="AV113" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114" spans="2:48" x14ac:dyDescent="0.25">
@@ -23852,7 +24002,7 @@
       </c>
       <c r="AU114" s="57"/>
       <c r="AV114" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="2:48" x14ac:dyDescent="0.25">
@@ -24460,78 +24610,78 @@
       </c>
     </row>
     <row r="119" spans="2:48" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B119" s="74" t="s">
+      <c r="B119" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C119" s="74"/>
-      <c r="D119" s="74"/>
-      <c r="E119" s="74"/>
-      <c r="F119" s="74"/>
-      <c r="G119" s="74"/>
-      <c r="H119" s="74"/>
-      <c r="I119" s="74"/>
-      <c r="J119" s="74"/>
-      <c r="K119" s="74"/>
-      <c r="L119" s="74"/>
-      <c r="M119" s="74"/>
-      <c r="N119" s="74"/>
-      <c r="O119" s="74"/>
-      <c r="P119" s="74"/>
-      <c r="Q119" s="74"/>
-      <c r="R119" s="74"/>
-      <c r="S119" s="74"/>
-      <c r="T119" s="74"/>
-      <c r="U119" s="74"/>
-      <c r="V119" s="74"/>
-      <c r="W119" s="74"/>
-      <c r="X119" s="74"/>
-      <c r="Y119" s="74"/>
-      <c r="AU119" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV119" s="66"/>
+      <c r="C119" s="60"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="60"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="60"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="60"/>
+      <c r="J119" s="60"/>
+      <c r="K119" s="60"/>
+      <c r="L119" s="60"/>
+      <c r="M119" s="60"/>
+      <c r="N119" s="60"/>
+      <c r="O119" s="60"/>
+      <c r="P119" s="60"/>
+      <c r="Q119" s="60"/>
+      <c r="R119" s="60"/>
+      <c r="S119" s="60"/>
+      <c r="T119" s="60"/>
+      <c r="U119" s="60"/>
+      <c r="V119" s="60"/>
+      <c r="W119" s="60"/>
+      <c r="X119" s="60"/>
+      <c r="Y119" s="60"/>
+      <c r="AU119" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV119" s="78"/>
     </row>
     <row r="120" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B120" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="24"/>
-      <c r="D120" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E120" s="75"/>
-      <c r="F120" s="75"/>
+      <c r="D120" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E120" s="63"/>
+      <c r="F120" s="63"/>
       <c r="G120" s="20"/>
-      <c r="H120" s="76" t="s">
+      <c r="H120" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I120" s="76"/>
-      <c r="J120" s="76"/>
-      <c r="K120" s="76" t="s">
+      <c r="I120" s="59"/>
+      <c r="J120" s="59"/>
+      <c r="K120" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L120" s="76"/>
-      <c r="M120" s="76"/>
-      <c r="N120" s="76" t="s">
+      <c r="L120" s="59"/>
+      <c r="M120" s="59"/>
+      <c r="N120" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O120" s="76"/>
-      <c r="P120" s="76"/>
-      <c r="Q120" s="76" t="s">
+      <c r="O120" s="59"/>
+      <c r="P120" s="59"/>
+      <c r="Q120" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R120" s="76"/>
-      <c r="S120" s="76"/>
-      <c r="T120" s="76" t="s">
+      <c r="R120" s="59"/>
+      <c r="S120" s="59"/>
+      <c r="T120" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U120" s="76"/>
-      <c r="V120" s="76"/>
-      <c r="W120" s="76" t="s">
+      <c r="U120" s="59"/>
+      <c r="V120" s="59"/>
+      <c r="W120" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X120" s="76"/>
-      <c r="Y120" s="76"/>
+      <c r="X120" s="59"/>
+      <c r="Y120" s="59"/>
       <c r="AA120" s="4" t="s">
         <v>38</v>
       </c>
@@ -24589,10 +24739,10 @@
       <c r="AT120" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU120" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV120" s="60"/>
+      <c r="AU120" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV120" s="65"/>
     </row>
     <row r="121" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B121" s="17">
@@ -24741,10 +24891,10 @@
         <f t="shared" ref="AT121:AT132" si="186">IF(D121&lt;F121,SUM(J121,M121,P121,S121,V121),SUM(H121,K121,N121,Q121,T121))</f>
         <v>102</v>
       </c>
-      <c r="AU121" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV121" s="62"/>
+      <c r="AU121" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV121" s="67"/>
     </row>
     <row r="122" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B122" s="17">
@@ -24893,10 +25043,10 @@
         <f t="shared" si="186"/>
         <v>96</v>
       </c>
-      <c r="AU122" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV122" s="62"/>
+      <c r="AU122" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV122" s="67"/>
     </row>
     <row r="123" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B123" s="17">
@@ -25041,10 +25191,10 @@
         <f t="shared" si="186"/>
         <v>75</v>
       </c>
-      <c r="AU123" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV123" s="62"/>
+      <c r="AU123" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV123" s="67"/>
     </row>
     <row r="124" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B124" s="17">
@@ -25197,10 +25347,10 @@
         <f t="shared" si="186"/>
         <v>105</v>
       </c>
-      <c r="AU124" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV124" s="64"/>
+      <c r="AU124" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV124" s="69"/>
     </row>
     <row r="125" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B125" s="17">
@@ -26377,16 +26527,83 @@
   </sheetData>
   <sheetProtection password="CC01" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="111">
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B2:Y2"/>
-    <mergeCell ref="B17:Y17"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="AU79:AV79"/>
+    <mergeCell ref="AU80:AV80"/>
+    <mergeCell ref="AU119:AV119"/>
+    <mergeCell ref="AU111:AV111"/>
+    <mergeCell ref="AU90:AW90"/>
+    <mergeCell ref="AX90:AZ90"/>
+    <mergeCell ref="BA90:BF90"/>
+    <mergeCell ref="AU120:AV120"/>
+    <mergeCell ref="AU121:AV121"/>
+    <mergeCell ref="AU122:AV122"/>
+    <mergeCell ref="AU123:AV123"/>
+    <mergeCell ref="AU124:AV124"/>
+    <mergeCell ref="BG90:BI90"/>
+    <mergeCell ref="BJ90:BL90"/>
+    <mergeCell ref="AU23:AV23"/>
+    <mergeCell ref="AU67:AV67"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AU46:AW46"/>
+    <mergeCell ref="AX46:AZ46"/>
+    <mergeCell ref="BA46:BF46"/>
+    <mergeCell ref="BG46:BI46"/>
+    <mergeCell ref="BJ46:BL46"/>
+    <mergeCell ref="AU31:AV31"/>
+    <mergeCell ref="AU32:AV32"/>
+    <mergeCell ref="AU33:AV33"/>
+    <mergeCell ref="AU34:AV34"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AU36:AV36"/>
+    <mergeCell ref="AU75:AV75"/>
+    <mergeCell ref="AU76:AV76"/>
+    <mergeCell ref="AU77:AV77"/>
+    <mergeCell ref="AU78:AV78"/>
+    <mergeCell ref="B119:Y119"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="N120:P120"/>
+    <mergeCell ref="Q120:S120"/>
+    <mergeCell ref="T120:V120"/>
+    <mergeCell ref="W120:Y120"/>
+    <mergeCell ref="B105:Y105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="N106:P106"/>
+    <mergeCell ref="Q106:S106"/>
+    <mergeCell ref="T106:V106"/>
+    <mergeCell ref="W106:Y106"/>
+    <mergeCell ref="W76:Y76"/>
+    <mergeCell ref="B90:Y90"/>
+    <mergeCell ref="B91:Y91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="H92:J92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="N92:P92"/>
+    <mergeCell ref="Q92:S92"/>
+    <mergeCell ref="T92:V92"/>
+    <mergeCell ref="W92:Y92"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="Q76:S76"/>
+    <mergeCell ref="T76:V76"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="T62:V62"/>
+    <mergeCell ref="W62:Y62"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="T48:V48"/>
     <mergeCell ref="B75:Y75"/>
     <mergeCell ref="B46:Y46"/>
     <mergeCell ref="B47:Y47"/>
@@ -26411,431 +26628,364 @@
     <mergeCell ref="H62:J62"/>
     <mergeCell ref="K62:M62"/>
     <mergeCell ref="N62:P62"/>
-    <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="T62:V62"/>
-    <mergeCell ref="W62:Y62"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="T48:V48"/>
-    <mergeCell ref="W76:Y76"/>
-    <mergeCell ref="B90:Y90"/>
-    <mergeCell ref="B91:Y91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="H92:J92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="N92:P92"/>
-    <mergeCell ref="Q92:S92"/>
-    <mergeCell ref="T92:V92"/>
-    <mergeCell ref="W92:Y92"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="H76:J76"/>
-    <mergeCell ref="K76:M76"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="Q76:S76"/>
-    <mergeCell ref="T76:V76"/>
-    <mergeCell ref="B119:Y119"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="H120:J120"/>
-    <mergeCell ref="K120:M120"/>
-    <mergeCell ref="N120:P120"/>
-    <mergeCell ref="Q120:S120"/>
-    <mergeCell ref="T120:V120"/>
-    <mergeCell ref="W120:Y120"/>
-    <mergeCell ref="B105:Y105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="H106:J106"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="N106:P106"/>
-    <mergeCell ref="Q106:S106"/>
-    <mergeCell ref="T106:V106"/>
-    <mergeCell ref="W106:Y106"/>
-    <mergeCell ref="BG90:BI90"/>
-    <mergeCell ref="BJ90:BL90"/>
-    <mergeCell ref="AU23:AV23"/>
-    <mergeCell ref="AU67:AV67"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BJ2:BL2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AU46:AW46"/>
-    <mergeCell ref="AX46:AZ46"/>
-    <mergeCell ref="BA46:BF46"/>
-    <mergeCell ref="BG46:BI46"/>
-    <mergeCell ref="BJ46:BL46"/>
-    <mergeCell ref="AU31:AV31"/>
-    <mergeCell ref="AU32:AV32"/>
-    <mergeCell ref="AU33:AV33"/>
-    <mergeCell ref="AU34:AV34"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AU36:AV36"/>
-    <mergeCell ref="AU75:AV75"/>
-    <mergeCell ref="AU76:AV76"/>
-    <mergeCell ref="AU111:AV111"/>
-    <mergeCell ref="AU90:AW90"/>
-    <mergeCell ref="AX90:AZ90"/>
-    <mergeCell ref="BA90:BF90"/>
-    <mergeCell ref="AU120:AV120"/>
-    <mergeCell ref="AU121:AV121"/>
-    <mergeCell ref="AU122:AV122"/>
-    <mergeCell ref="AU123:AV123"/>
-    <mergeCell ref="AU124:AV124"/>
-    <mergeCell ref="AU77:AV77"/>
-    <mergeCell ref="AU78:AV78"/>
-    <mergeCell ref="AU79:AV79"/>
-    <mergeCell ref="AU80:AV80"/>
-    <mergeCell ref="AU119:AV119"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B2:Y2"/>
+    <mergeCell ref="B17:Y17"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="T5:V16">
-    <cfRule type="expression" dxfId="101" priority="88">
+    <cfRule type="expression" dxfId="102" priority="88">
       <formula>$AA5&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:S16">
-    <cfRule type="expression" dxfId="100" priority="87">
+    <cfRule type="expression" dxfId="101" priority="87">
       <formula>$AA5&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:P16">
-    <cfRule type="expression" dxfId="99" priority="86">
+    <cfRule type="expression" dxfId="100" priority="86">
       <formula>$AA5&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:M16">
-    <cfRule type="expression" dxfId="98" priority="85">
+    <cfRule type="expression" dxfId="99" priority="85">
       <formula>$AA5&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:J16">
-    <cfRule type="expression" dxfId="97" priority="84">
+    <cfRule type="expression" dxfId="98" priority="84">
       <formula>$AA5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:Y16">
-    <cfRule type="expression" dxfId="96" priority="83">
+    <cfRule type="expression" dxfId="97" priority="83">
       <formula>$AA5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:V44">
-    <cfRule type="expression" dxfId="95" priority="82">
+    <cfRule type="expression" dxfId="96" priority="82">
       <formula>$AA33&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33:S44">
-    <cfRule type="expression" dxfId="94" priority="81">
+    <cfRule type="expression" dxfId="95" priority="81">
       <formula>$AA33&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:P44">
-    <cfRule type="expression" dxfId="93" priority="80">
+    <cfRule type="expression" dxfId="94" priority="80">
       <formula>$AA33&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33:M44">
-    <cfRule type="expression" dxfId="92" priority="79">
+    <cfRule type="expression" dxfId="93" priority="79">
       <formula>$AA33&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:J44">
-    <cfRule type="expression" dxfId="91" priority="78">
+    <cfRule type="expression" dxfId="92" priority="78">
       <formula>$AA33=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33:Y44">
-    <cfRule type="expression" dxfId="90" priority="77">
+    <cfRule type="expression" dxfId="91" priority="77">
       <formula>$AA33=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:V30">
-    <cfRule type="expression" dxfId="89" priority="76">
+    <cfRule type="expression" dxfId="90" priority="76">
       <formula>$AA19&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q19:S30">
-    <cfRule type="expression" dxfId="88" priority="75">
+    <cfRule type="expression" dxfId="89" priority="75">
       <formula>$AA19&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:P30">
-    <cfRule type="expression" dxfId="87" priority="74">
+    <cfRule type="expression" dxfId="88" priority="74">
       <formula>$AA19&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:M30">
-    <cfRule type="expression" dxfId="86" priority="73">
+    <cfRule type="expression" dxfId="87" priority="73">
       <formula>$AA19&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:J30">
-    <cfRule type="expression" dxfId="85" priority="72">
+    <cfRule type="expression" dxfId="86" priority="72">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y30">
-    <cfRule type="expression" dxfId="84" priority="71">
+    <cfRule type="expression" dxfId="85" priority="71">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T49:V60">
-    <cfRule type="expression" dxfId="83" priority="70">
+    <cfRule type="expression" dxfId="84" priority="70">
       <formula>$AA49&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q49:S60">
-    <cfRule type="expression" dxfId="82" priority="69">
+    <cfRule type="expression" dxfId="83" priority="69">
       <formula>$AA49&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N49:P60">
-    <cfRule type="expression" dxfId="81" priority="68">
+    <cfRule type="expression" dxfId="82" priority="68">
       <formula>$AA49&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49:M60">
-    <cfRule type="expression" dxfId="80" priority="67">
+    <cfRule type="expression" dxfId="81" priority="67">
       <formula>$AA49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:J60">
-    <cfRule type="expression" dxfId="79" priority="66">
+    <cfRule type="expression" dxfId="80" priority="66">
       <formula>$AA49=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W49:Y60">
-    <cfRule type="expression" dxfId="78" priority="65">
+    <cfRule type="expression" dxfId="79" priority="65">
       <formula>$AA49=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T77:V88">
-    <cfRule type="expression" dxfId="77" priority="64">
+    <cfRule type="expression" dxfId="78" priority="64">
       <formula>$AA77&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q77:S88">
-    <cfRule type="expression" dxfId="76" priority="63">
+    <cfRule type="expression" dxfId="77" priority="63">
       <formula>$AA77&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N77:P88">
-    <cfRule type="expression" dxfId="75" priority="62">
+    <cfRule type="expression" dxfId="76" priority="62">
       <formula>$AA77&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77:M88">
-    <cfRule type="expression" dxfId="74" priority="61">
+    <cfRule type="expression" dxfId="75" priority="61">
       <formula>$AA77&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77:J88">
-    <cfRule type="expression" dxfId="73" priority="60">
+    <cfRule type="expression" dxfId="74" priority="60">
       <formula>$AA77=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W77:Y88">
-    <cfRule type="expression" dxfId="72" priority="59">
+    <cfRule type="expression" dxfId="73" priority="59">
       <formula>$AA77=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T63:V74">
-    <cfRule type="expression" dxfId="71" priority="58">
+    <cfRule type="expression" dxfId="72" priority="58">
       <formula>$AA63&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63:S74">
-    <cfRule type="expression" dxfId="70" priority="57">
+    <cfRule type="expression" dxfId="71" priority="57">
       <formula>$AA63&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N63:P74">
-    <cfRule type="expression" dxfId="69" priority="56">
+    <cfRule type="expression" dxfId="70" priority="56">
       <formula>$AA63&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:M74">
-    <cfRule type="expression" dxfId="68" priority="55">
+    <cfRule type="expression" dxfId="69" priority="55">
       <formula>$AA63&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H63:J74">
-    <cfRule type="expression" dxfId="67" priority="54">
+    <cfRule type="expression" dxfId="68" priority="54">
       <formula>$AA63=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63:Y74">
-    <cfRule type="expression" dxfId="66" priority="53">
+    <cfRule type="expression" dxfId="67" priority="53">
       <formula>$AA63=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T93:V104">
-    <cfRule type="expression" dxfId="65" priority="52">
+    <cfRule type="expression" dxfId="66" priority="52">
       <formula>$AA93&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q93:S104">
-    <cfRule type="expression" dxfId="64" priority="51">
+    <cfRule type="expression" dxfId="65" priority="51">
       <formula>$AA93&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N93:P104">
-    <cfRule type="expression" dxfId="63" priority="50">
+    <cfRule type="expression" dxfId="64" priority="50">
       <formula>$AA93&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:M104">
-    <cfRule type="expression" dxfId="62" priority="49">
+    <cfRule type="expression" dxfId="63" priority="49">
       <formula>$AA93&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H93:J104">
-    <cfRule type="expression" dxfId="61" priority="48">
+    <cfRule type="expression" dxfId="62" priority="48">
       <formula>$AA93=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W93:Y104">
-    <cfRule type="expression" dxfId="60" priority="47">
+    <cfRule type="expression" dxfId="61" priority="47">
       <formula>$AA93=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T121:V132">
-    <cfRule type="expression" dxfId="59" priority="46">
+    <cfRule type="expression" dxfId="60" priority="46">
       <formula>$AA121&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q121:S132">
-    <cfRule type="expression" dxfId="58" priority="45">
+    <cfRule type="expression" dxfId="59" priority="45">
       <formula>$AA121&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N121:P132">
-    <cfRule type="expression" dxfId="57" priority="44">
+    <cfRule type="expression" dxfId="58" priority="44">
       <formula>$AA121&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K121:M132">
-    <cfRule type="expression" dxfId="56" priority="43">
+    <cfRule type="expression" dxfId="57" priority="43">
       <formula>$AA121&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H121:J132">
-    <cfRule type="expression" dxfId="55" priority="42">
+    <cfRule type="expression" dxfId="56" priority="42">
       <formula>$AA121=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W121:Y132">
-    <cfRule type="expression" dxfId="54" priority="41">
+    <cfRule type="expression" dxfId="55" priority="41">
       <formula>$AA121=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T107:V118">
-    <cfRule type="expression" dxfId="53" priority="40">
+    <cfRule type="expression" dxfId="54" priority="40">
       <formula>$AA107&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q107:S118">
-    <cfRule type="expression" dxfId="52" priority="39">
+    <cfRule type="expression" dxfId="53" priority="39">
       <formula>$AA107&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N107:P118">
-    <cfRule type="expression" dxfId="51" priority="38">
+    <cfRule type="expression" dxfId="52" priority="38">
       <formula>$AA107&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:M118">
-    <cfRule type="expression" dxfId="50" priority="37">
+    <cfRule type="expression" dxfId="51" priority="37">
       <formula>$AA107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H107:J118">
-    <cfRule type="expression" dxfId="49" priority="36">
+    <cfRule type="expression" dxfId="50" priority="36">
       <formula>$AA107=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W107:Y118">
-    <cfRule type="expression" dxfId="48" priority="35">
+    <cfRule type="expression" dxfId="49" priority="35">
       <formula>$AA107=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:XFD21 AY22:XFD22 BM46:XFD69 BM90:XFD113 A1:XFD1 A27:XFD30 A22:AW22 A71:XFD74 A115:XFD118 A2:AT21 A23:AT26 AW23:XFD26 A46:AT70 AW70:XFD70 A90:AT114 AW114:XFD114 A37:XFD45 A31:AT36 AW31:XFD36 A81:XFD89 A75:AT80 AW75:XFD80 A125:XFD1048576 A119:AT124 AW119:XFD124">
-    <cfRule type="cellIs" dxfId="47" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="34" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y19">
-    <cfRule type="expression" dxfId="46" priority="33">
+    <cfRule type="expression" dxfId="47" priority="33">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y30">
-    <cfRule type="expression" dxfId="45" priority="32">
+    <cfRule type="expression" dxfId="46" priority="32">
       <formula>$AA19=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:BL3 AV4:BL21">
-    <cfRule type="cellIs" dxfId="44" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="31" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU66:AW66 AY66:BL66 AW67:BL69">
-    <cfRule type="cellIs" dxfId="43" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU46:BL47 AV48:BL64">
-    <cfRule type="cellIs" dxfId="42" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU110:AW110 AY110:BL110 AW111:BL113">
-    <cfRule type="cellIs" dxfId="41" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="17" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU90:BL91 AV92:BL108">
-    <cfRule type="cellIs" dxfId="40" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU21:BL21">
-    <cfRule type="expression" dxfId="39" priority="12">
+    <cfRule type="expression" dxfId="40" priority="12">
       <formula>$AX$22=216</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV65:BL65">
-    <cfRule type="cellIs" dxfId="38" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="11" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU65:BL65">
-    <cfRule type="expression" dxfId="37" priority="8">
+    <cfRule type="expression" dxfId="38" priority="8">
       <formula>$AX$22=216</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV109:BL109">
-    <cfRule type="cellIs" dxfId="36" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="7" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU109:BL109">
-    <cfRule type="expression" dxfId="35" priority="4">
+    <cfRule type="expression" dxfId="36" priority="4">
       <formula>$AX$22=216</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU31:AU36">
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU75:AU80">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU119:AU124">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26981,7 +27131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8907CF4-F9AC-40E8-A2EF-9961349DD93C}">
-  <dimension ref="B2:BL39"/>
+  <dimension ref="B2:BM59"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
@@ -27014,119 +27164,120 @@
     <col min="32" max="34" width="4.28515625" style="4" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="3.28515625" style="4" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="3.42578125" style="4" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="2.7109375" style="4" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="6.7109375" style="4" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="2.140625" style="4" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="4" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="2.28515625" style="4" hidden="1" customWidth="1"/>
     <col min="40" max="40" width="5.5703125" style="4" hidden="1" customWidth="1"/>
     <col min="41" max="41" width="5.42578125" style="4" hidden="1" customWidth="1"/>
     <col min="42" max="44" width="4.28515625" style="4" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="3.28515625" style="4" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="3.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="45" max="46" width="4.42578125" style="4" hidden="1" customWidth="1"/>
     <col min="47" max="47" width="4.7109375" style="4" customWidth="1"/>
     <col min="48" max="48" width="22.7109375" style="4" customWidth="1"/>
-    <col min="49" max="49" width="4.7109375" style="4" customWidth="1"/>
-    <col min="50" max="60" width="3.7109375" style="4" customWidth="1"/>
-    <col min="61" max="61" width="6.7109375" style="4" customWidth="1"/>
-    <col min="62" max="63" width="5.7109375" style="4" customWidth="1"/>
-    <col min="64" max="64" width="6.7109375" style="4" customWidth="1"/>
-    <col min="65" max="16384" width="9.140625" style="4"/>
+    <col min="49" max="49" width="3.7109375" style="4" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="4.7109375" style="4" customWidth="1"/>
+    <col min="51" max="61" width="3.7109375" style="4" customWidth="1"/>
+    <col min="62" max="62" width="6.7109375" style="4" customWidth="1"/>
+    <col min="63" max="64" width="5.7109375" style="4" customWidth="1"/>
+    <col min="65" max="65" width="6.7109375" style="4" customWidth="1"/>
+    <col min="66" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="78" t="s">
+    <row r="2" spans="2:65" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="AU2" s="71" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="AU2" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="73"/>
-      <c r="AX2" s="71" t="s">
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="75"/>
+      <c r="AX2" s="76"/>
+      <c r="AY2" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AY2" s="72"/>
-      <c r="AZ2" s="73"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="75"/>
+      <c r="BA2" s="76"/>
+      <c r="BB2" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="BB2" s="72"/>
-      <c r="BC2" s="72"/>
-      <c r="BD2" s="72"/>
-      <c r="BE2" s="72"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="71" t="s">
+      <c r="BC2" s="75"/>
+      <c r="BD2" s="75"/>
+      <c r="BE2" s="75"/>
+      <c r="BF2" s="75"/>
+      <c r="BG2" s="76"/>
+      <c r="BH2" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="BH2" s="72"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="71" t="s">
+      <c r="BI2" s="75"/>
+      <c r="BJ2" s="76"/>
+      <c r="BK2" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="72"/>
-      <c r="BL2" s="73"/>
+      <c r="BL2" s="75"/>
+      <c r="BM2" s="76"/>
     </row>
-    <row r="3" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
+      <c r="D3" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
       <c r="G3" s="20"/>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76" t="s">
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76" t="s">
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76" t="s">
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76" t="s">
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="76"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
       <c r="AA3" s="4" t="s">
         <v>38</v>
       </c>
@@ -27190,56 +27341,57 @@
       <c r="AV3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="AW3" s="32" t="s">
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="AX3" s="32" t="s">
+      <c r="AY3" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="AY3" s="32" t="s">
+      <c r="AZ3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AZ3" s="32" t="s">
-        <v>25</v>
-      </c>
       <c r="BA3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="BB3" s="32" t="s">
+      <c r="BC3" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="BC3" s="32" t="s">
+      <c r="BD3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="BD3" s="32" t="s">
+      <c r="BE3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="BE3" s="32" t="s">
+      <c r="BF3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="BF3" s="32" t="s">
+      <c r="BG3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="BG3" s="32" t="s">
+      <c r="BH3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BH3" s="32" t="s">
+      <c r="BI3" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="BI3" s="32" t="s">
+      <c r="BJ3" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="BJ3" s="32" t="s">
+      <c r="BK3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="BK3" s="32" t="s">
+      <c r="BL3" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="BL3" s="32" t="s">
+      <c r="BM3" s="32" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
         <v>45861</v>
       </c>
@@ -27247,30 +27399,46 @@
         <f>IF(Dummy!C37&lt;12,"1º Colocado",Dummy!B37)</f>
         <v>Itália</v>
       </c>
-      <c r="D4" s="56"/>
+      <c r="D4" s="56">
+        <v>3</v>
+      </c>
       <c r="E4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="34"/>
+      <c r="F4" s="34">
+        <v>0</v>
+      </c>
       <c r="G4" s="21" t="str">
         <f>IF(Dummy!C44&lt;12,"8º Colocado",Dummy!B44)</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="H4" s="33"/>
+      <c r="H4" s="33">
+        <v>25</v>
+      </c>
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="34">
+        <v>22</v>
+      </c>
+      <c r="K4" s="33">
+        <v>25</v>
+      </c>
       <c r="L4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="33"/>
+      <c r="M4" s="34">
+        <v>21</v>
+      </c>
+      <c r="N4" s="33">
+        <v>28</v>
+      </c>
       <c r="O4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="34"/>
+      <c r="P4" s="34">
+        <v>26</v>
+      </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="11" t="s">
         <v>6</v>
@@ -27283,30 +27451,30 @@
       <c r="V4" s="34"/>
       <c r="W4" s="12">
         <f>SUM(H4,K4,N4,Q4,T4)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="X4" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y4" s="14">
         <f>SUM(J4,M4,P4,S4,V4)</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AA4" s="4">
         <f>AD4+AE4</f>
-        <v>0</v>
-      </c>
-      <c r="AB4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="4" t="str">
         <f>IF(OR(D4="",F4=""),0,IF(D4&gt;F4,C4,G4))</f>
-        <v>0</v>
+        <v>Itália</v>
       </c>
       <c r="AC4" s="4">
         <f>IF(OR(D4="",F4=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" s="4">
         <f>IF(OR(D4="",F4=""),0,IF(D4&gt;F4,D4,F4))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE4" s="4">
         <f>IF(OR(D4="",F4=""),0,IF(D4&gt;F4,F4,D4))</f>
@@ -27314,7 +27482,7 @@
       </c>
       <c r="AF4" s="4">
         <f>IF(AND(AD4=3,AE4=0),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" s="4">
         <f>IF(AND(AD4=3,AE4=1),1,0)</f>
@@ -27326,19 +27494,19 @@
       </c>
       <c r="AI4" s="4">
         <f>IF(D4&gt;F4,SUM(H4,K4,N4,Q4,T4,),SUM(J4,M4,P4,S4,V4))</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AJ4" s="4">
         <f>IF(D4&gt;F4,SUM(J4,M4,P4,S4,V4),SUM(H4,K4,N4,Q4,T4))</f>
-        <v>0</v>
-      </c>
-      <c r="AL4" s="4">
+        <v>69</v>
+      </c>
+      <c r="AL4" s="4" t="str">
         <f>IF(OR(D4="",F4=""),0,IF(D4&lt;F4,C4,G4))</f>
-        <v>0</v>
+        <v>Estados Unidos</v>
       </c>
       <c r="AM4" s="4">
         <f>IF(OR(D4="",F4=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" s="4">
         <f>IF(OR(D4="",F4=""),0,IF(D4&lt;F4,D4,F4))</f>
@@ -27346,7 +27514,7 @@
       </c>
       <c r="AO4" s="4">
         <f>IF(OR(D4="",F4=""),0,IF(D4&lt;F4,F4,D4))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP4" s="4">
         <f>IF(AND(AN4=2,AO4=3),1,0)</f>
@@ -27358,15 +27526,15 @@
       </c>
       <c r="AR4" s="4">
         <f>IF(AND(AN4=0,AO4=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4" s="4">
         <f>IF(D4&lt;F4,SUM(H4,K4,N4,Q4,T4,),SUM(J4,M4,P4,S4,V4))</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT4" s="4">
         <f>IF(D4&lt;F4,SUM(J4,M4,P4,S4,V4),SUM(H4,K4,N4,Q4,T4))</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU4" s="31">
         <v>1</v>
@@ -27375,143 +27543,170 @@
         <f>VLOOKUP($AU4,Dummy!$A:$R,2,FALSE)</f>
         <v>Itália</v>
       </c>
-      <c r="AW4" s="28">
+      <c r="AW4" s="30">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,3,FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AX4" s="28">
+      <c r="AY4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY4" s="28">
+      <c r="AZ4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,5,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AZ4" s="28">
+      <c r="BA4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BA4" s="28">
+      <c r="BB4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,7,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="BB4" s="28">
+      <c r="BC4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC4" s="28">
+      <c r="BD4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,9,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="28">
+      <c r="BE4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="28">
+      <c r="BF4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,11,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BF4" s="28">
+      <c r="BG4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,12,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BG4" s="28">
+      <c r="BH4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,13,FALSE)</f>
         <v>36</v>
       </c>
-      <c r="BH4" s="28">
+      <c r="BI4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,14,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BI4" s="29">
+      <c r="BJ4" s="29">
         <f>VLOOKUP($AU4,Dummy!$A:$R,15,FALSE)</f>
         <v>5142.8571428571431</v>
       </c>
-      <c r="BJ4" s="28">
+      <c r="BK4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,16,FALSE)</f>
         <v>1037</v>
       </c>
-      <c r="BK4" s="28">
+      <c r="BL4" s="28">
         <f>VLOOKUP($AU4,Dummy!$A:$R,17,FALSE)</f>
         <v>822</v>
       </c>
-      <c r="BL4" s="29">
+      <c r="BM4" s="29">
         <f>VLOOKUP($AU4,Dummy!$A:$R,18,FALSE)</f>
         <v>1261.5571776155718</v>
       </c>
     </row>
-    <row r="5" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B5" s="17">
-        <v>45862</v>
+        <v>45861</v>
       </c>
       <c r="C5" s="25" t="str">
-        <f>IF(Dummy!C38&lt;12,"2º Colocado",Dummy!B38)</f>
-        <v>Brasil</v>
-      </c>
-      <c r="D5" s="56"/>
+        <f>IF(Dummy!C40&lt;12,"4º Colocado",Dummy!B40)</f>
+        <v>Polônia</v>
+      </c>
+      <c r="D5" s="56">
+        <v>3</v>
+      </c>
       <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="34">
+        <v>2</v>
+      </c>
       <c r="G5" s="21" t="str">
-        <f>IF(Dummy!C43&lt;12,"7º Colocado",Dummy!B43)</f>
-        <v>Alemanha</v>
-      </c>
-      <c r="H5" s="33"/>
+        <f>IF(Dummy!C41&lt;12,"5º Colocado",Dummy!B41)</f>
+        <v>China</v>
+      </c>
+      <c r="H5" s="33">
+        <v>17</v>
+      </c>
       <c r="I5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="33"/>
+      <c r="J5" s="34">
+        <v>25</v>
+      </c>
+      <c r="K5" s="33">
+        <v>25</v>
+      </c>
       <c r="L5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="34"/>
-      <c r="N5" s="33"/>
+      <c r="M5" s="34">
+        <v>20</v>
+      </c>
+      <c r="N5" s="33">
+        <v>19</v>
+      </c>
       <c r="O5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="33"/>
+      <c r="P5" s="34">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="33">
+        <v>25</v>
+      </c>
       <c r="R5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="34"/>
-      <c r="T5" s="33"/>
+      <c r="S5" s="34">
+        <v>19</v>
+      </c>
+      <c r="T5" s="33">
+        <v>15</v>
+      </c>
       <c r="U5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="34"/>
+      <c r="V5" s="34">
+        <v>12</v>
+      </c>
       <c r="W5" s="12">
         <f>SUM(H5,K5,N5,Q5,T5)</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="X5" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y5" s="14">
         <f>SUM(J5,M5,P5,S5,V5)</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AA5" s="4">
         <f>AD5+AE5</f>
-        <v>0</v>
-      </c>
-      <c r="AB5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="4" t="str">
         <f>IF(OR(D5="",F5=""),0,IF(D5&gt;F5,C5,G5))</f>
-        <v>0</v>
+        <v>Polônia</v>
       </c>
       <c r="AC5" s="4">
         <f>IF(OR(D5="",F5=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(OR(D5="",F5=""),0,IF(D5&gt;F5,D5,F5))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE5" s="4">
         <f>IF(OR(D5="",F5=""),0,IF(D5&gt;F5,F5,D5))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF5" s="4">
         <f>IF(AND(AD5=3,AE5=0),1,0)</f>
@@ -27523,35 +27718,35 @@
       </c>
       <c r="AH5" s="4">
         <f>IF(AND(AD5=3,AE5=2),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" s="4">
         <f>IF(D5&gt;F5,SUM(H5,K5,N5,Q5,T5,),SUM(J5,M5,P5,S5,V5))</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AJ5" s="4">
         <f>IF(D5&gt;F5,SUM(J5,M5,P5,S5,V5),SUM(H5,K5,N5,Q5,T5))</f>
-        <v>0</v>
-      </c>
-      <c r="AL5" s="4">
+        <v>101</v>
+      </c>
+      <c r="AL5" s="4" t="str">
         <f>IF(OR(D5="",F5=""),0,IF(D5&lt;F5,C5,G5))</f>
-        <v>0</v>
+        <v>China</v>
       </c>
       <c r="AM5" s="4">
         <f>IF(OR(D5="",F5=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="4">
         <f>IF(OR(D5="",F5=""),0,IF(D5&lt;F5,D5,F5))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO5" s="4">
         <f>IF(OR(D5="",F5=""),0,IF(D5&lt;F5,F5,D5))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP5" s="4">
         <f>IF(AND(AN5=2,AO5=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" s="4">
         <f>IF(AND(AN5=1,AO5=3),1,0)</f>
@@ -27563,11 +27758,11 @@
       </c>
       <c r="AS5" s="4">
         <f>IF(D5&lt;F5,SUM(H5,K5,N5,Q5,T5,),SUM(J5,M5,P5,S5,V5))</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AT5" s="4">
         <f>IF(D5&lt;F5,SUM(J5,M5,P5,S5,V5),SUM(H5,K5,N5,Q5,T5))</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AU5" s="31">
         <v>2</v>
@@ -27576,103 +27771,122 @@
         <f>VLOOKUP($AU5,Dummy!$A:$R,2,FALSE)</f>
         <v>Brasil</v>
       </c>
-      <c r="AW5" s="28">
+      <c r="AW5" s="30">
+        <v>2</v>
+      </c>
+      <c r="AX5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,3,FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AX5" s="28">
+      <c r="AY5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY5" s="28">
+      <c r="AZ5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,5,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AZ5" s="28">
+      <c r="BA5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,6,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BA5" s="28">
+      <c r="BB5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,7,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BB5" s="28">
+      <c r="BC5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,8,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BC5" s="28">
+      <c r="BD5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,9,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BD5" s="28">
+      <c r="BE5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="28">
+      <c r="BF5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,11,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BF5" s="28">
+      <c r="BG5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,12,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="28">
+      <c r="BH5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,13,FALSE)</f>
         <v>33</v>
       </c>
-      <c r="BH5" s="28">
+      <c r="BI5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,14,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="BI5" s="29">
+      <c r="BJ5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,15,FALSE)</f>
         <v>3000</v>
       </c>
-      <c r="BJ5" s="28">
+      <c r="BK5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,16,FALSE)</f>
         <v>1051</v>
       </c>
-      <c r="BK5" s="28">
+      <c r="BL5" s="28">
         <f>VLOOKUP($AU5,Dummy!$A:$R,17,FALSE)</f>
         <v>906</v>
       </c>
-      <c r="BL5" s="29">
+      <c r="BM5" s="29">
         <f>VLOOKUP($AU5,Dummy!$A:$R,18,FALSE)</f>
         <v>1160.0441501103753</v>
       </c>
     </row>
-    <row r="6" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B6" s="17">
         <v>45862</v>
       </c>
       <c r="C6" s="25" t="str">
-        <f>IF(Dummy!C39&lt;12,"3º Colocado",Dummy!B39)</f>
-        <v>Japão</v>
-      </c>
-      <c r="D6" s="56"/>
+        <f>IF(Dummy!C38&lt;12,"2º Colocado",Dummy!B38)</f>
+        <v>Brasil</v>
+      </c>
+      <c r="D6" s="56">
+        <v>3</v>
+      </c>
       <c r="E6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="34">
+        <v>0</v>
+      </c>
       <c r="G6" s="21" t="str">
-        <f>IF(Dummy!C42&lt;12,"6º Colocado",Dummy!B42)</f>
-        <v>Turquia</v>
-      </c>
-      <c r="H6" s="33"/>
+        <f>IF(Dummy!C43&lt;12,"7º Colocado",Dummy!B43)</f>
+        <v>Alemanha</v>
+      </c>
+      <c r="H6" s="33">
+        <v>25</v>
+      </c>
       <c r="I6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="33"/>
+      <c r="J6" s="34">
+        <v>19</v>
+      </c>
+      <c r="K6" s="33">
+        <v>26</v>
+      </c>
       <c r="L6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="34"/>
-      <c r="N6" s="33"/>
+      <c r="M6" s="34">
+        <v>24</v>
+      </c>
+      <c r="N6" s="33">
+        <v>25</v>
+      </c>
       <c r="O6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="34"/>
+      <c r="P6" s="34">
+        <v>14</v>
+      </c>
       <c r="Q6" s="33"/>
       <c r="R6" s="11" t="s">
         <v>6</v>
@@ -27685,30 +27899,30 @@
       <c r="V6" s="34"/>
       <c r="W6" s="12">
         <f>SUM(H6,K6,N6,Q6,T6)</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="X6" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y6" s="14">
         <f>SUM(J6,M6,P6,S6,V6)</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AA6" s="4">
         <f>AD6+AE6</f>
-        <v>0</v>
-      </c>
-      <c r="AB6" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="4" t="str">
         <f>IF(OR(D6="",F6=""),0,IF(D6&gt;F6,C6,G6))</f>
-        <v>0</v>
+        <v>Brasil</v>
       </c>
       <c r="AC6" s="4">
         <f>IF(OR(D6="",F6=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(OR(D6="",F6=""),0,IF(D6&gt;F6,D6,F6))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE6" s="4">
         <f>IF(OR(D6="",F6=""),0,IF(D6&gt;F6,F6,D6))</f>
@@ -27716,7 +27930,7 @@
       </c>
       <c r="AF6" s="4">
         <f>IF(AND(AD6=3,AE6=0),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="4">
         <f>IF(AND(AD6=3,AE6=1),1,0)</f>
@@ -27728,19 +27942,19 @@
       </c>
       <c r="AI6" s="4">
         <f>IF(D6&gt;F6,SUM(H6,K6,N6,Q6,T6,),SUM(J6,M6,P6,S6,V6))</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AJ6" s="4">
         <f>IF(D6&gt;F6,SUM(J6,M6,P6,S6,V6),SUM(H6,K6,N6,Q6,T6))</f>
-        <v>0</v>
-      </c>
-      <c r="AL6" s="4">
+        <v>57</v>
+      </c>
+      <c r="AL6" s="4" t="str">
         <f>IF(OR(D6="",F6=""),0,IF(D6&lt;F6,C6,G6))</f>
-        <v>0</v>
+        <v>Alemanha</v>
       </c>
       <c r="AM6" s="4">
         <f>IF(OR(D6="",F6=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" s="4">
         <f>IF(OR(D6="",F6=""),0,IF(D6&lt;F6,D6,F6))</f>
@@ -27748,7 +27962,7 @@
       </c>
       <c r="AO6" s="4">
         <f>IF(OR(D6="",F6=""),0,IF(D6&lt;F6,F6,D6))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP6" s="4">
         <f>IF(AND(AN6=2,AO6=3),1,0)</f>
@@ -27760,15 +27974,15 @@
       </c>
       <c r="AR6" s="4">
         <f>IF(AND(AN6=0,AO6=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="4">
         <f>IF(D6&lt;F6,SUM(H6,K6,N6,Q6,T6,),SUM(J6,M6,P6,S6,V6))</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT6" s="4">
         <f>IF(D6&lt;F6,SUM(J6,M6,P6,S6,V6),SUM(H6,K6,N6,Q6,T6))</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU6" s="31">
         <v>3</v>
@@ -27777,143 +27991,170 @@
         <f>VLOOKUP($AU6,Dummy!$A:$R,2,FALSE)</f>
         <v>Japão</v>
       </c>
-      <c r="AW6" s="28">
+      <c r="AW6" s="30">
+        <v>3</v>
+      </c>
+      <c r="AX6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,3,FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AX6" s="28">
+      <c r="AY6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY6" s="28">
+      <c r="AZ6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,5,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="AZ6" s="28">
+      <c r="BA6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,6,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BA6" s="28">
+      <c r="BB6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,7,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BB6" s="28">
+      <c r="BC6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC6" s="28">
+      <c r="BD6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,9,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BD6" s="28">
+      <c r="BE6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE6" s="28">
+      <c r="BF6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,11,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BF6" s="28">
+      <c r="BG6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,12,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BG6" s="28">
+      <c r="BH6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,13,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="BH6" s="28">
+      <c r="BI6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,14,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="BI6" s="29">
+      <c r="BJ6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,15,FALSE)</f>
         <v>2500</v>
       </c>
-      <c r="BJ6" s="28">
+      <c r="BK6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,16,FALSE)</f>
         <v>966</v>
       </c>
-      <c r="BK6" s="28">
+      <c r="BL6" s="28">
         <f>VLOOKUP($AU6,Dummy!$A:$R,17,FALSE)</f>
         <v>858</v>
       </c>
-      <c r="BL6" s="29">
+      <c r="BM6" s="29">
         <f>VLOOKUP($AU6,Dummy!$A:$R,18,FALSE)</f>
         <v>1125.8741258741259</v>
       </c>
     </row>
-    <row r="7" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="C7" s="25" t="str">
-        <f>IF(Dummy!C40&lt;12,"4º Colocado",Dummy!B40)</f>
-        <v>Polônia</v>
-      </c>
-      <c r="D7" s="56"/>
+        <f>IF(Dummy!C39&lt;12,"3º Colocado",Dummy!B39)</f>
+        <v>Japão</v>
+      </c>
+      <c r="D7" s="56">
+        <v>3</v>
+      </c>
       <c r="E7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="34"/>
+      <c r="F7" s="34">
+        <v>2</v>
+      </c>
       <c r="G7" s="21" t="str">
-        <f>IF(Dummy!C41&lt;12,"5º Colocado",Dummy!B41)</f>
-        <v>China</v>
-      </c>
-      <c r="H7" s="33"/>
+        <f>IF(Dummy!C42&lt;12,"6º Colocado",Dummy!B42)</f>
+        <v>Turquia</v>
+      </c>
+      <c r="H7" s="33">
+        <v>25</v>
+      </c>
       <c r="I7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="33"/>
+      <c r="J7" s="34">
+        <v>21</v>
+      </c>
+      <c r="K7" s="33">
+        <v>16</v>
+      </c>
       <c r="L7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="34"/>
-      <c r="N7" s="33"/>
+      <c r="M7" s="34">
+        <v>25</v>
+      </c>
+      <c r="N7" s="33">
+        <v>25</v>
+      </c>
       <c r="O7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="33"/>
+      <c r="P7" s="34">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="33">
+        <v>22</v>
+      </c>
       <c r="R7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="34"/>
-      <c r="T7" s="33"/>
+      <c r="S7" s="34">
+        <v>25</v>
+      </c>
+      <c r="T7" s="33">
+        <v>15</v>
+      </c>
       <c r="U7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="34"/>
+      <c r="V7" s="34">
+        <v>9</v>
+      </c>
       <c r="W7" s="12">
         <f>SUM(H7,K7,N7,Q7,T7)</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="X7" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y7" s="14">
         <f>SUM(J7,M7,P7,S7,V7)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA7" s="4">
         <f>AD7+AE7</f>
-        <v>0</v>
-      </c>
-      <c r="AB7" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB7" s="4" t="str">
         <f>IF(OR(D7="",F7=""),0,IF(D7&gt;F7,C7,G7))</f>
-        <v>0</v>
+        <v>Japão</v>
       </c>
       <c r="AC7" s="4">
         <f>IF(OR(D7="",F7=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(OR(D7="",F7=""),0,IF(D7&gt;F7,D7,F7))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" s="4">
         <f>IF(OR(D7="",F7=""),0,IF(D7&gt;F7,F7,D7))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" s="4">
         <f>IF(AND(AD7=3,AE7=0),1,0)</f>
@@ -27925,35 +28166,35 @@
       </c>
       <c r="AH7" s="4">
         <f>IF(AND(AD7=3,AE7=2),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="4">
         <f>IF(D7&gt;F7,SUM(H7,K7,N7,Q7,T7,),SUM(J7,M7,P7,S7,V7))</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AJ7" s="4">
         <f>IF(D7&gt;F7,SUM(J7,M7,P7,S7,V7),SUM(H7,K7,N7,Q7,T7))</f>
-        <v>0</v>
-      </c>
-      <c r="AL7" s="4">
+        <v>100</v>
+      </c>
+      <c r="AL7" s="4" t="str">
         <f>IF(OR(D7="",F7=""),0,IF(D7&lt;F7,C7,G7))</f>
-        <v>0</v>
+        <v>Turquia</v>
       </c>
       <c r="AM7" s="4">
         <f>IF(OR(D7="",F7=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="4">
         <f>IF(OR(D7="",F7=""),0,IF(D7&lt;F7,D7,F7))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO7" s="4">
         <f>IF(OR(D7="",F7=""),0,IF(D7&lt;F7,F7,D7))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP7" s="4">
         <f>IF(AND(AN7=2,AO7=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="4">
         <f>IF(AND(AN7=1,AO7=3),1,0)</f>
@@ -27965,11 +28206,11 @@
       </c>
       <c r="AS7" s="4">
         <f>IF(D7&lt;F7,SUM(H7,K7,N7,Q7,T7,),SUM(J7,M7,P7,S7,V7))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT7" s="4">
         <f>IF(D7&lt;F7,SUM(J7,M7,P7,S7,V7),SUM(H7,K7,N7,Q7,T7))</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AU7" s="31">
         <v>4</v>
@@ -27978,72 +28219,75 @@
         <f>VLOOKUP($AU7,Dummy!$A:$R,2,FALSE)</f>
         <v>Polônia</v>
       </c>
-      <c r="AW7" s="28">
+      <c r="AW7" s="30">
+        <v>4</v>
+      </c>
+      <c r="AX7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,3,FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AX7" s="28">
+      <c r="AY7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY7" s="28">
+      <c r="AZ7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,5,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="AZ7" s="28">
+      <c r="BA7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,6,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BA7" s="28">
+      <c r="BB7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,7,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BB7" s="28">
+      <c r="BC7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,8,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BC7" s="28">
+      <c r="BD7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,9,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BD7" s="28">
+      <c r="BE7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE7" s="28">
+      <c r="BF7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF7" s="28">
+      <c r="BG7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,12,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BG7" s="28">
+      <c r="BH7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,13,FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BH7" s="28">
+      <c r="BI7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,14,FALSE)</f>
         <v>15</v>
       </c>
-      <c r="BI7" s="29">
+      <c r="BJ7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,15,FALSE)</f>
         <v>2066.666666666667</v>
       </c>
-      <c r="BJ7" s="28">
+      <c r="BK7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,16,FALSE)</f>
         <v>1067</v>
       </c>
-      <c r="BK7" s="28">
+      <c r="BL7" s="28">
         <f>VLOOKUP($AU7,Dummy!$A:$R,17,FALSE)</f>
         <v>958</v>
       </c>
-      <c r="BL7" s="29">
+      <c r="BM7" s="29">
         <f>VLOOKUP($AU7,Dummy!$A:$R,18,FALSE)</f>
         <v>1113.7787056367431</v>
       </c>
     </row>
-    <row r="8" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU8" s="31">
         <v>5</v>
       </c>
@@ -28051,72 +28295,75 @@
         <f>VLOOKUP($AU8,Dummy!$A:$R,2,FALSE)</f>
         <v>China</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="30">
+        <v>5</v>
+      </c>
+      <c r="AX8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,3,FALSE)</f>
         <v>24</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AY8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AZ8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,5,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="BA8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,6,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BB8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BC8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,8,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BD8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,9,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BE8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BF8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,11,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BG8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,12,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BH8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,13,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BI8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,14,FALSE)</f>
         <v>20</v>
       </c>
-      <c r="BI8" s="29">
+      <c r="BJ8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,15,FALSE)</f>
         <v>1500</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BK8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,16,FALSE)</f>
         <v>1142</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BL8" s="28">
         <f>VLOOKUP($AU8,Dummy!$A:$R,17,FALSE)</f>
         <v>1059</v>
       </c>
-      <c r="BL8" s="29">
+      <c r="BM8" s="29">
         <f>VLOOKUP($AU8,Dummy!$A:$R,18,FALSE)</f>
         <v>1078.3758262511803</v>
       </c>
     </row>
-    <row r="9" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU9" s="31">
         <v>6</v>
       </c>
@@ -28124,98 +28371,101 @@
         <f>VLOOKUP($AU9,Dummy!$A:$R,2,FALSE)</f>
         <v>Turquia</v>
       </c>
-      <c r="AW9" s="28">
+      <c r="AW9" s="30">
+        <v>6</v>
+      </c>
+      <c r="AX9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,3,FALSE)</f>
         <v>23</v>
       </c>
-      <c r="AX9" s="28">
+      <c r="AY9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY9" s="28">
+      <c r="AZ9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,5,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="AZ9" s="28">
+      <c r="BA9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,6,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BA9" s="28">
+      <c r="BB9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,7,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BB9" s="28">
+      <c r="BC9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC9" s="28">
+      <c r="BD9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,9,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BD9" s="28">
+      <c r="BE9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE9" s="28">
+      <c r="BF9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF9" s="28">
+      <c r="BG9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,12,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BG9" s="28">
+      <c r="BH9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,13,FALSE)</f>
         <v>28</v>
       </c>
-      <c r="BH9" s="28">
+      <c r="BI9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,14,FALSE)</f>
         <v>17</v>
       </c>
-      <c r="BI9" s="29">
+      <c r="BJ9" s="29">
         <f>VLOOKUP($AU9,Dummy!$A:$R,15,FALSE)</f>
         <v>1647.0588235294117</v>
       </c>
-      <c r="BJ9" s="28">
+      <c r="BK9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,16,FALSE)</f>
         <v>1025</v>
       </c>
-      <c r="BK9" s="28">
+      <c r="BL9" s="28">
         <f>VLOOKUP($AU9,Dummy!$A:$R,17,FALSE)</f>
         <v>927</v>
       </c>
-      <c r="BL9" s="29">
+      <c r="BM9" s="29">
         <f>VLOOKUP($AU9,Dummy!$A:$R,18,FALSE)</f>
         <v>1105.7173678532902</v>
       </c>
     </row>
-    <row r="10" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="78" t="s">
+    <row r="10" spans="2:65" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-      <c r="V10" s="78"/>
-      <c r="W10" s="78"/>
-      <c r="X10" s="78"/>
-      <c r="Y10" s="78"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
       <c r="AU10" s="31">
         <v>7</v>
       </c>
@@ -28223,110 +28473,113 @@
         <f>VLOOKUP($AU10,Dummy!$A:$R,2,FALSE)</f>
         <v>Alemanha</v>
       </c>
-      <c r="AW10" s="28">
+      <c r="AW10" s="30">
+        <v>7</v>
+      </c>
+      <c r="AX10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,3,FALSE)</f>
         <v>23</v>
       </c>
-      <c r="AX10" s="28">
+      <c r="AY10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY10" s="28">
+      <c r="AZ10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,5,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="AZ10" s="28">
+      <c r="BA10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,6,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BA10" s="28">
+      <c r="BB10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB10" s="28">
+      <c r="BC10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,8,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BC10" s="28">
+      <c r="BD10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,9,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BD10" s="28">
+      <c r="BE10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,10,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BE10" s="28">
+      <c r="BF10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,11,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BF10" s="28">
+      <c r="BG10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,12,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="28">
+      <c r="BH10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,13,FALSE)</f>
         <v>29</v>
       </c>
-      <c r="BH10" s="28">
+      <c r="BI10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,14,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="BI10" s="29">
+      <c r="BJ10" s="29">
         <f>VLOOKUP($AU10,Dummy!$A:$R,15,FALSE)</f>
         <v>1318.181818181818</v>
       </c>
-      <c r="BJ10" s="28">
+      <c r="BK10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,16,FALSE)</f>
         <v>1110</v>
       </c>
-      <c r="BK10" s="28">
+      <c r="BL10" s="28">
         <f>VLOOKUP($AU10,Dummy!$A:$R,17,FALSE)</f>
         <v>1092</v>
       </c>
-      <c r="BL10" s="29">
+      <c r="BM10" s="29">
         <f>VLOOKUP($AU10,Dummy!$A:$R,18,FALSE)</f>
         <v>1016.4835164835164</v>
       </c>
     </row>
-    <row r="11" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
+      <c r="D11" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="76" t="s">
+      <c r="H11" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="76"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="76" t="s">
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76" t="s">
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="76"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="76" t="s">
+      <c r="R11" s="59"/>
+      <c r="S11" s="59"/>
+      <c r="T11" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U11" s="76"/>
-      <c r="V11" s="76"/>
-      <c r="W11" s="76" t="s">
+      <c r="U11" s="59"/>
+      <c r="V11" s="59"/>
+      <c r="W11" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="76"/>
-      <c r="Y11" s="76"/>
+      <c r="X11" s="59"/>
+      <c r="Y11" s="59"/>
       <c r="AA11" s="4" t="s">
         <v>38</v>
       </c>
@@ -28391,78 +28644,81 @@
         <f>VLOOKUP($AU11,Dummy!$A:$R,2,FALSE)</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="AW11" s="28">
+      <c r="AW11" s="30">
+        <v>8</v>
+      </c>
+      <c r="AX11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,3,FALSE)</f>
         <v>20</v>
       </c>
-      <c r="AX11" s="28">
+      <c r="AY11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY11" s="28">
+      <c r="AZ11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,5,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="AZ11" s="28">
+      <c r="BA11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,6,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BA11" s="28">
+      <c r="BB11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB11" s="28">
+      <c r="BC11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,8,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BC11" s="28">
+      <c r="BD11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,9,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BD11" s="28">
+      <c r="BE11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,10,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BE11" s="28">
+      <c r="BF11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,11,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BF11" s="28">
+      <c r="BG11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,12,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BG11" s="28">
+      <c r="BH11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,13,FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BH11" s="28">
+      <c r="BI11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,14,FALSE)</f>
         <v>23</v>
       </c>
-      <c r="BI11" s="29">
+      <c r="BJ11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,15,FALSE)</f>
         <v>1130.4347826086955</v>
       </c>
-      <c r="BJ11" s="28">
+      <c r="BK11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,16,FALSE)</f>
         <v>1084</v>
       </c>
-      <c r="BK11" s="28">
+      <c r="BL11" s="28">
         <f>VLOOKUP($AU11,Dummy!$A:$R,17,FALSE)</f>
         <v>1085</v>
       </c>
-      <c r="BL11" s="29">
+      <c r="BM11" s="29">
         <f>VLOOKUP($AU11,Dummy!$A:$R,18,FALSE)</f>
         <v>999.07834101382491</v>
       </c>
     </row>
-    <row r="12" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B12" s="17">
         <v>45864</v>
       </c>
       <c r="C12" s="25" t="str">
         <f>IF(AB4=0,"Vencedor Q1",AB4)</f>
-        <v>Vencedor Q1</v>
+        <v>Itália</v>
       </c>
       <c r="D12" s="56"/>
       <c r="E12" s="11" t="s">
@@ -28470,8 +28726,8 @@
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="21" t="str">
-        <f>IF(AB7=0,"Vencedor Q4",AB7)</f>
-        <v>Vencedor Q4</v>
+        <f>IF(AB5=0,"Vencedor Q4",AB5)</f>
+        <v>Polônia</v>
       </c>
       <c r="H12" s="33"/>
       <c r="I12" s="11" t="s">
@@ -28592,78 +28848,81 @@
         <f>VLOOKUP($AU12,Dummy!$A:$R,2,FALSE)</f>
         <v>França</v>
       </c>
-      <c r="AW12" s="28">
+      <c r="AW12" s="30">
+        <v>9</v>
+      </c>
+      <c r="AX12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,3,FALSE)</f>
         <v>17</v>
       </c>
-      <c r="AX12" s="28">
+      <c r="AY12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY12" s="28">
+      <c r="AZ12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,5,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AZ12" s="28">
+      <c r="BA12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,6,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BA12" s="28">
+      <c r="BB12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB12" s="28">
+      <c r="BC12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,8,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BC12" s="28">
+      <c r="BD12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,9,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BD12" s="28">
+      <c r="BE12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,10,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BE12" s="28">
+      <c r="BF12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="28">
+      <c r="BG12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,12,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BG12" s="28">
+      <c r="BH12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,13,FALSE)</f>
         <v>23</v>
       </c>
-      <c r="BH12" s="28">
+      <c r="BI12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,14,FALSE)</f>
         <v>25</v>
       </c>
-      <c r="BI12" s="29">
+      <c r="BJ12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,15,FALSE)</f>
         <v>920</v>
       </c>
-      <c r="BJ12" s="28">
+      <c r="BK12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,16,FALSE)</f>
         <v>1010</v>
       </c>
-      <c r="BK12" s="28">
+      <c r="BL12" s="28">
         <f>VLOOKUP($AU12,Dummy!$A:$R,17,FALSE)</f>
         <v>1042</v>
       </c>
-      <c r="BL12" s="29">
+      <c r="BM12" s="29">
         <f>VLOOKUP($AU12,Dummy!$A:$R,18,FALSE)</f>
         <v>969.2898272552784</v>
       </c>
     </row>
-    <row r="13" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
         <v>45864</v>
       </c>
       <c r="C13" s="25" t="str">
-        <f>IF(AB5=0,"Vencedor Q2",AB5)</f>
-        <v>Vencedor Q2</v>
+        <f>IF(AB6=0,"Vencedor Q2",AB6)</f>
+        <v>Brasil</v>
       </c>
       <c r="D13" s="56"/>
       <c r="E13" s="11" t="s">
@@ -28671,8 +28930,8 @@
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="21" t="str">
-        <f>IF(AB6=0,"Vencedor Q3",AB6)</f>
-        <v>Vencedor Q3</v>
+        <f>IF(AB7=0,"Vencedor Q3",AB7)</f>
+        <v>Japão</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="11" t="s">
@@ -28793,72 +29052,75 @@
         <f>VLOOKUP($AU13,Dummy!$A:$R,2,FALSE)</f>
         <v>Holanda</v>
       </c>
-      <c r="AW13" s="28">
+      <c r="AW13" s="30">
+        <v>10</v>
+      </c>
+      <c r="AX13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,3,FALSE)</f>
         <v>15</v>
       </c>
-      <c r="AX13" s="28">
+      <c r="AY13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY13" s="28">
+      <c r="AZ13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,5,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AZ13" s="28">
+      <c r="BA13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,6,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BA13" s="28">
+      <c r="BB13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,7,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BB13" s="28">
+      <c r="BC13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,8,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BC13" s="28">
+      <c r="BD13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,9,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BD13" s="28">
+      <c r="BE13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,10,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BE13" s="28">
+      <c r="BF13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,11,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BF13" s="28">
+      <c r="BG13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,12,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BG13" s="28">
+      <c r="BH13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,13,FALSE)</f>
         <v>19</v>
       </c>
-      <c r="BH13" s="28">
+      <c r="BI13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,14,FALSE)</f>
         <v>27</v>
       </c>
-      <c r="BI13" s="29">
+      <c r="BJ13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,15,FALSE)</f>
         <v>703.7037037037037</v>
       </c>
-      <c r="BJ13" s="28">
+      <c r="BK13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,16,FALSE)</f>
         <v>973</v>
       </c>
-      <c r="BK13" s="28">
+      <c r="BL13" s="28">
         <f>VLOOKUP($AU13,Dummy!$A:$R,17,FALSE)</f>
         <v>1029</v>
       </c>
-      <c r="BL13" s="29">
+      <c r="BM13" s="29">
         <f>VLOOKUP($AU13,Dummy!$A:$R,18,FALSE)</f>
         <v>945.5782312925171</v>
       </c>
     </row>
-    <row r="14" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU14" s="31">
         <v>11</v>
       </c>
@@ -28866,72 +29128,75 @@
         <f>VLOOKUP($AU14,Dummy!$A:$R,2,FALSE)</f>
         <v>República Tcheca</v>
       </c>
-      <c r="AW14" s="28">
+      <c r="AW14" s="30">
+        <v>11</v>
+      </c>
+      <c r="AX14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,3,FALSE)</f>
         <v>14</v>
       </c>
-      <c r="AX14" s="28">
+      <c r="AY14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY14" s="28">
+      <c r="AZ14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,5,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AZ14" s="28">
+      <c r="BA14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,6,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BA14" s="28">
+      <c r="BB14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB14" s="28">
+      <c r="BC14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC14" s="28">
+      <c r="BD14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,9,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BD14" s="28">
+      <c r="BE14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE14" s="28">
+      <c r="BF14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,11,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BF14" s="28">
+      <c r="BG14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,12,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BG14" s="28">
+      <c r="BH14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,13,FALSE)</f>
         <v>21</v>
       </c>
-      <c r="BH14" s="28">
+      <c r="BI14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,14,FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BI14" s="29">
+      <c r="BJ14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,15,FALSE)</f>
         <v>807.69230769230774</v>
       </c>
-      <c r="BJ14" s="28">
+      <c r="BK14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,16,FALSE)</f>
         <v>1032</v>
       </c>
-      <c r="BK14" s="28">
+      <c r="BL14" s="28">
         <f>VLOOKUP($AU14,Dummy!$A:$R,17,FALSE)</f>
         <v>1046</v>
       </c>
-      <c r="BL14" s="29">
+      <c r="BM14" s="29">
         <f>VLOOKUP($AU14,Dummy!$A:$R,18,FALSE)</f>
         <v>986.61567877629068</v>
       </c>
     </row>
-    <row r="15" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU15" s="31">
         <v>12</v>
       </c>
@@ -28939,72 +29204,75 @@
         <f>VLOOKUP($AU15,Dummy!$A:$R,2,FALSE)</f>
         <v>República Dominicana</v>
       </c>
-      <c r="AW15" s="28">
+      <c r="AW15" s="30">
+        <v>12</v>
+      </c>
+      <c r="AX15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,3,FALSE)</f>
         <v>13</v>
       </c>
-      <c r="AX15" s="28">
+      <c r="AY15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY15" s="28">
+      <c r="AZ15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,5,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AZ15" s="28">
+      <c r="BA15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,6,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="BA15" s="28">
+      <c r="BB15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB15" s="28">
+      <c r="BC15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BC15" s="28">
+      <c r="BD15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,9,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BD15" s="28">
+      <c r="BE15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,10,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BE15" s="28">
+      <c r="BF15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,11,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BF15" s="28">
+      <c r="BG15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,12,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BG15" s="28">
+      <c r="BH15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,13,FALSE)</f>
         <v>20</v>
       </c>
-      <c r="BH15" s="28">
+      <c r="BI15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,14,FALSE)</f>
         <v>27</v>
       </c>
-      <c r="BI15" s="29">
+      <c r="BJ15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,15,FALSE)</f>
         <v>740.74074074074065</v>
       </c>
-      <c r="BJ15" s="28">
+      <c r="BK15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,16,FALSE)</f>
         <v>1039</v>
       </c>
-      <c r="BK15" s="28">
+      <c r="BL15" s="28">
         <f>VLOOKUP($AU15,Dummy!$A:$R,17,FALSE)</f>
         <v>1086</v>
       </c>
-      <c r="BL15" s="29">
+      <c r="BM15" s="29">
         <f>VLOOKUP($AU15,Dummy!$A:$R,18,FALSE)</f>
         <v>956.72191528545125</v>
       </c>
     </row>
-    <row r="16" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU16" s="31">
         <v>13</v>
       </c>
@@ -29012,98 +29280,101 @@
         <f>VLOOKUP($AU16,Dummy!$A:$R,2,FALSE)</f>
         <v>Bulgária</v>
       </c>
-      <c r="AW16" s="28">
+      <c r="AW16" s="30">
+        <v>13</v>
+      </c>
+      <c r="AX16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,3,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AX16" s="28">
+      <c r="AY16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY16" s="28">
+      <c r="AZ16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,5,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AZ16" s="28">
+      <c r="BA16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,6,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="BA16" s="28">
+      <c r="BB16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BB16" s="28">
+      <c r="BC16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC16" s="28">
+      <c r="BD16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,9,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BD16" s="28">
+      <c r="BE16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,10,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BE16" s="28">
+      <c r="BF16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,11,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BF16" s="28">
+      <c r="BG16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,12,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BG16" s="28">
+      <c r="BH16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,13,FALSE)</f>
         <v>19</v>
       </c>
-      <c r="BH16" s="28">
+      <c r="BI16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,14,FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BI16" s="29">
+      <c r="BJ16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,15,FALSE)</f>
         <v>612.90322580645159</v>
       </c>
-      <c r="BJ16" s="28">
+      <c r="BK16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,16,FALSE)</f>
         <v>1016</v>
       </c>
-      <c r="BK16" s="28">
+      <c r="BL16" s="28">
         <f>VLOOKUP($AU16,Dummy!$A:$R,17,FALSE)</f>
         <v>1153</v>
       </c>
-      <c r="BL16" s="29">
+      <c r="BM16" s="29">
         <f>VLOOKUP($AU16,Dummy!$A:$R,18,FALSE)</f>
         <v>881.17953165654819</v>
       </c>
     </row>
-    <row r="17" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="78" t="s">
+    <row r="17" spans="2:65" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="78"/>
-      <c r="T17" s="78"/>
-      <c r="U17" s="78"/>
-      <c r="V17" s="78"/>
-      <c r="W17" s="78"/>
-      <c r="X17" s="78"/>
-      <c r="Y17" s="78"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
       <c r="AA17" s="4" t="s">
         <v>38</v>
       </c>
@@ -29168,110 +29439,113 @@
         <f>VLOOKUP($AU17,Dummy!$A:$R,2,FALSE)</f>
         <v>Bélgica</v>
       </c>
-      <c r="AW17" s="28">
+      <c r="AW17" s="30">
+        <v>14</v>
+      </c>
+      <c r="AX17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,3,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AX17" s="28">
+      <c r="AY17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY17" s="28">
+      <c r="AZ17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,5,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AZ17" s="28">
+      <c r="BA17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,6,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="BA17" s="28">
+      <c r="BB17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BB17" s="28">
+      <c r="BC17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,8,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BC17" s="28">
+      <c r="BD17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,9,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BD17" s="28">
+      <c r="BE17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BE17" s="28">
+      <c r="BF17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,11,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BF17" s="28">
+      <c r="BG17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,12,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BG17" s="28">
+      <c r="BH17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,13,FALSE)</f>
         <v>15</v>
       </c>
-      <c r="BH17" s="28">
+      <c r="BI17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,14,FALSE)</f>
         <v>29</v>
       </c>
-      <c r="BI17" s="29">
+      <c r="BJ17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,15,FALSE)</f>
         <v>517.24137931034488</v>
       </c>
-      <c r="BJ17" s="28">
+      <c r="BK17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,16,FALSE)</f>
         <v>931</v>
       </c>
-      <c r="BK17" s="28">
+      <c r="BL17" s="28">
         <f>VLOOKUP($AU17,Dummy!$A:$R,17,FALSE)</f>
         <v>1029</v>
       </c>
-      <c r="BL17" s="29">
+      <c r="BM17" s="29">
         <f>VLOOKUP($AU17,Dummy!$A:$R,18,FALSE)</f>
         <v>904.76190476190482</v>
       </c>
     </row>
-    <row r="18" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B18" s="16"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
+      <c r="D18" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76" t="s">
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76" t="s">
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="76"/>
-      <c r="P18" s="76"/>
-      <c r="Q18" s="76" t="s">
+      <c r="O18" s="59"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="76"/>
-      <c r="S18" s="76"/>
-      <c r="T18" s="76" t="s">
+      <c r="R18" s="59"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="76"/>
-      <c r="V18" s="76"/>
-      <c r="W18" s="76" t="s">
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="76"/>
-      <c r="Y18" s="76"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="59"/>
       <c r="AA18" s="4">
         <f>AD18+AE18</f>
         <v>0</v>
@@ -29355,72 +29629,75 @@
         <f>VLOOKUP($AU18,Dummy!$A:$R,2,FALSE)</f>
         <v>Sérvia</v>
       </c>
-      <c r="AW18" s="28">
+      <c r="AW18" s="30">
+        <v>15</v>
+      </c>
+      <c r="AX18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,3,FALSE)</f>
         <v>14</v>
       </c>
-      <c r="AX18" s="28">
+      <c r="AY18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY18" s="28">
+      <c r="AZ18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,5,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="AZ18" s="28">
+      <c r="BA18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,6,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="BA18" s="28">
+      <c r="BB18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,7,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BB18" s="28">
+      <c r="BC18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC18" s="28">
+      <c r="BD18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BD18" s="28">
+      <c r="BE18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,10,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="BE18" s="28">
+      <c r="BF18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF18" s="28">
+      <c r="BG18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,12,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BG18" s="28">
+      <c r="BH18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,13,FALSE)</f>
         <v>21</v>
       </c>
-      <c r="BH18" s="28">
+      <c r="BI18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,14,FALSE)</f>
         <v>28</v>
       </c>
-      <c r="BI18" s="29">
+      <c r="BJ18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,15,FALSE)</f>
         <v>750</v>
       </c>
-      <c r="BJ18" s="28">
+      <c r="BK18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,16,FALSE)</f>
         <v>1043</v>
       </c>
-      <c r="BK18" s="28">
+      <c r="BL18" s="28">
         <f>VLOOKUP($AU18,Dummy!$A:$R,17,FALSE)</f>
         <v>1068</v>
       </c>
-      <c r="BL18" s="29">
+      <c r="BM18" s="29">
         <f>VLOOKUP($AU18,Dummy!$A:$R,18,FALSE)</f>
         <v>976.59176029962543</v>
       </c>
     </row>
-    <row r="19" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B19" s="17">
         <v>45865</v>
       </c>
@@ -29480,72 +29757,75 @@
         <f>VLOOKUP($AU19,Dummy!$A:$R,2,FALSE)</f>
         <v>Canadá</v>
       </c>
-      <c r="AW19" s="28">
+      <c r="AW19" s="30">
+        <v>16</v>
+      </c>
+      <c r="AX19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,3,FALSE)</f>
         <v>10</v>
       </c>
-      <c r="AX19" s="28">
+      <c r="AY19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY19" s="28">
+      <c r="AZ19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,5,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="AZ19" s="28">
+      <c r="BA19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,6,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="BA19" s="28">
+      <c r="BB19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BB19" s="28">
+      <c r="BC19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BC19" s="28">
+      <c r="BD19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,9,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BD19" s="28">
+      <c r="BE19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,10,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="BE19" s="28">
+      <c r="BF19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF19" s="28">
+      <c r="BG19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,12,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BG19" s="28">
+      <c r="BH19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,13,FALSE)</f>
         <v>19</v>
       </c>
-      <c r="BH19" s="28">
+      <c r="BI19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,14,FALSE)</f>
         <v>33</v>
       </c>
-      <c r="BI19" s="29">
+      <c r="BJ19" s="29">
         <f>VLOOKUP($AU19,Dummy!$A:$R,15,FALSE)</f>
         <v>575.75757575757575</v>
       </c>
-      <c r="BJ19" s="28">
+      <c r="BK19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,16,FALSE)</f>
         <v>1099</v>
       </c>
-      <c r="BK19" s="28">
+      <c r="BL19" s="28">
         <f>VLOOKUP($AU19,Dummy!$A:$R,17,FALSE)</f>
         <v>1157</v>
       </c>
-      <c r="BL19" s="29">
+      <c r="BM19" s="29">
         <f>VLOOKUP($AU19,Dummy!$A:$R,18,FALSE)</f>
         <v>949.87035436473639</v>
       </c>
     </row>
-    <row r="20" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU20" s="31">
         <v>17</v>
       </c>
@@ -29553,72 +29833,75 @@
         <f>VLOOKUP($AU20,Dummy!$A:$R,2,FALSE)</f>
         <v>Tailândia</v>
       </c>
-      <c r="AW20" s="28">
+      <c r="AW20" s="30">
+        <v>17</v>
+      </c>
+      <c r="AX20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="AX20" s="28">
+      <c r="AY20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY20" s="28">
+      <c r="AZ20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,5,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="AZ20" s="28">
+      <c r="BA20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,6,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="BA20" s="28">
+      <c r="BB20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BB20" s="28">
+      <c r="BC20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BC20" s="28">
+      <c r="BD20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BD20" s="28">
+      <c r="BE20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,10,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BE20" s="28">
+      <c r="BF20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF20" s="28">
+      <c r="BG20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,12,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="BG20" s="28">
+      <c r="BH20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,13,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="BH20" s="28">
+      <c r="BI20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,14,FALSE)</f>
         <v>34</v>
       </c>
-      <c r="BI20" s="29">
+      <c r="BJ20" s="29">
         <f>VLOOKUP($AU20,Dummy!$A:$R,15,FALSE)</f>
         <v>323.52941176470591</v>
       </c>
-      <c r="BJ20" s="28">
+      <c r="BK20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,16,FALSE)</f>
         <v>948</v>
       </c>
-      <c r="BK20" s="28">
+      <c r="BL20" s="28">
         <f>VLOOKUP($AU20,Dummy!$A:$R,17,FALSE)</f>
         <v>1059</v>
       </c>
-      <c r="BL20" s="29">
+      <c r="BM20" s="29">
         <f>VLOOKUP($AU20,Dummy!$A:$R,18,FALSE)</f>
         <v>895.18413597733718</v>
       </c>
     </row>
-    <row r="21" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU21" s="31">
         <v>18</v>
       </c>
@@ -29626,104 +29909,107 @@
         <f>VLOOKUP($AU21,Dummy!$A:$R,2,FALSE)</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="AW21" s="28">
+      <c r="AW21" s="30">
+        <v>18</v>
+      </c>
+      <c r="AX21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,3,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AX21" s="28">
+      <c r="AY21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,4,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="AY21" s="28">
+      <c r="AZ21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,5,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="AZ21" s="28">
+      <c r="BA21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,6,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="BA21" s="28">
+      <c r="BB21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BB21" s="28">
+      <c r="BC21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BC21" s="28">
+      <c r="BD21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,9,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="BD21" s="28">
+      <c r="BE21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,10,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="BE21" s="28">
+      <c r="BF21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,11,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="BF21" s="28">
+      <c r="BG21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,12,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="BG21" s="28">
+      <c r="BH21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,13,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="BH21" s="28">
+      <c r="BI21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,14,FALSE)</f>
         <v>35</v>
       </c>
-      <c r="BI21" s="29">
+      <c r="BJ21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,15,FALSE)</f>
         <v>314.28571428571428</v>
       </c>
-      <c r="BJ21" s="28">
+      <c r="BK21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,16,FALSE)</f>
         <v>877</v>
       </c>
-      <c r="BK21" s="28">
+      <c r="BL21" s="28">
         <f>VLOOKUP($AU21,Dummy!$A:$R,17,FALSE)</f>
         <v>1074</v>
       </c>
-      <c r="BL21" s="29">
+      <c r="BM21" s="29">
         <f>VLOOKUP($AU21,Dummy!$A:$R,18,FALSE)</f>
         <v>816.5735567970205</v>
       </c>
     </row>
-    <row r="22" spans="2:64" x14ac:dyDescent="0.25">
-      <c r="AX22" s="53">
-        <f>SUM(AX4:AX21)</f>
+    <row r="22" spans="2:65" x14ac:dyDescent="0.25">
+      <c r="AY22" s="53">
+        <f>SUM(AY4:AY21)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
+    <row r="23" spans="2:65" ht="15" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
-      <c r="X23" s="78"/>
-      <c r="Y23" s="78"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
       <c r="AA23" s="4" t="s">
         <v>38</v>
       </c>
@@ -29781,50 +30067,51 @@
       <c r="AT23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU23" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV23" s="67"/>
+      <c r="AU23" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV23" s="73"/>
+      <c r="AW23" s="84"/>
     </row>
-    <row r="24" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B24" s="16"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
+      <c r="D24" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
       <c r="G24" s="20"/>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76" t="s">
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76" t="s">
+      <c r="L24" s="59"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
-      <c r="Q24" s="76" t="s">
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="76" t="s">
+      <c r="R24" s="59"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="76"/>
-      <c r="V24" s="76"/>
-      <c r="W24" s="76" t="s">
+      <c r="U24" s="59"/>
+      <c r="V24" s="59"/>
+      <c r="W24" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="X24" s="76"/>
-      <c r="Y24" s="76"/>
+      <c r="X24" s="59"/>
+      <c r="Y24" s="59"/>
       <c r="AA24" s="4">
         <f>AD24+AE24</f>
         <v>0</v>
@@ -29903,10 +30190,11 @@
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="7" t="s">
-        <v>89</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AW24" s="85"/>
     </row>
-    <row r="25" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
         <v>45865</v>
       </c>
@@ -29961,16 +30249,18 @@
       </c>
       <c r="AU25" s="55"/>
       <c r="AV25" s="7" t="s">
-        <v>90</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="AW25" s="85"/>
     </row>
-    <row r="26" spans="2:64" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU26" s="57"/>
       <c r="AV26" s="7" t="s">
-        <v>91</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AW26" s="85"/>
     </row>
-    <row r="27" spans="2:64" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:65" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="19"/>
       <c r="C27" s="27"/>
       <c r="D27" s="43"/>
@@ -29996,9 +30286,9 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28" spans="2:64" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="79" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C28" s="79"/>
       <c r="D28" s="44"/>
@@ -30023,14 +30313,15 @@
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
       <c r="Y28" s="39"/>
-      <c r="AU28" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV28" s="66"/>
+      <c r="AU28" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV28" s="78"/>
+      <c r="AW28" s="86"/>
     </row>
-    <row r="29" spans="2:64" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="48" t="str">
         <f>IF(AB24=0,"Campeão",AB24)</f>
@@ -30039,14 +30330,15 @@
       <c r="D29" s="45"/>
       <c r="F29" s="47"/>
       <c r="G29" s="42"/>
-      <c r="AU29" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV29" s="60"/>
+      <c r="AU29" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV29" s="65"/>
+      <c r="AW29" s="87"/>
     </row>
-    <row r="30" spans="2:64" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="49" t="str">
         <f>IF(AL24=0,"Vice",AL24)</f>
@@ -30055,14 +30347,15 @@
       <c r="D30" s="45"/>
       <c r="F30" s="47"/>
       <c r="G30" s="42"/>
-      <c r="AU30" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV30" s="62"/>
+      <c r="AU30" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV30" s="67"/>
+      <c r="AW30" s="88"/>
     </row>
-    <row r="31" spans="2:64" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:65" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="49" t="str">
         <f>IF(AB18=0,"Terceiro",AB18)</f>
@@ -30090,31 +30383,442 @@
       <c r="W31" s="41"/>
       <c r="X31" s="41"/>
       <c r="Y31" s="41"/>
-      <c r="AU31" s="61" t="s">
+      <c r="AU31" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV31" s="67"/>
+      <c r="AW31" s="88"/>
+    </row>
+    <row r="32" spans="2:65" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="81">
+        <v>4</v>
+      </c>
+      <c r="C32" s="96" t="str">
+        <f>IF(AL18=0,"",AL18)</f>
+        <v/>
+      </c>
+      <c r="AU32" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="AV31" s="62"/>
+      <c r="AV32" s="67"/>
+      <c r="AW32" s="88"/>
     </row>
-    <row r="32" spans="2:64" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AU32" s="61" t="s">
+    <row r="33" spans="2:49" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="83">
+        <v>5</v>
+      </c>
+      <c r="C33" s="95" t="str">
+        <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,1),$AK$34:$AL$37,2,FALSE),"")</f>
+        <v>China</v>
+      </c>
+      <c r="AU33" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="AV32" s="62"/>
+      <c r="AV33" s="69"/>
+      <c r="AW33" s="89"/>
     </row>
-    <row r="33" spans="2:48" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AU33" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV33" s="64"/>
+    <row r="34" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B34" s="82">
+        <v>6</v>
+      </c>
+      <c r="C34" s="80" t="str">
+        <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,2),$AK$34:$AL$37,2,FALSE),"")</f>
+        <v>Turquia</v>
+      </c>
+      <c r="AK34" s="4">
+        <f t="shared" ref="AK34:AK35" si="0">IFERROR(VLOOKUP(AL34,$AV$4:$AW$21,2,FALSE),0)</f>
+        <v>8</v>
+      </c>
+      <c r="AL34" s="4" t="str">
+        <f>AL4</f>
+        <v>Estados Unidos</v>
+      </c>
+      <c r="AM34" s="4">
+        <f>IF(AL34&lt;&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="2:48" x14ac:dyDescent="0.25">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
+    <row r="35" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B35" s="82">
+        <v>7</v>
+      </c>
+      <c r="C35" s="80" t="str">
+        <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,3),$AK$34:$AL$37,2,FALSE),"")</f>
+        <v>Alemanha</v>
+      </c>
+      <c r="AK35" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AL35" s="4" t="str">
+        <f t="shared" ref="AL35:AL36" si="1">AL6</f>
+        <v>Alemanha</v>
+      </c>
+      <c r="AM35" s="4">
+        <f t="shared" ref="AM35:AM37" si="2">IF(AL35&lt;&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B36" s="82">
+        <v>8</v>
+      </c>
+      <c r="C36" s="80" t="str">
+        <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,4),$AK$34:$AL$37,2,FALSE),"")</f>
+        <v>Estados Unidos</v>
+      </c>
+      <c r="AK36" s="4">
+        <f>IFERROR(VLOOKUP(AL36,$AV$4:$AW$21,2,FALSE),0)</f>
+        <v>6</v>
+      </c>
+      <c r="AL36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Turquia</v>
+      </c>
+      <c r="AM36" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B37" s="82">
+        <v>9</v>
+      </c>
+      <c r="C37" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B37-D37,$AU$4:AV$21,2,FALSE))</f>
+        <v>França</v>
+      </c>
+      <c r="D37" s="90">
+        <f t="shared" ref="D37:D45" si="3">IF(B37&lt;=$G$50,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK37" s="4">
+        <f>IFERROR(VLOOKUP(AL37,$AV$4:$AW$21,2,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="AL37" s="4" t="str">
+        <f>AL5</f>
+        <v>China</v>
+      </c>
+      <c r="AM37" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B38" s="82">
+        <v>10</v>
+      </c>
+      <c r="C38" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B38-D38,$AU$4:AV$21,2,FALSE))</f>
+        <v>Holanda</v>
+      </c>
+      <c r="D38" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM38" s="4">
+        <f>SUM(AM34:AM37)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B39" s="82">
+        <v>11</v>
+      </c>
+      <c r="C39" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B39-D39,$AU$4:AV$21,2,FALSE))</f>
+        <v>República Tcheca</v>
+      </c>
+      <c r="D39" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B40" s="82">
+        <v>12</v>
+      </c>
+      <c r="C40" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B40-D40,$AU$4:AV$21,2,FALSE))</f>
+        <v>República Dominicana</v>
+      </c>
+      <c r="D40" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B41" s="82">
+        <v>13</v>
+      </c>
+      <c r="C41" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B41-D41,$AU$4:AV$21,2,FALSE))</f>
+        <v>Bulgária</v>
+      </c>
+      <c r="D41" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B42" s="82">
+        <v>14</v>
+      </c>
+      <c r="C42" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B42-D42,$AU$4:AV$21,2,FALSE))</f>
+        <v>Bélgica</v>
+      </c>
+      <c r="D42" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B43" s="82">
+        <v>15</v>
+      </c>
+      <c r="C43" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B43-D43,$AU$4:AV$21,2,FALSE))</f>
+        <v>Sérvia</v>
+      </c>
+      <c r="D43" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B44" s="82">
+        <v>16</v>
+      </c>
+      <c r="C44" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B44-D44,$AU$4:AV$21,2,FALSE))</f>
+        <v>Canadá</v>
+      </c>
+      <c r="D44" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B45" s="82">
+        <v>17</v>
+      </c>
+      <c r="C45" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B45-D45,$AU$4:AV$21,2,FALSE))</f>
+        <v>Tailândia</v>
+      </c>
+      <c r="D45" s="90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="B46" s="82">
+        <v>18</v>
+      </c>
+      <c r="C46" s="80" t="str">
+        <f>IF($AY$22&lt;216,"",VLOOKUP(B46-D46,$AU$4:AV$21,2,FALSE))</f>
+        <v>Coreia do Sul</v>
+      </c>
+      <c r="D46" s="90">
+        <f>IF(B46&lt;=$G$50,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="91">
+        <v>9</v>
+      </c>
+      <c r="C50" s="92" t="str">
+        <f t="shared" ref="C50:C58" si="4">IF($AY$22&lt;216,"",AV12)</f>
+        <v>França</v>
+      </c>
+      <c r="D50" s="90">
+        <v>1</v>
+      </c>
+      <c r="E50" s="53"/>
+      <c r="F50" s="93">
+        <f>SUMIF(C50:C59,Dummy!Z1,Finais!D50:D60)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="94">
+        <f>IF(F50=1,VLOOKUP(Dummy!Z1,AV4:AW21,2,FALSE),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="91">
+        <v>10</v>
+      </c>
+      <c r="C51" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Holanda</v>
+      </c>
+      <c r="D51" s="90">
+        <v>1</v>
+      </c>
+      <c r="E51" s="53"/>
+      <c r="F51" s="93"/>
+      <c r="G51" s="94"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="91">
+        <v>11</v>
+      </c>
+      <c r="C52" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>República Tcheca</v>
+      </c>
+      <c r="D52" s="90">
+        <v>1</v>
+      </c>
+      <c r="E52" s="53"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="94"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="91">
+        <v>12</v>
+      </c>
+      <c r="C53" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>República Dominicana</v>
+      </c>
+      <c r="D53" s="90">
+        <v>1</v>
+      </c>
+      <c r="E53" s="53"/>
+      <c r="F53" s="93"/>
+      <c r="G53" s="94"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="91">
+        <v>13</v>
+      </c>
+      <c r="C54" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Bulgária</v>
+      </c>
+      <c r="D54" s="90">
+        <v>1</v>
+      </c>
+      <c r="E54" s="53"/>
+      <c r="F54" s="93"/>
+      <c r="G54" s="94"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="91">
+        <v>14</v>
+      </c>
+      <c r="C55" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Bélgica</v>
+      </c>
+      <c r="D55" s="90">
+        <v>1</v>
+      </c>
+      <c r="E55" s="53"/>
+      <c r="F55" s="93"/>
+      <c r="G55" s="94"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="91">
+        <v>15</v>
+      </c>
+      <c r="C56" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Sérvia</v>
+      </c>
+      <c r="D56" s="90">
+        <v>1</v>
+      </c>
+      <c r="E56" s="53"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="94"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="91">
+        <v>16</v>
+      </c>
+      <c r="C57" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Canadá</v>
+      </c>
+      <c r="D57" s="90">
+        <v>1</v>
+      </c>
+      <c r="E57" s="53"/>
+      <c r="F57" s="93"/>
+      <c r="G57" s="94"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="91">
+        <v>17</v>
+      </c>
+      <c r="C58" s="92" t="str">
+        <f t="shared" si="4"/>
+        <v>Tailândia</v>
+      </c>
+      <c r="D58" s="90">
+        <v>1</v>
+      </c>
+      <c r="E58" s="53"/>
+      <c r="F58" s="93"/>
+      <c r="G58" s="94"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="91">
+        <v>18</v>
+      </c>
+      <c r="C59" s="92" t="str">
+        <f>IF($AY$22&lt;216,"",AV21)</f>
+        <v>Coreia do Sul</v>
+      </c>
+      <c r="D59" s="90">
+        <v>1</v>
+      </c>
+      <c r="E59" s="53"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="94"/>
     </row>
   </sheetData>
   <sheetProtection password="CC01" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="AU29:AV29"/>
+    <mergeCell ref="AU30:AV30"/>
+    <mergeCell ref="AU31:AV31"/>
+    <mergeCell ref="AU32:AV32"/>
+    <mergeCell ref="AU33:AV33"/>
+    <mergeCell ref="W24:Y24"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="AU23:AV23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="B23:Y23"/>
+    <mergeCell ref="AU28:AV28"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="AU2:AX2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="BK2:BM2"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="B10:Y10"/>
@@ -30127,128 +30831,100 @@
     <mergeCell ref="Q3:S3"/>
     <mergeCell ref="T11:V11"/>
     <mergeCell ref="W11:Y11"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BJ2:BL2"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="W24:Y24"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="AU23:AV23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="B23:Y23"/>
-    <mergeCell ref="AU28:AV28"/>
-    <mergeCell ref="AU29:AV29"/>
-    <mergeCell ref="AU30:AV30"/>
-    <mergeCell ref="AU31:AV31"/>
-    <mergeCell ref="AU32:AV32"/>
-    <mergeCell ref="AU33:AV33"/>
   </mergeCells>
-  <conditionalFormatting sqref="T4:V7 T12:V13">
-    <cfRule type="expression" dxfId="21" priority="69">
+  <conditionalFormatting sqref="T12:V13 T4:V7">
+    <cfRule type="expression" dxfId="22" priority="70">
       <formula>$AA4&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:S7 Q12:S13">
-    <cfRule type="expression" dxfId="20" priority="68">
+  <conditionalFormatting sqref="Q12:S13 Q4:S7">
+    <cfRule type="expression" dxfId="21" priority="69">
       <formula>$AA4&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:P7 N12:P13">
-    <cfRule type="expression" dxfId="19" priority="67">
+  <conditionalFormatting sqref="N12:P13 N4:P7">
+    <cfRule type="expression" dxfId="20" priority="68">
       <formula>$AA4&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:M7 K12:M13">
-    <cfRule type="expression" dxfId="18" priority="66">
+  <conditionalFormatting sqref="K12:M13 K4:M7">
+    <cfRule type="expression" dxfId="19" priority="67">
       <formula>$AA4&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:J7 W4:Y7 H12:J13 W12:Y13">
-    <cfRule type="expression" dxfId="17" priority="65">
+  <conditionalFormatting sqref="H12:J13 W12:Y13 H4:J7 W4:Y7">
+    <cfRule type="expression" dxfId="18" priority="66">
       <formula>$AA4=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM16:XFD16 BM21:XFD22 BM2:XFD10 BM12:XFD13 BM18:XFD18 BM24:XFD38 AU3:BL20 A1:XFD1 A2:AT13 A16:A18 Z16:AT18 B17:Y19 B22:Y27 A43:A1048576 Z43:XFD1048576 B44:Y1048576 B29:Y38 A21:A38 B28 Z21:AT38 D28:Y28">
-    <cfRule type="cellIs" dxfId="16" priority="15" operator="equal">
+  <conditionalFormatting sqref="BN16:XFD16 BN21:XFD22 BN2:XFD10 BN12:XFD13 BN18:XFD18 BN24:XFD38 AU3:BM20 A1:XFD1 A16:A18 Z16:AT18 B17:Y19 B22:Y27 A43:A1048576 A21:A38 B28 D28:Y28 C36:Y36 C46:Y46 B36:B46 E44:Y45 E37:Y38 Z21:AT33 Z38:AT38 B29:Y35 AA34:AT37 Z43:XFD1048576 A2:AT13 B47:Y1048576 C37:D45">
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM11:XFD11">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+  <conditionalFormatting sqref="BN11:XFD11">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM17:XFD17">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
+  <conditionalFormatting sqref="BN17:XFD17">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM23:XFD23">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+  <conditionalFormatting sqref="BN23:XFD23">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:BL2">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+  <conditionalFormatting sqref="AU2:BM2">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV21:BL21">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="AV21:BM21">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU21:BL21">
-    <cfRule type="expression" dxfId="10" priority="2">
-      <formula>$AX$22=216</formula>
+  <conditionalFormatting sqref="AU21:BM21">
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>$AY$22=216</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T25:V25 T19:V19">
-    <cfRule type="expression" dxfId="9" priority="87">
+    <cfRule type="expression" dxfId="11" priority="88">
       <formula>$AA18&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25:S25 Q19:S19">
-    <cfRule type="expression" dxfId="8" priority="89">
+    <cfRule type="expression" dxfId="10" priority="90">
       <formula>$AA18&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25:P25 N19:P19">
-    <cfRule type="expression" dxfId="7" priority="91">
+    <cfRule type="expression" dxfId="9" priority="92">
       <formula>$AA18&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:M25 K19:M19">
-    <cfRule type="expression" dxfId="6" priority="93">
+    <cfRule type="expression" dxfId="8" priority="94">
       <formula>$AA18&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y19 H25:J25 W25:Y25 H19:J19">
-    <cfRule type="expression" dxfId="5" priority="95">
+    <cfRule type="expression" dxfId="7" priority="96">
       <formula>$AA18=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU28:AU33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Brasil"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C36">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$C33=0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -30263,8 +30939,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="8" id="{846C8833-E3D2-4ED5-A15E-097CE8650A3F}">
-            <xm:f>OR(AND($AU4=Dummy!$Z$3,$AX$22=216),AND($AU4=Dummy!$Z$4,$AX$22=216),AND($AU4=Dummy!$Z$5,$AX$22=216),AND($AU4=Dummy!$Z$6,$AX$22=216),AND($AU4=Dummy!$Z$7,$AX$22=216),AND($AU4=Dummy!$Z$8,$AX$22=216),AND($AU4=Dummy!$Z$9,$AX$22=216),)</xm:f>
+          <x14:cfRule type="expression" priority="9" id="{846C8833-E3D2-4ED5-A15E-097CE8650A3F}">
+            <xm:f>OR(AND($AU4=Dummy!$Z$3,$AY$22=216),AND($AU4=Dummy!$Z$4,$AY$22=216),AND($AU4=Dummy!$Z$5,$AY$22=216),AND($AU4=Dummy!$Z$6,$AY$22=216),AND($AU4=Dummy!$Z$7,$AY$22=216),AND($AU4=Dummy!$Z$8,$AY$22=216),AND($AU4=Dummy!$Z$9,$AY$22=216),)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -30273,7 +30949,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="9" id="{8397423E-44A1-4671-96AF-62E1881D16AF}">
+          <x14:cfRule type="expression" priority="10" id="{8397423E-44A1-4671-96AF-62E1881D16AF}">
             <xm:f>$AV4=Dummy!$Z$1</xm:f>
             <x14:dxf>
               <fill>
@@ -30283,10 +30959,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>AU4:BL20</xm:sqref>
+          <xm:sqref>AU4:BM20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" id="{67DE61A7-195A-4B56-9920-F9056EC613BB}">
+          <x14:cfRule type="expression" priority="4" id="{67DE61A7-195A-4B56-9920-F9056EC613BB}">
             <xm:f>$AV21=Dummy!$Z$1</xm:f>
             <x14:dxf>
               <fill>
@@ -30296,8 +30972,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="4" id="{4BBF20C2-EE6F-4506-BB56-D1F5587D6B07}">
-            <xm:f>OR(AND($AU21=Dummy!$Z$3,$AX$22=216),AND($AU21=Dummy!$Z$4,$AX$22=216),AND($AU21=Dummy!$Z$5,$AX$22=216),AND($AU21=Dummy!$Z$6,$AX$22=216),AND($AU21=Dummy!$Z$7,$AX$22=216),AND($AU21=Dummy!$Z$8,$AX$22=216),AND($AU21=Dummy!$Z$9,$AX$22=216),)</xm:f>
+          <x14:cfRule type="expression" priority="5" id="{4BBF20C2-EE6F-4506-BB56-D1F5587D6B07}">
+            <xm:f>OR(AND($AU21=Dummy!$Z$3,$AY$22=216),AND($AU21=Dummy!$Z$4,$AY$22=216),AND($AU21=Dummy!$Z$5,$AY$22=216),AND($AU21=Dummy!$Z$6,$AY$22=216),AND($AU21=Dummy!$Z$7,$AY$22=216),AND($AU21=Dummy!$Z$8,$AY$22=216),AND($AU21=Dummy!$Z$9,$AY$22=216),)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -30306,7 +30982,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>AU21:BL21</xm:sqref>
+          <xm:sqref>AU21:BM21</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -30315,23 +30991,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DBF2846C41E31A469E3CED25F2422E48" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0c08e4af4d80db6585ac36ba965bb3a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8c20e6-817c-474f-b9c2-eb2b1ac24837" xmlns:ns4="dc8c2798-6aba-4af7-93a4-b89253b03650" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e7db2db65f9cb533b4933096bc9b657" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
@@ -30564,32 +31223,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0F6A83-8A20-4128-AC08-526BDD0F4F5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5079BA11-B2F9-4F45-9320-B0ECAAE97A1E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="dc8c2798-6aba-4af7-93a4-b89253b03650" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1A4F3B6-8EF3-43FC-AA6E-56F4B11E76F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30606,4 +31257,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5079BA11-B2F9-4F45-9320-B0ECAAE97A1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0F6A83-8A20-4128-AC08-526BDD0F4F5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
+    <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/VNL Feminina 2025.xlsx
+++ b/VNL Feminina 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mjunior\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{193B2670-6E0D-4629-8A7F-D6F0F42BF775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4288B275-99FF-4688-BC8C-6E7ACB57CB84}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="CC01" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="1" activeTab="2" xr2:uid="{701403F6-3112-456D-B33A-FC5595D41656}"/>
@@ -857,6 +857,59 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -927,76 +980,12 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1024,6 +1013,11 @@
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1087,6 +1081,12 @@
           <bgColor rgb="FFFF9B9B"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2217,36 +2217,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58" t="s">
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58" t="s">
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
       <c r="Y1" s="1" t="s">
         <v>83</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>2</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" ref="Z4:Z20" si="9">IF(Y4&gt;=$A$16,Y4+$AA$3,Y4)</f>
+        <f t="shared" ref="Z4:Z19" si="9">IF(Y4&gt;=$A$16,Y4+$AA$3,Y4)</f>
         <v>2</v>
       </c>
     </row>
@@ -4113,36 +4113,36 @@
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="58" t="s">
+      <c r="D25" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58" t="s">
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58" t="s">
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58" t="s">
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58" t="s">
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="58"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -5138,88 +5138,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="AU2" s="74" t="s">
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="78"/>
+      <c r="AU2" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="76"/>
-      <c r="AX2" s="74" t="s">
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="93"/>
+      <c r="AX2" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="AY2" s="75"/>
-      <c r="AZ2" s="76"/>
-      <c r="BA2" s="74" t="s">
+      <c r="AY2" s="92"/>
+      <c r="AZ2" s="93"/>
+      <c r="BA2" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="BB2" s="75"/>
-      <c r="BC2" s="75"/>
-      <c r="BD2" s="75"/>
-      <c r="BE2" s="75"/>
-      <c r="BF2" s="76"/>
-      <c r="BG2" s="74" t="s">
+      <c r="BB2" s="92"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="93"/>
+      <c r="BG2" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="BH2" s="75"/>
-      <c r="BI2" s="76"/>
-      <c r="BJ2" s="74" t="s">
+      <c r="BH2" s="92"/>
+      <c r="BI2" s="93"/>
+      <c r="BJ2" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="75"/>
-      <c r="BL2" s="76"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="93"/>
     </row>
     <row r="3" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
+      <c r="B3" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
       <c r="AU3" s="32" t="s">
         <v>43</v>
       </c>
@@ -5280,42 +5280,42 @@
         <v>2</v>
       </c>
       <c r="C4" s="24"/>
-      <c r="D4" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
+      <c r="D4" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
       <c r="G4" s="20"/>
-      <c r="H4" s="59" t="s">
+      <c r="H4" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59" t="s">
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59" t="s">
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59" t="s">
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59" t="s">
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="59"/>
-      <c r="V4" s="59"/>
-      <c r="W4" s="59" t="s">
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="W4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="76"/>
       <c r="AA4" s="4" t="s">
         <v>38</v>
       </c>
@@ -8078,32 +8078,32 @@
       </c>
     </row>
     <row r="17" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="77"/>
+      <c r="S17" s="77"/>
+      <c r="T17" s="77"/>
+      <c r="U17" s="77"/>
+      <c r="V17" s="77"/>
+      <c r="W17" s="77"/>
+      <c r="X17" s="77"/>
+      <c r="Y17" s="77"/>
       <c r="AU17" s="31">
         <v>14</v>
       </c>
@@ -8181,42 +8181,42 @@
         <v>2</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
+      <c r="D18" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59" t="s">
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="59" t="s">
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="59"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59" t="s">
+      <c r="O18" s="76"/>
+      <c r="P18" s="76"/>
+      <c r="Q18" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59" t="s">
+      <c r="R18" s="76"/>
+      <c r="S18" s="76"/>
+      <c r="T18" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="59"/>
-      <c r="V18" s="59"/>
-      <c r="W18" s="59" t="s">
+      <c r="U18" s="76"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="59"/>
-      <c r="Y18" s="59"/>
+      <c r="X18" s="76"/>
+      <c r="Y18" s="76"/>
       <c r="AA18" s="4" t="s">
         <v>38</v>
       </c>
@@ -9290,10 +9290,10 @@
         <f t="shared" si="39"/>
         <v>75</v>
       </c>
-      <c r="AU23" s="73" t="s">
+      <c r="AU23" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="AV23" s="73"/>
+      <c r="AV23" s="90"/>
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
@@ -10344,78 +10344,78 @@
       </c>
     </row>
     <row r="31" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="60"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="60"/>
-      <c r="T31" s="60"/>
-      <c r="U31" s="60"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="60"/>
-      <c r="Y31" s="60"/>
-      <c r="AU31" s="77" t="s">
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="77"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="77"/>
+      <c r="R31" s="77"/>
+      <c r="S31" s="77"/>
+      <c r="T31" s="77"/>
+      <c r="U31" s="77"/>
+      <c r="V31" s="77"/>
+      <c r="W31" s="77"/>
+      <c r="X31" s="77"/>
+      <c r="Y31" s="77"/>
+      <c r="AU31" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="AV31" s="78"/>
+      <c r="AV31" s="95"/>
     </row>
     <row r="32" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="24"/>
-      <c r="D32" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
+      <c r="D32" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="59" t="s">
+      <c r="H32" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59" t="s">
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="59"/>
-      <c r="M32" s="59"/>
-      <c r="N32" s="59" t="s">
+      <c r="L32" s="76"/>
+      <c r="M32" s="76"/>
+      <c r="N32" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O32" s="59"/>
-      <c r="P32" s="59"/>
-      <c r="Q32" s="59" t="s">
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="59"/>
-      <c r="S32" s="59"/>
-      <c r="T32" s="59" t="s">
+      <c r="R32" s="76"/>
+      <c r="S32" s="76"/>
+      <c r="T32" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U32" s="59"/>
-      <c r="V32" s="59"/>
-      <c r="W32" s="59" t="s">
+      <c r="U32" s="76"/>
+      <c r="V32" s="76"/>
+      <c r="W32" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X32" s="59"/>
-      <c r="Y32" s="59"/>
+      <c r="X32" s="76"/>
+      <c r="Y32" s="76"/>
       <c r="AA32" s="4" t="s">
         <v>38</v>
       </c>
@@ -10473,10 +10473,10 @@
       <c r="AT32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU32" s="64" t="s">
+      <c r="AU32" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="AV32" s="65"/>
+      <c r="AV32" s="82"/>
     </row>
     <row r="33" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B33" s="17">
@@ -10625,10 +10625,10 @@
         <f t="shared" ref="AT33:AT44" si="60">IF(D33&lt;F33,SUM(J33,M33,P33,S33,V33),SUM(H33,K33,N33,Q33,T33))</f>
         <v>98</v>
       </c>
-      <c r="AU33" s="66" t="s">
+      <c r="AU33" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="AV33" s="67"/>
+      <c r="AV33" s="84"/>
     </row>
     <row r="34" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B34" s="17">
@@ -10773,10 +10773,10 @@
         <f t="shared" si="60"/>
         <v>76</v>
       </c>
-      <c r="AU34" s="66" t="s">
+      <c r="AU34" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="AV34" s="67"/>
+      <c r="AV34" s="84"/>
     </row>
     <row r="35" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B35" s="17">
@@ -10921,10 +10921,10 @@
         <f t="shared" si="60"/>
         <v>77</v>
       </c>
-      <c r="AU35" s="66" t="s">
+      <c r="AU35" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AV35" s="67"/>
+      <c r="AV35" s="84"/>
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B36" s="17">
@@ -11073,10 +11073,10 @@
         <f t="shared" si="60"/>
         <v>99</v>
       </c>
-      <c r="AU36" s="68" t="s">
+      <c r="AU36" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="AV36" s="69"/>
+      <c r="AV36" s="86"/>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B37" s="17">
@@ -12259,88 +12259,88 @@
       </c>
     </row>
     <row r="46" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="61"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="61"/>
-      <c r="R46" s="61"/>
-      <c r="S46" s="61"/>
-      <c r="T46" s="61"/>
-      <c r="U46" s="61"/>
-      <c r="V46" s="61"/>
-      <c r="W46" s="61"/>
-      <c r="X46" s="61"/>
-      <c r="Y46" s="61"/>
-      <c r="AU46" s="70" t="s">
+      <c r="C46" s="78"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="78"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="78"/>
+      <c r="Q46" s="78"/>
+      <c r="R46" s="78"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="78"/>
+      <c r="U46" s="78"/>
+      <c r="V46" s="78"/>
+      <c r="W46" s="78"/>
+      <c r="X46" s="78"/>
+      <c r="Y46" s="78"/>
+      <c r="AU46" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="AV46" s="71"/>
-      <c r="AW46" s="72"/>
-      <c r="AX46" s="70" t="s">
+      <c r="AV46" s="88"/>
+      <c r="AW46" s="89"/>
+      <c r="AX46" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AY46" s="71"/>
-      <c r="AZ46" s="72"/>
-      <c r="BA46" s="70" t="s">
+      <c r="AY46" s="88"/>
+      <c r="AZ46" s="89"/>
+      <c r="BA46" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="BB46" s="71"/>
-      <c r="BC46" s="71"/>
-      <c r="BD46" s="71"/>
-      <c r="BE46" s="71"/>
-      <c r="BF46" s="72"/>
-      <c r="BG46" s="70" t="s">
+      <c r="BB46" s="88"/>
+      <c r="BC46" s="88"/>
+      <c r="BD46" s="88"/>
+      <c r="BE46" s="88"/>
+      <c r="BF46" s="89"/>
+      <c r="BG46" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="BH46" s="71"/>
-      <c r="BI46" s="72"/>
-      <c r="BJ46" s="70" t="s">
+      <c r="BH46" s="88"/>
+      <c r="BI46" s="89"/>
+      <c r="BJ46" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="BK46" s="71"/>
-      <c r="BL46" s="72"/>
+      <c r="BK46" s="88"/>
+      <c r="BL46" s="89"/>
     </row>
     <row r="47" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="60"/>
-      <c r="K47" s="60"/>
-      <c r="L47" s="60"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="60"/>
-      <c r="S47" s="60"/>
-      <c r="T47" s="60"/>
-      <c r="U47" s="60"/>
-      <c r="V47" s="60"/>
-      <c r="W47" s="60"/>
-      <c r="X47" s="60"/>
-      <c r="Y47" s="60"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="77"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="77"/>
+      <c r="O47" s="77"/>
+      <c r="P47" s="77"/>
+      <c r="Q47" s="77"/>
+      <c r="R47" s="77"/>
+      <c r="S47" s="77"/>
+      <c r="T47" s="77"/>
+      <c r="U47" s="77"/>
+      <c r="V47" s="77"/>
+      <c r="W47" s="77"/>
+      <c r="X47" s="77"/>
+      <c r="Y47" s="77"/>
       <c r="AU47" s="32" t="s">
         <v>43</v>
       </c>
@@ -12401,42 +12401,42 @@
         <v>2</v>
       </c>
       <c r="C48" s="24"/>
-      <c r="D48" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="63"/>
-      <c r="F48" s="63"/>
+      <c r="D48" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
       <c r="G48" s="20"/>
-      <c r="H48" s="59" t="s">
+      <c r="H48" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I48" s="59"/>
-      <c r="J48" s="59"/>
-      <c r="K48" s="59" t="s">
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="59"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="59" t="s">
+      <c r="L48" s="76"/>
+      <c r="M48" s="76"/>
+      <c r="N48" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O48" s="59"/>
-      <c r="P48" s="59"/>
-      <c r="Q48" s="59" t="s">
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="59"/>
-      <c r="S48" s="59"/>
-      <c r="T48" s="59" t="s">
+      <c r="R48" s="76"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U48" s="59"/>
-      <c r="V48" s="59"/>
-      <c r="W48" s="59" t="s">
+      <c r="U48" s="76"/>
+      <c r="V48" s="76"/>
+      <c r="W48" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X48" s="59"/>
-      <c r="Y48" s="59"/>
+      <c r="X48" s="76"/>
+      <c r="Y48" s="76"/>
       <c r="AA48" s="4" t="s">
         <v>38</v>
       </c>
@@ -15183,32 +15183,32 @@
       </c>
     </row>
     <row r="61" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B61" s="60" t="s">
+      <c r="B61" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="60"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="62"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="60"/>
-      <c r="H61" s="60"/>
-      <c r="I61" s="60"/>
-      <c r="J61" s="60"/>
-      <c r="K61" s="60"/>
-      <c r="L61" s="60"/>
-      <c r="M61" s="60"/>
-      <c r="N61" s="60"/>
-      <c r="O61" s="60"/>
-      <c r="P61" s="60"/>
-      <c r="Q61" s="60"/>
-      <c r="R61" s="60"/>
-      <c r="S61" s="60"/>
-      <c r="T61" s="60"/>
-      <c r="U61" s="60"/>
-      <c r="V61" s="60"/>
-      <c r="W61" s="60"/>
-      <c r="X61" s="60"/>
-      <c r="Y61" s="60"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="79"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="77"/>
+      <c r="N61" s="77"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="77"/>
+      <c r="U61" s="77"/>
+      <c r="V61" s="77"/>
+      <c r="W61" s="77"/>
+      <c r="X61" s="77"/>
+      <c r="Y61" s="77"/>
       <c r="AU61" s="31">
         <v>14</v>
       </c>
@@ -15286,42 +15286,42 @@
         <v>2</v>
       </c>
       <c r="C62" s="24"/>
-      <c r="D62" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="59"/>
-      <c r="F62" s="59"/>
+      <c r="D62" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="76"/>
+      <c r="F62" s="76"/>
       <c r="G62" s="20"/>
-      <c r="H62" s="59" t="s">
+      <c r="H62" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="59"/>
-      <c r="J62" s="59"/>
-      <c r="K62" s="59" t="s">
+      <c r="I62" s="76"/>
+      <c r="J62" s="76"/>
+      <c r="K62" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="59"/>
-      <c r="M62" s="59"/>
-      <c r="N62" s="59" t="s">
+      <c r="L62" s="76"/>
+      <c r="M62" s="76"/>
+      <c r="N62" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O62" s="59"/>
-      <c r="P62" s="59"/>
-      <c r="Q62" s="59" t="s">
+      <c r="O62" s="76"/>
+      <c r="P62" s="76"/>
+      <c r="Q62" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="59"/>
-      <c r="S62" s="59"/>
-      <c r="T62" s="59" t="s">
+      <c r="R62" s="76"/>
+      <c r="S62" s="76"/>
+      <c r="T62" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U62" s="59"/>
-      <c r="V62" s="59"/>
-      <c r="W62" s="59" t="s">
+      <c r="U62" s="76"/>
+      <c r="V62" s="76"/>
+      <c r="W62" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X62" s="59"/>
-      <c r="Y62" s="59"/>
+      <c r="X62" s="76"/>
+      <c r="Y62" s="76"/>
       <c r="AA62" s="4" t="s">
         <v>38</v>
       </c>
@@ -16411,10 +16411,10 @@
         <f t="shared" si="102"/>
         <v>112</v>
       </c>
-      <c r="AU67" s="73" t="s">
+      <c r="AU67" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="AV67" s="73"/>
+      <c r="AV67" s="90"/>
     </row>
     <row r="68" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B68" s="18">
@@ -17457,78 +17457,78 @@
       </c>
     </row>
     <row r="75" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="60" t="s">
+      <c r="B75" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="60"/>
-      <c r="D75" s="60"/>
-      <c r="E75" s="60"/>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="60"/>
-      <c r="K75" s="60"/>
-      <c r="L75" s="60"/>
-      <c r="M75" s="60"/>
-      <c r="N75" s="60"/>
-      <c r="O75" s="60"/>
-      <c r="P75" s="60"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="60"/>
-      <c r="S75" s="60"/>
-      <c r="T75" s="60"/>
-      <c r="U75" s="60"/>
-      <c r="V75" s="60"/>
-      <c r="W75" s="60"/>
-      <c r="X75" s="60"/>
-      <c r="Y75" s="60"/>
-      <c r="AU75" s="77" t="s">
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="77"/>
+      <c r="F75" s="77"/>
+      <c r="G75" s="77"/>
+      <c r="H75" s="77"/>
+      <c r="I75" s="77"/>
+      <c r="J75" s="77"/>
+      <c r="K75" s="77"/>
+      <c r="L75" s="77"/>
+      <c r="M75" s="77"/>
+      <c r="N75" s="77"/>
+      <c r="O75" s="77"/>
+      <c r="P75" s="77"/>
+      <c r="Q75" s="77"/>
+      <c r="R75" s="77"/>
+      <c r="S75" s="77"/>
+      <c r="T75" s="77"/>
+      <c r="U75" s="77"/>
+      <c r="V75" s="77"/>
+      <c r="W75" s="77"/>
+      <c r="X75" s="77"/>
+      <c r="Y75" s="77"/>
+      <c r="AU75" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="AV75" s="78"/>
+      <c r="AV75" s="95"/>
     </row>
     <row r="76" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C76" s="24"/>
-      <c r="D76" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="63"/>
-      <c r="F76" s="63"/>
+      <c r="D76" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="80"/>
+      <c r="F76" s="80"/>
       <c r="G76" s="20"/>
-      <c r="H76" s="59" t="s">
+      <c r="H76" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="59"/>
-      <c r="J76" s="59"/>
-      <c r="K76" s="59" t="s">
+      <c r="I76" s="76"/>
+      <c r="J76" s="76"/>
+      <c r="K76" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L76" s="59"/>
-      <c r="M76" s="59"/>
-      <c r="N76" s="59" t="s">
+      <c r="L76" s="76"/>
+      <c r="M76" s="76"/>
+      <c r="N76" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O76" s="59"/>
-      <c r="P76" s="59"/>
-      <c r="Q76" s="59" t="s">
+      <c r="O76" s="76"/>
+      <c r="P76" s="76"/>
+      <c r="Q76" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R76" s="59"/>
-      <c r="S76" s="59"/>
-      <c r="T76" s="59" t="s">
+      <c r="R76" s="76"/>
+      <c r="S76" s="76"/>
+      <c r="T76" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U76" s="59"/>
-      <c r="V76" s="59"/>
-      <c r="W76" s="59" t="s">
+      <c r="U76" s="76"/>
+      <c r="V76" s="76"/>
+      <c r="W76" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X76" s="59"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="76"/>
+      <c r="Y76" s="76"/>
       <c r="AA76" s="4" t="s">
         <v>38</v>
       </c>
@@ -17586,10 +17586,10 @@
       <c r="AT76" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU76" s="64" t="s">
+      <c r="AU76" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="AV76" s="65"/>
+      <c r="AV76" s="82"/>
     </row>
     <row r="77" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B77" s="17">
@@ -17742,10 +17742,10 @@
         <f t="shared" ref="AT77:AT88" si="123">IF(D77&lt;F77,SUM(J77,M77,P77,S77,V77),SUM(H77,K77,N77,Q77,T77))</f>
         <v>112</v>
       </c>
-      <c r="AU77" s="66" t="s">
+      <c r="AU77" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="AV77" s="67"/>
+      <c r="AV77" s="84"/>
     </row>
     <row r="78" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B78" s="17">
@@ -17898,10 +17898,10 @@
         <f t="shared" si="123"/>
         <v>99</v>
       </c>
-      <c r="AU78" s="66" t="s">
+      <c r="AU78" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="AV78" s="67"/>
+      <c r="AV78" s="84"/>
     </row>
     <row r="79" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
@@ -18054,10 +18054,10 @@
         <f t="shared" si="123"/>
         <v>109</v>
       </c>
-      <c r="AU79" s="66" t="s">
+      <c r="AU79" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AV79" s="67"/>
+      <c r="AV79" s="84"/>
     </row>
     <row r="80" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B80" s="17">
@@ -18206,10 +18206,10 @@
         <f t="shared" si="123"/>
         <v>95</v>
       </c>
-      <c r="AU80" s="68" t="s">
+      <c r="AU80" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="AV80" s="69"/>
+      <c r="AV80" s="86"/>
     </row>
     <row r="81" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
@@ -19396,88 +19396,88 @@
       </c>
     </row>
     <row r="90" spans="2:64" ht="15" x14ac:dyDescent="0.25">
-      <c r="B90" s="61" t="s">
+      <c r="B90" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="61"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="61"/>
-      <c r="L90" s="61"/>
-      <c r="M90" s="61"/>
-      <c r="N90" s="61"/>
-      <c r="O90" s="61"/>
-      <c r="P90" s="61"/>
-      <c r="Q90" s="61"/>
-      <c r="R90" s="61"/>
-      <c r="S90" s="61"/>
-      <c r="T90" s="61"/>
-      <c r="U90" s="61"/>
-      <c r="V90" s="61"/>
-      <c r="W90" s="61"/>
-      <c r="X90" s="61"/>
-      <c r="Y90" s="61"/>
-      <c r="AU90" s="70" t="s">
+      <c r="C90" s="78"/>
+      <c r="D90" s="78"/>
+      <c r="E90" s="78"/>
+      <c r="F90" s="78"/>
+      <c r="G90" s="78"/>
+      <c r="H90" s="78"/>
+      <c r="I90" s="78"/>
+      <c r="J90" s="78"/>
+      <c r="K90" s="78"/>
+      <c r="L90" s="78"/>
+      <c r="M90" s="78"/>
+      <c r="N90" s="78"/>
+      <c r="O90" s="78"/>
+      <c r="P90" s="78"/>
+      <c r="Q90" s="78"/>
+      <c r="R90" s="78"/>
+      <c r="S90" s="78"/>
+      <c r="T90" s="78"/>
+      <c r="U90" s="78"/>
+      <c r="V90" s="78"/>
+      <c r="W90" s="78"/>
+      <c r="X90" s="78"/>
+      <c r="Y90" s="78"/>
+      <c r="AU90" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="AV90" s="71"/>
-      <c r="AW90" s="72"/>
-      <c r="AX90" s="70" t="s">
+      <c r="AV90" s="88"/>
+      <c r="AW90" s="89"/>
+      <c r="AX90" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AY90" s="71"/>
-      <c r="AZ90" s="72"/>
-      <c r="BA90" s="70" t="s">
+      <c r="AY90" s="88"/>
+      <c r="AZ90" s="89"/>
+      <c r="BA90" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="BB90" s="71"/>
-      <c r="BC90" s="71"/>
-      <c r="BD90" s="71"/>
-      <c r="BE90" s="71"/>
-      <c r="BF90" s="72"/>
-      <c r="BG90" s="70" t="s">
+      <c r="BB90" s="88"/>
+      <c r="BC90" s="88"/>
+      <c r="BD90" s="88"/>
+      <c r="BE90" s="88"/>
+      <c r="BF90" s="89"/>
+      <c r="BG90" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="BH90" s="71"/>
-      <c r="BI90" s="72"/>
-      <c r="BJ90" s="70" t="s">
+      <c r="BH90" s="88"/>
+      <c r="BI90" s="89"/>
+      <c r="BJ90" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="BK90" s="71"/>
-      <c r="BL90" s="72"/>
+      <c r="BK90" s="88"/>
+      <c r="BL90" s="89"/>
     </row>
     <row r="91" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B91" s="60" t="s">
+      <c r="B91" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="C91" s="60"/>
-      <c r="D91" s="60"/>
-      <c r="E91" s="60"/>
-      <c r="F91" s="60"/>
-      <c r="G91" s="60"/>
-      <c r="H91" s="60"/>
-      <c r="I91" s="60"/>
-      <c r="J91" s="60"/>
-      <c r="K91" s="60"/>
-      <c r="L91" s="60"/>
-      <c r="M91" s="60"/>
-      <c r="N91" s="60"/>
-      <c r="O91" s="60"/>
-      <c r="P91" s="60"/>
-      <c r="Q91" s="60"/>
-      <c r="R91" s="60"/>
-      <c r="S91" s="60"/>
-      <c r="T91" s="60"/>
-      <c r="U91" s="60"/>
-      <c r="V91" s="60"/>
-      <c r="W91" s="60"/>
-      <c r="X91" s="60"/>
-      <c r="Y91" s="60"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="77"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="77"/>
+      <c r="G91" s="77"/>
+      <c r="H91" s="77"/>
+      <c r="I91" s="77"/>
+      <c r="J91" s="77"/>
+      <c r="K91" s="77"/>
+      <c r="L91" s="77"/>
+      <c r="M91" s="77"/>
+      <c r="N91" s="77"/>
+      <c r="O91" s="77"/>
+      <c r="P91" s="77"/>
+      <c r="Q91" s="77"/>
+      <c r="R91" s="77"/>
+      <c r="S91" s="77"/>
+      <c r="T91" s="77"/>
+      <c r="U91" s="77"/>
+      <c r="V91" s="77"/>
+      <c r="W91" s="77"/>
+      <c r="X91" s="77"/>
+      <c r="Y91" s="77"/>
       <c r="AU91" s="32" t="s">
         <v>43</v>
       </c>
@@ -19538,42 +19538,42 @@
         <v>2</v>
       </c>
       <c r="C92" s="24"/>
-      <c r="D92" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
+      <c r="D92" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="80"/>
+      <c r="F92" s="80"/>
       <c r="G92" s="20"/>
-      <c r="H92" s="59" t="s">
+      <c r="H92" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59" t="s">
+      <c r="I92" s="76"/>
+      <c r="J92" s="76"/>
+      <c r="K92" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59" t="s">
+      <c r="L92" s="76"/>
+      <c r="M92" s="76"/>
+      <c r="N92" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59" t="s">
+      <c r="O92" s="76"/>
+      <c r="P92" s="76"/>
+      <c r="Q92" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59" t="s">
+      <c r="R92" s="76"/>
+      <c r="S92" s="76"/>
+      <c r="T92" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U92" s="59"/>
-      <c r="V92" s="59"/>
-      <c r="W92" s="59" t="s">
+      <c r="U92" s="76"/>
+      <c r="V92" s="76"/>
+      <c r="W92" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X92" s="59"/>
-      <c r="Y92" s="59"/>
+      <c r="X92" s="76"/>
+      <c r="Y92" s="76"/>
       <c r="AA92" s="4" t="s">
         <v>38</v>
       </c>
@@ -22316,32 +22316,32 @@
       </c>
     </row>
     <row r="105" spans="2:64" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B105" s="60" t="s">
+      <c r="B105" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C105" s="60"/>
-      <c r="D105" s="60"/>
-      <c r="E105" s="62"/>
-      <c r="F105" s="60"/>
-      <c r="G105" s="60"/>
-      <c r="H105" s="60"/>
-      <c r="I105" s="60"/>
-      <c r="J105" s="60"/>
-      <c r="K105" s="60"/>
-      <c r="L105" s="60"/>
-      <c r="M105" s="60"/>
-      <c r="N105" s="60"/>
-      <c r="O105" s="60"/>
-      <c r="P105" s="60"/>
-      <c r="Q105" s="60"/>
-      <c r="R105" s="60"/>
-      <c r="S105" s="60"/>
-      <c r="T105" s="60"/>
-      <c r="U105" s="60"/>
-      <c r="V105" s="60"/>
-      <c r="W105" s="60"/>
-      <c r="X105" s="60"/>
-      <c r="Y105" s="60"/>
+      <c r="C105" s="77"/>
+      <c r="D105" s="77"/>
+      <c r="E105" s="79"/>
+      <c r="F105" s="77"/>
+      <c r="G105" s="77"/>
+      <c r="H105" s="77"/>
+      <c r="I105" s="77"/>
+      <c r="J105" s="77"/>
+      <c r="K105" s="77"/>
+      <c r="L105" s="77"/>
+      <c r="M105" s="77"/>
+      <c r="N105" s="77"/>
+      <c r="O105" s="77"/>
+      <c r="P105" s="77"/>
+      <c r="Q105" s="77"/>
+      <c r="R105" s="77"/>
+      <c r="S105" s="77"/>
+      <c r="T105" s="77"/>
+      <c r="U105" s="77"/>
+      <c r="V105" s="77"/>
+      <c r="W105" s="77"/>
+      <c r="X105" s="77"/>
+      <c r="Y105" s="77"/>
       <c r="AU105" s="31">
         <v>14</v>
       </c>
@@ -22419,42 +22419,42 @@
         <v>2</v>
       </c>
       <c r="C106" s="24"/>
-      <c r="D106" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E106" s="59"/>
-      <c r="F106" s="59"/>
+      <c r="D106" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E106" s="76"/>
+      <c r="F106" s="76"/>
       <c r="G106" s="20"/>
-      <c r="H106" s="59" t="s">
+      <c r="H106" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I106" s="59"/>
-      <c r="J106" s="59"/>
-      <c r="K106" s="59" t="s">
+      <c r="I106" s="76"/>
+      <c r="J106" s="76"/>
+      <c r="K106" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L106" s="59"/>
-      <c r="M106" s="59"/>
-      <c r="N106" s="59" t="s">
+      <c r="L106" s="76"/>
+      <c r="M106" s="76"/>
+      <c r="N106" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O106" s="59"/>
-      <c r="P106" s="59"/>
-      <c r="Q106" s="59" t="s">
+      <c r="O106" s="76"/>
+      <c r="P106" s="76"/>
+      <c r="Q106" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R106" s="59"/>
-      <c r="S106" s="59"/>
-      <c r="T106" s="59" t="s">
+      <c r="R106" s="76"/>
+      <c r="S106" s="76"/>
+      <c r="T106" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U106" s="59"/>
-      <c r="V106" s="59"/>
-      <c r="W106" s="59" t="s">
+      <c r="U106" s="76"/>
+      <c r="V106" s="76"/>
+      <c r="W106" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X106" s="59"/>
-      <c r="Y106" s="59"/>
+      <c r="X106" s="76"/>
+      <c r="Y106" s="76"/>
       <c r="AA106" s="4" t="s">
         <v>38</v>
       </c>
@@ -23544,10 +23544,10 @@
         <f t="shared" si="165"/>
         <v>98</v>
       </c>
-      <c r="AU111" s="73" t="s">
+      <c r="AU111" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="AV111" s="73"/>
+      <c r="AV111" s="90"/>
     </row>
     <row r="112" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B112" s="18">
@@ -24610,78 +24610,78 @@
       </c>
     </row>
     <row r="119" spans="2:48" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B119" s="60" t="s">
+      <c r="B119" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="C119" s="60"/>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="60"/>
-      <c r="J119" s="60"/>
-      <c r="K119" s="60"/>
-      <c r="L119" s="60"/>
-      <c r="M119" s="60"/>
-      <c r="N119" s="60"/>
-      <c r="O119" s="60"/>
-      <c r="P119" s="60"/>
-      <c r="Q119" s="60"/>
-      <c r="R119" s="60"/>
-      <c r="S119" s="60"/>
-      <c r="T119" s="60"/>
-      <c r="U119" s="60"/>
-      <c r="V119" s="60"/>
-      <c r="W119" s="60"/>
-      <c r="X119" s="60"/>
-      <c r="Y119" s="60"/>
-      <c r="AU119" s="77" t="s">
+      <c r="C119" s="77"/>
+      <c r="D119" s="77"/>
+      <c r="E119" s="77"/>
+      <c r="F119" s="77"/>
+      <c r="G119" s="77"/>
+      <c r="H119" s="77"/>
+      <c r="I119" s="77"/>
+      <c r="J119" s="77"/>
+      <c r="K119" s="77"/>
+      <c r="L119" s="77"/>
+      <c r="M119" s="77"/>
+      <c r="N119" s="77"/>
+      <c r="O119" s="77"/>
+      <c r="P119" s="77"/>
+      <c r="Q119" s="77"/>
+      <c r="R119" s="77"/>
+      <c r="S119" s="77"/>
+      <c r="T119" s="77"/>
+      <c r="U119" s="77"/>
+      <c r="V119" s="77"/>
+      <c r="W119" s="77"/>
+      <c r="X119" s="77"/>
+      <c r="Y119" s="77"/>
+      <c r="AU119" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="AV119" s="78"/>
+      <c r="AV119" s="95"/>
     </row>
     <row r="120" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B120" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="24"/>
-      <c r="D120" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E120" s="63"/>
-      <c r="F120" s="63"/>
+      <c r="D120" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E120" s="80"/>
+      <c r="F120" s="80"/>
       <c r="G120" s="20"/>
-      <c r="H120" s="59" t="s">
+      <c r="H120" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I120" s="59"/>
-      <c r="J120" s="59"/>
-      <c r="K120" s="59" t="s">
+      <c r="I120" s="76"/>
+      <c r="J120" s="76"/>
+      <c r="K120" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L120" s="59"/>
-      <c r="M120" s="59"/>
-      <c r="N120" s="59" t="s">
+      <c r="L120" s="76"/>
+      <c r="M120" s="76"/>
+      <c r="N120" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O120" s="59"/>
-      <c r="P120" s="59"/>
-      <c r="Q120" s="59" t="s">
+      <c r="O120" s="76"/>
+      <c r="P120" s="76"/>
+      <c r="Q120" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R120" s="59"/>
-      <c r="S120" s="59"/>
-      <c r="T120" s="59" t="s">
+      <c r="R120" s="76"/>
+      <c r="S120" s="76"/>
+      <c r="T120" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U120" s="59"/>
-      <c r="V120" s="59"/>
-      <c r="W120" s="59" t="s">
+      <c r="U120" s="76"/>
+      <c r="V120" s="76"/>
+      <c r="W120" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X120" s="59"/>
-      <c r="Y120" s="59"/>
+      <c r="X120" s="76"/>
+      <c r="Y120" s="76"/>
       <c r="AA120" s="4" t="s">
         <v>38</v>
       </c>
@@ -24739,10 +24739,10 @@
       <c r="AT120" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU120" s="64" t="s">
+      <c r="AU120" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="AV120" s="65"/>
+      <c r="AV120" s="82"/>
     </row>
     <row r="121" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B121" s="17">
@@ -24891,10 +24891,10 @@
         <f t="shared" ref="AT121:AT132" si="186">IF(D121&lt;F121,SUM(J121,M121,P121,S121,V121),SUM(H121,K121,N121,Q121,T121))</f>
         <v>102</v>
       </c>
-      <c r="AU121" s="66" t="s">
+      <c r="AU121" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="AV121" s="67"/>
+      <c r="AV121" s="84"/>
     </row>
     <row r="122" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B122" s="17">
@@ -25043,10 +25043,10 @@
         <f t="shared" si="186"/>
         <v>96</v>
       </c>
-      <c r="AU122" s="66" t="s">
+      <c r="AU122" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="AV122" s="67"/>
+      <c r="AV122" s="84"/>
     </row>
     <row r="123" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B123" s="17">
@@ -25191,10 +25191,10 @@
         <f t="shared" si="186"/>
         <v>75</v>
       </c>
-      <c r="AU123" s="66" t="s">
+      <c r="AU123" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AV123" s="67"/>
+      <c r="AV123" s="84"/>
     </row>
     <row r="124" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B124" s="17">
@@ -25347,10 +25347,10 @@
         <f t="shared" si="186"/>
         <v>105</v>
       </c>
-      <c r="AU124" s="68" t="s">
+      <c r="AU124" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="AV124" s="69"/>
+      <c r="AV124" s="86"/>
     </row>
     <row r="125" spans="2:48" x14ac:dyDescent="0.25">
       <c r="B125" s="17">
@@ -27183,101 +27183,101 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:65" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="AU2" s="74" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="78"/>
+      <c r="AU2" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="76"/>
-      <c r="AY2" s="74" t="s">
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="93"/>
+      <c r="AY2" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="AZ2" s="75"/>
-      <c r="BA2" s="76"/>
-      <c r="BB2" s="74" t="s">
+      <c r="AZ2" s="92"/>
+      <c r="BA2" s="93"/>
+      <c r="BB2" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="BC2" s="75"/>
-      <c r="BD2" s="75"/>
-      <c r="BE2" s="75"/>
-      <c r="BF2" s="75"/>
-      <c r="BG2" s="76"/>
-      <c r="BH2" s="74" t="s">
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="93"/>
+      <c r="BH2" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="BI2" s="75"/>
-      <c r="BJ2" s="76"/>
-      <c r="BK2" s="74" t="s">
+      <c r="BI2" s="92"/>
+      <c r="BJ2" s="93"/>
+      <c r="BK2" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="BL2" s="75"/>
-      <c r="BM2" s="76"/>
+      <c r="BL2" s="92"/>
+      <c r="BM2" s="93"/>
     </row>
     <row r="3" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
+      <c r="D3" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
       <c r="G3" s="20"/>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59" t="s">
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59" t="s">
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59" t="s">
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59" t="s">
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="59"/>
-      <c r="V3" s="59"/>
-      <c r="W3" s="59" t="s">
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="59"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
       <c r="AA3" s="4" t="s">
         <v>38</v>
       </c>
@@ -28440,32 +28440,32 @@
       </c>
     </row>
     <row r="10" spans="2:65" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="61"/>
-      <c r="T10" s="61"/>
-      <c r="U10" s="61"/>
-      <c r="V10" s="61"/>
-      <c r="W10" s="61"/>
-      <c r="X10" s="61"/>
-      <c r="Y10" s="61"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="78"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="78"/>
+      <c r="W10" s="78"/>
+      <c r="X10" s="78"/>
+      <c r="Y10" s="78"/>
       <c r="AU10" s="31">
         <v>7</v>
       </c>
@@ -28544,42 +28544,42 @@
     <row r="11" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
+      <c r="D11" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59" t="s">
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59" t="s">
+      <c r="L11" s="76"/>
+      <c r="M11" s="76"/>
+      <c r="N11" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59" t="s">
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="59"/>
-      <c r="S11" s="59"/>
-      <c r="T11" s="59" t="s">
+      <c r="R11" s="76"/>
+      <c r="S11" s="76"/>
+      <c r="T11" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U11" s="59"/>
-      <c r="V11" s="59"/>
-      <c r="W11" s="59" t="s">
+      <c r="U11" s="76"/>
+      <c r="V11" s="76"/>
+      <c r="W11" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="59"/>
-      <c r="Y11" s="59"/>
+      <c r="X11" s="76"/>
+      <c r="Y11" s="76"/>
       <c r="AA11" s="4" t="s">
         <v>38</v>
       </c>
@@ -28720,30 +28720,46 @@
         <f>IF(AB4=0,"Vencedor Q1",AB4)</f>
         <v>Itália</v>
       </c>
-      <c r="D12" s="56"/>
+      <c r="D12" s="56">
+        <v>3</v>
+      </c>
       <c r="E12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="34"/>
+      <c r="F12" s="34">
+        <v>0</v>
+      </c>
       <c r="G12" s="21" t="str">
         <f>IF(AB5=0,"Vencedor Q4",AB5)</f>
         <v>Polônia</v>
       </c>
-      <c r="H12" s="33"/>
+      <c r="H12" s="33">
+        <v>25</v>
+      </c>
       <c r="I12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="33"/>
+      <c r="J12" s="34">
+        <v>18</v>
+      </c>
+      <c r="K12" s="33">
+        <v>25</v>
+      </c>
       <c r="L12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="34"/>
-      <c r="N12" s="33"/>
+      <c r="M12" s="34">
+        <v>16</v>
+      </c>
+      <c r="N12" s="33">
+        <v>25</v>
+      </c>
       <c r="O12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P12" s="34"/>
+      <c r="P12" s="34">
+        <v>14</v>
+      </c>
       <c r="Q12" s="33"/>
       <c r="R12" s="11" t="s">
         <v>6</v>
@@ -28756,30 +28772,30 @@
       <c r="V12" s="34"/>
       <c r="W12" s="12">
         <f>SUM(H12,K12,N12,Q12,T12)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="X12" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y12" s="14">
         <f>SUM(J12,M12,P12,S12,V12)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA12" s="4">
         <f>AD12+AE12</f>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="4" t="str">
         <f>IF(OR(D12="",F12=""),0,IF(D12&gt;F12,C12,G12))</f>
-        <v>0</v>
+        <v>Itália</v>
       </c>
       <c r="AC12" s="4">
         <f>IF(OR(D12="",F12=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" s="4">
         <f>IF(OR(D12="",F12=""),0,IF(D12&gt;F12,D12,F12))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE12" s="4">
         <f>IF(OR(D12="",F12=""),0,IF(D12&gt;F12,F12,D12))</f>
@@ -28787,7 +28803,7 @@
       </c>
       <c r="AF12" s="4">
         <f>IF(AND(AD12=3,AE12=0),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="4">
         <f>IF(AND(AD12=3,AE12=1),1,0)</f>
@@ -28799,19 +28815,19 @@
       </c>
       <c r="AI12" s="4">
         <f>IF(D12&gt;F12,SUM(H12,K12,N12,Q12,T12,),SUM(J12,M12,P12,S12,V12))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ12" s="4">
         <f>IF(D12&gt;F12,SUM(J12,M12,P12,S12,V12),SUM(H12,K12,N12,Q12,T12))</f>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="4">
+        <v>48</v>
+      </c>
+      <c r="AL12" s="4" t="str">
         <f>IF(OR(D12="",F12=""),0,IF(D12&lt;F12,C12,G12))</f>
-        <v>0</v>
+        <v>Polônia</v>
       </c>
       <c r="AM12" s="4">
         <f>IF(OR(D12="",F12=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="4">
         <f>IF(OR(D12="",F12=""),0,IF(D12&lt;F12,D12,F12))</f>
@@ -28819,7 +28835,7 @@
       </c>
       <c r="AO12" s="4">
         <f>IF(OR(D12="",F12=""),0,IF(D12&lt;F12,F12,D12))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP12" s="4">
         <f>IF(AND(AN12=2,AO12=3),1,0)</f>
@@ -28831,15 +28847,15 @@
       </c>
       <c r="AR12" s="4">
         <f>IF(AND(AN12=0,AO12=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" s="4">
         <f>IF(D12&lt;F12,SUM(H12,K12,N12,Q12,T12,),SUM(J12,M12,P12,S12,V12))</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT12" s="4">
         <f>IF(D12&lt;F12,SUM(J12,M12,P12,S12,V12),SUM(H12,K12,N12,Q12,T12))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU12" s="31">
         <v>9</v>
@@ -28924,70 +28940,94 @@
         <f>IF(AB6=0,"Vencedor Q2",AB6)</f>
         <v>Brasil</v>
       </c>
-      <c r="D13" s="56"/>
+      <c r="D13" s="56">
+        <v>3</v>
+      </c>
       <c r="E13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="34"/>
+      <c r="F13" s="34">
+        <v>2</v>
+      </c>
       <c r="G13" s="21" t="str">
         <f>IF(AB7=0,"Vencedor Q3",AB7)</f>
         <v>Japão</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="33">
+        <v>23</v>
+      </c>
       <c r="I13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="33"/>
+      <c r="J13" s="34">
+        <v>25</v>
+      </c>
+      <c r="K13" s="33">
+        <v>25</v>
+      </c>
       <c r="L13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M13" s="34"/>
-      <c r="N13" s="33"/>
+      <c r="M13" s="34">
+        <v>21</v>
+      </c>
+      <c r="N13" s="33">
+        <v>25</v>
+      </c>
       <c r="O13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="33"/>
+      <c r="P13" s="34">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>19</v>
+      </c>
       <c r="R13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S13" s="34"/>
-      <c r="T13" s="33"/>
+      <c r="S13" s="34">
+        <v>25</v>
+      </c>
+      <c r="T13" s="33">
+        <v>15</v>
+      </c>
       <c r="U13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="V13" s="34"/>
+      <c r="V13" s="34">
+        <v>8</v>
+      </c>
       <c r="W13" s="12">
         <f>SUM(H13,K13,N13,Q13,T13)</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="X13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y13" s="14">
         <f>SUM(J13,M13,P13,S13,V13)</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AA13" s="4">
         <f>AD13+AE13</f>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB13" s="4" t="str">
         <f>IF(OR(D13="",F13=""),0,IF(D13&gt;F13,C13,G13))</f>
-        <v>0</v>
+        <v>Brasil</v>
       </c>
       <c r="AC13" s="4">
         <f>IF(OR(D13="",F13=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="4">
         <f>IF(OR(D13="",F13=""),0,IF(D13&gt;F13,D13,F13))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE13" s="4">
         <f>IF(OR(D13="",F13=""),0,IF(D13&gt;F13,F13,D13))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" s="4">
         <f>IF(AND(AD13=3,AE13=0),1,0)</f>
@@ -28999,35 +29039,35 @@
       </c>
       <c r="AH13" s="4">
         <f>IF(AND(AD13=3,AE13=2),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" s="4">
         <f>IF(D13&gt;F13,SUM(H13,K13,N13,Q13,T13,),SUM(J13,M13,P13,S13,V13))</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AJ13" s="4">
         <f>IF(D13&gt;F13,SUM(J13,M13,P13,S13,V13),SUM(H13,K13,N13,Q13,T13))</f>
-        <v>0</v>
-      </c>
-      <c r="AL13" s="4">
+        <v>97</v>
+      </c>
+      <c r="AL13" s="4" t="str">
         <f>IF(OR(D13="",F13=""),0,IF(D13&lt;F13,C13,G13))</f>
-        <v>0</v>
+        <v>Japão</v>
       </c>
       <c r="AM13" s="4">
         <f>IF(OR(D13="",F13=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" s="4">
         <f>IF(OR(D13="",F13=""),0,IF(D13&lt;F13,D13,F13))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO13" s="4">
         <f>IF(OR(D13="",F13=""),0,IF(D13&lt;F13,F13,D13))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13" s="4">
         <f>IF(AND(AN13=2,AO13=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" s="4">
         <f>IF(AND(AN13=1,AO13=3),1,0)</f>
@@ -29039,11 +29079,11 @@
       </c>
       <c r="AS13" s="4">
         <f>IF(D13&lt;F13,SUM(H13,K13,N13,Q13,T13,),SUM(J13,M13,P13,S13,V13))</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT13" s="4">
         <f>IF(D13&lt;F13,SUM(J13,M13,P13,S13,V13),SUM(H13,K13,N13,Q13,T13))</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AU13" s="31">
         <v>10</v>
@@ -29349,32 +29389,32 @@
       </c>
     </row>
     <row r="17" spans="2:65" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="61"/>
-      <c r="R17" s="61"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="61"/>
-      <c r="V17" s="61"/>
-      <c r="W17" s="61"/>
-      <c r="X17" s="61"/>
-      <c r="Y17" s="61"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="78"/>
+      <c r="U17" s="78"/>
+      <c r="V17" s="78"/>
+      <c r="W17" s="78"/>
+      <c r="X17" s="78"/>
+      <c r="Y17" s="78"/>
       <c r="AA17" s="4" t="s">
         <v>38</v>
       </c>
@@ -29510,61 +29550,61 @@
     <row r="18" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B18" s="16"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
+      <c r="D18" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59" t="s">
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="59" t="s">
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="59"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59" t="s">
+      <c r="O18" s="76"/>
+      <c r="P18" s="76"/>
+      <c r="Q18" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59" t="s">
+      <c r="R18" s="76"/>
+      <c r="S18" s="76"/>
+      <c r="T18" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="59"/>
-      <c r="V18" s="59"/>
-      <c r="W18" s="59" t="s">
+      <c r="U18" s="76"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="59"/>
-      <c r="Y18" s="59"/>
+      <c r="X18" s="76"/>
+      <c r="Y18" s="76"/>
       <c r="AA18" s="4">
         <f>AD18+AE18</f>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="4" t="str">
         <f>IF(OR(D19="",F19=""),0,IF(D19&gt;F19,C19,G19))</f>
-        <v>0</v>
+        <v>Polônia</v>
       </c>
       <c r="AC18" s="4">
         <f>IF(OR(D19="",F19=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(OR(D19="",F19=""),0,IF(D19&gt;F19,D19,F19))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE18" s="4">
         <f>IF(OR(D19="",F19=""),0,IF(D19&gt;F19,F19,D19))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" s="4">
         <f>IF(AND(AD18=3,AE18=0),1,0)</f>
@@ -29572,7 +29612,7 @@
       </c>
       <c r="AG18" s="4">
         <f>IF(AND(AD18=3,AE18=1),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18" s="4">
         <f>IF(AND(AD18=3,AE18=2),1,0)</f>
@@ -29580,27 +29620,27 @@
       </c>
       <c r="AI18" s="4">
         <f>IF(D19&gt;F19,SUM(H19,K19,N19,Q19,T19,),SUM(J19,M19,P19,S19,V19))</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AJ18" s="4">
         <f>IF(D19&gt;F19,SUM(J19,M19,P19,S19,V19),SUM(H19,K19,N19,Q19,T19))</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="4">
+        <v>80</v>
+      </c>
+      <c r="AL18" s="4" t="str">
         <f>IF(OR(D19="",F19=""),0,IF(D19&lt;F19,C19,G19))</f>
-        <v>0</v>
+        <v>Japão</v>
       </c>
       <c r="AM18" s="4">
         <f>IF(OR(D19="",F19=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" s="4">
         <f>IF(OR(D19="",F19=""),0,IF(D19&lt;F19,D19,F19))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" s="4">
         <f>IF(OR(D19="",F19=""),0,IF(D19&lt;F19,F19,D19))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP18" s="4">
         <f>IF(AND(AN18=2,AO18=3),1,0)</f>
@@ -29608,7 +29648,7 @@
       </c>
       <c r="AQ18" s="4">
         <f>IF(AND(AN18=1,AO18=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" s="4">
         <f>IF(AND(AN18=0,AO18=3),1,0)</f>
@@ -29616,11 +29656,11 @@
       </c>
       <c r="AS18" s="4">
         <f>IF(D19&lt;F19,SUM(H19,K19,N19,Q19,T19,),SUM(J19,M19,P19,S19,V19))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT18" s="4">
         <f>IF(D19&lt;F19,SUM(J19,M19,P19,S19,V19),SUM(H19,K19,N19,Q19,T19))</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AU18" s="31">
         <v>15</v>
@@ -29703,37 +29743,57 @@
       </c>
       <c r="C19" s="25" t="str">
         <f>IF(AL12=0,"Perdedor S1",AL12)</f>
-        <v>Perdedor S1</v>
-      </c>
-      <c r="D19" s="56"/>
+        <v>Polônia</v>
+      </c>
+      <c r="D19" s="56">
+        <v>3</v>
+      </c>
       <c r="E19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="34"/>
+      <c r="F19" s="34">
+        <v>1</v>
+      </c>
       <c r="G19" s="21" t="str">
         <f>IF(AL13=0,"Perdedor S2",AL13)</f>
-        <v>Perdedor S2</v>
-      </c>
-      <c r="H19" s="33"/>
+        <v>Japão</v>
+      </c>
+      <c r="H19" s="33">
+        <v>25</v>
+      </c>
       <c r="I19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="33"/>
+      <c r="J19" s="34">
+        <v>15</v>
+      </c>
+      <c r="K19" s="33">
+        <v>24</v>
+      </c>
       <c r="L19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M19" s="34"/>
-      <c r="N19" s="33"/>
+      <c r="M19" s="34">
+        <v>26</v>
+      </c>
+      <c r="N19" s="33">
+        <v>25</v>
+      </c>
       <c r="O19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="33"/>
+      <c r="P19" s="34">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="33">
+        <v>25</v>
+      </c>
       <c r="R19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="34"/>
+      <c r="S19" s="34">
+        <v>23</v>
+      </c>
       <c r="T19" s="33"/>
       <c r="U19" s="11" t="s">
         <v>6</v>
@@ -29741,14 +29801,14 @@
       <c r="V19" s="34"/>
       <c r="W19" s="12">
         <f>SUM(H19,K19,N19,Q19,T19)</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="X19" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y19" s="14">
         <f>SUM(J19,M19,P19,S19,V19)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU19" s="31">
         <v>16</v>
@@ -29984,32 +30044,32 @@
       </c>
     </row>
     <row r="23" spans="2:65" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="61"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="61"/>
-      <c r="V23" s="61"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="78"/>
+      <c r="V23" s="78"/>
+      <c r="W23" s="78"/>
+      <c r="X23" s="78"/>
+      <c r="Y23" s="78"/>
       <c r="AA23" s="4" t="s">
         <v>38</v>
       </c>
@@ -30067,70 +30127,70 @@
       <c r="AT23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AU23" s="73" t="s">
+      <c r="AU23" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="AV23" s="73"/>
-      <c r="AW23" s="84"/>
+      <c r="AV23" s="90"/>
+      <c r="AW23" s="62"/>
     </row>
     <row r="24" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B24" s="16"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="D24" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
       <c r="G24" s="20"/>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59" t="s">
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="59"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="59" t="s">
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59" t="s">
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="59" t="s">
+      <c r="R24" s="76"/>
+      <c r="S24" s="76"/>
+      <c r="T24" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="59"/>
-      <c r="V24" s="59"/>
-      <c r="W24" s="59" t="s">
+      <c r="U24" s="76"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="X24" s="59"/>
-      <c r="Y24" s="59"/>
+      <c r="X24" s="76"/>
+      <c r="Y24" s="76"/>
       <c r="AA24" s="4">
         <f>AD24+AE24</f>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="4" t="str">
         <f>IF(OR(D25="",F25=""),0,IF(D25&gt;F25,C25,G25))</f>
-        <v>0</v>
+        <v>Itália</v>
       </c>
       <c r="AC24" s="4">
         <f>IF(OR(D25="",F25=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(OR(D25="",F25=""),0,IF(D25&gt;F25,D25,F25))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE24" s="4">
         <f>IF(OR(D25="",F25=""),0,IF(D25&gt;F25,F25,D25))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" s="4">
         <f>IF(AND(AD24=3,AE24=0),1,0)</f>
@@ -30138,7 +30198,7 @@
       </c>
       <c r="AG24" s="4">
         <f>IF(AND(AD24=3,AE24=1),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="4">
         <f>IF(AND(AD24=3,AE24=2),1,0)</f>
@@ -30146,27 +30206,27 @@
       </c>
       <c r="AI24" s="4">
         <f>IF(D25&gt;F25,SUM(H25,K25,N25,Q25,T25,),SUM(J25,M25,P25,S25,V25))</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AJ24" s="4">
         <f>IF(D25&gt;F25,SUM(J25,M25,P25,S25,V25),SUM(H25,K25,N25,Q25,T25))</f>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="4">
+        <v>87</v>
+      </c>
+      <c r="AL24" s="4" t="str">
         <f>IF(OR(D25="",F25=""),0,IF(D25&lt;F25,C25,G25))</f>
-        <v>0</v>
+        <v>Brasil</v>
       </c>
       <c r="AM24" s="4">
         <f>IF(OR(D25="",F25=""),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" s="4">
         <f>IF(OR(D25="",F25=""),0,IF(D25&lt;F25,D25,F25))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" s="4">
         <f>IF(OR(D25="",F25=""),0,IF(D25&lt;F25,F25,D25))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP24" s="4">
         <f>IF(AND(AN24=2,AO24=3),1,0)</f>
@@ -30174,7 +30234,7 @@
       </c>
       <c r="AQ24" s="4">
         <f>IF(AND(AN24=1,AO24=3),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" s="4">
         <f>IF(AND(AN24=0,AO24=3),1,0)</f>
@@ -30182,17 +30242,17 @@
       </c>
       <c r="AS24" s="4">
         <f>IF(D25&lt;F25,SUM(H25,K25,N25,Q25,T25,),SUM(J25,M25,P25,S25,V25))</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT24" s="4">
         <f>IF(D25&lt;F25,SUM(J25,M25,P25,S25,V25),SUM(H25,K25,N25,Q25,T25))</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AU24" s="54"/>
       <c r="AV24" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AW24" s="85"/>
+      <c r="AW24" s="63"/>
     </row>
     <row r="25" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
@@ -30200,37 +30260,57 @@
       </c>
       <c r="C25" s="25" t="str">
         <f>IF(AB12=0,"Vencedor S1",AB12)</f>
-        <v>Vencedor S1</v>
-      </c>
-      <c r="D25" s="56"/>
+        <v>Itália</v>
+      </c>
+      <c r="D25" s="56">
+        <v>3</v>
+      </c>
       <c r="E25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="34"/>
+      <c r="F25" s="34">
+        <v>1</v>
+      </c>
       <c r="G25" s="21" t="str">
         <f>IF(AB13=0,"Vencedor S2",AB13)</f>
-        <v>Vencedor S2</v>
-      </c>
-      <c r="H25" s="33"/>
+        <v>Brasil</v>
+      </c>
+      <c r="H25" s="33">
+        <v>22</v>
+      </c>
       <c r="I25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="34"/>
-      <c r="K25" s="33"/>
+      <c r="J25" s="34">
+        <v>25</v>
+      </c>
+      <c r="K25" s="33">
+        <v>25</v>
+      </c>
       <c r="L25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M25" s="34"/>
-      <c r="N25" s="33"/>
+      <c r="M25" s="34">
+        <v>18</v>
+      </c>
+      <c r="N25" s="33">
+        <v>25</v>
+      </c>
       <c r="O25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="33"/>
+      <c r="P25" s="34">
+        <v>22</v>
+      </c>
+      <c r="Q25" s="33">
+        <v>25</v>
+      </c>
       <c r="R25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S25" s="34"/>
+      <c r="S25" s="34">
+        <v>22</v>
+      </c>
       <c r="T25" s="33"/>
       <c r="U25" s="11" t="s">
         <v>6</v>
@@ -30238,27 +30318,27 @@
       <c r="V25" s="34"/>
       <c r="W25" s="12">
         <f>SUM(H25,K25,N25,Q25,T25)</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="X25" s="13" t="s">
         <v>6</v>
       </c>
       <c r="Y25" s="14">
         <f>SUM(J25,M25,P25,S25,V25)</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU25" s="55"/>
       <c r="AV25" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AW25" s="85"/>
+      <c r="AW25" s="63"/>
     </row>
     <row r="26" spans="2:65" x14ac:dyDescent="0.25">
       <c r="AU26" s="57"/>
       <c r="AV26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AW26" s="85"/>
+      <c r="AW26" s="63"/>
     </row>
     <row r="27" spans="2:65" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="19"/>
@@ -30287,10 +30367,10 @@
       <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="96" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="79"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="44"/>
       <c r="E28" s="39"/>
       <c r="F28" s="46"/>
@@ -30313,11 +30393,11 @@
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
       <c r="Y28" s="39"/>
-      <c r="AU28" s="77" t="s">
+      <c r="AU28" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="AV28" s="78"/>
-      <c r="AW28" s="86"/>
+      <c r="AV28" s="95"/>
+      <c r="AW28" s="64"/>
     </row>
     <row r="29" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="s">
@@ -30325,16 +30405,16 @@
       </c>
       <c r="C29" s="48" t="str">
         <f>IF(AB24=0,"Campeão",AB24)</f>
-        <v>Campeão</v>
+        <v>Itália</v>
       </c>
       <c r="D29" s="45"/>
       <c r="F29" s="47"/>
       <c r="G29" s="42"/>
-      <c r="AU29" s="64" t="s">
+      <c r="AU29" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="AV29" s="65"/>
-      <c r="AW29" s="87"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="65"/>
     </row>
     <row r="30" spans="2:65" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
@@ -30342,16 +30422,16 @@
       </c>
       <c r="C30" s="49" t="str">
         <f>IF(AL24=0,"Vice",AL24)</f>
-        <v>Vice</v>
+        <v>Brasil</v>
       </c>
       <c r="D30" s="45"/>
       <c r="F30" s="47"/>
       <c r="G30" s="42"/>
-      <c r="AU30" s="66" t="s">
+      <c r="AU30" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="AV30" s="67"/>
-      <c r="AW30" s="88"/>
+      <c r="AV30" s="84"/>
+      <c r="AW30" s="66"/>
     </row>
     <row r="31" spans="2:65" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="52" t="s">
@@ -30359,7 +30439,7 @@
       </c>
       <c r="C31" s="49" t="str">
         <f>IF(AB18=0,"Terceiro",AB18)</f>
-        <v>Terceiro</v>
+        <v>Polônia</v>
       </c>
       <c r="D31" s="45"/>
       <c r="E31" s="41"/>
@@ -30383,45 +30463,45 @@
       <c r="W31" s="41"/>
       <c r="X31" s="41"/>
       <c r="Y31" s="41"/>
-      <c r="AU31" s="66" t="s">
+      <c r="AU31" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="AV31" s="67"/>
-      <c r="AW31" s="88"/>
+      <c r="AV31" s="84"/>
+      <c r="AW31" s="66"/>
     </row>
     <row r="32" spans="2:65" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="81">
+      <c r="B32" s="59">
         <v>4</v>
       </c>
-      <c r="C32" s="96" t="str">
+      <c r="C32" s="74" t="str">
         <f>IF(AL18=0,"",AL18)</f>
-        <v/>
-      </c>
-      <c r="AU32" s="66" t="s">
+        <v>Japão</v>
+      </c>
+      <c r="AU32" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="AV32" s="67"/>
-      <c r="AW32" s="88"/>
+      <c r="AV32" s="84"/>
+      <c r="AW32" s="66"/>
     </row>
     <row r="33" spans="2:49" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="83">
+      <c r="B33" s="61">
         <v>5</v>
       </c>
-      <c r="C33" s="95" t="str">
+      <c r="C33" s="73" t="str">
         <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,1),$AK$34:$AL$37,2,FALSE),"")</f>
         <v>China</v>
       </c>
-      <c r="AU33" s="68" t="s">
+      <c r="AU33" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="AV33" s="69"/>
-      <c r="AW33" s="89"/>
+      <c r="AV33" s="86"/>
+      <c r="AW33" s="67"/>
     </row>
     <row r="34" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B34" s="82">
-        <v>6</v>
-      </c>
-      <c r="C34" s="80" t="str">
+      <c r="B34" s="60">
+        <v>6</v>
+      </c>
+      <c r="C34" s="58" t="str">
         <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,2),$AK$34:$AL$37,2,FALSE),"")</f>
         <v>Turquia</v>
       </c>
@@ -30439,10 +30519,10 @@
       </c>
     </row>
     <row r="35" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B35" s="82">
+      <c r="B35" s="60">
         <v>7</v>
       </c>
-      <c r="C35" s="80" t="str">
+      <c r="C35" s="58" t="str">
         <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,3),$AK$34:$AL$37,2,FALSE),"")</f>
         <v>Alemanha</v>
       </c>
@@ -30460,10 +30540,10 @@
       </c>
     </row>
     <row r="36" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B36" s="82">
+      <c r="B36" s="60">
         <v>8</v>
       </c>
-      <c r="C36" s="80" t="str">
+      <c r="C36" s="58" t="str">
         <f>IFERROR(VLOOKUP(SMALL($AK$34:$AK$37,4),$AK$34:$AL$37,2,FALSE),"")</f>
         <v>Estados Unidos</v>
       </c>
@@ -30481,14 +30561,14 @@
       </c>
     </row>
     <row r="37" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B37" s="82">
+      <c r="B37" s="60">
         <v>9</v>
       </c>
-      <c r="C37" s="80" t="str">
+      <c r="C37" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B37-D37,$AU$4:AV$21,2,FALSE))</f>
         <v>França</v>
       </c>
-      <c r="D37" s="90">
+      <c r="D37" s="68">
         <f t="shared" ref="D37:D45" si="3">IF(B37&lt;=$G$50,1,0)</f>
         <v>0</v>
       </c>
@@ -30506,14 +30586,14 @@
       </c>
     </row>
     <row r="38" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B38" s="82">
+      <c r="B38" s="60">
         <v>10</v>
       </c>
-      <c r="C38" s="80" t="str">
+      <c r="C38" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B38-D38,$AU$4:AV$21,2,FALSE))</f>
         <v>Holanda</v>
       </c>
-      <c r="D38" s="90">
+      <c r="D38" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30523,265 +30603,265 @@
       </c>
     </row>
     <row r="39" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B39" s="82">
+      <c r="B39" s="60">
         <v>11</v>
       </c>
-      <c r="C39" s="80" t="str">
+      <c r="C39" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B39-D39,$AU$4:AV$21,2,FALSE))</f>
         <v>República Tcheca</v>
       </c>
-      <c r="D39" s="90">
+      <c r="D39" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B40" s="82">
+      <c r="B40" s="60">
         <v>12</v>
       </c>
-      <c r="C40" s="80" t="str">
+      <c r="C40" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B40-D40,$AU$4:AV$21,2,FALSE))</f>
         <v>República Dominicana</v>
       </c>
-      <c r="D40" s="90">
+      <c r="D40" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B41" s="82">
+      <c r="B41" s="60">
         <v>13</v>
       </c>
-      <c r="C41" s="80" t="str">
+      <c r="C41" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B41-D41,$AU$4:AV$21,2,FALSE))</f>
         <v>Bulgária</v>
       </c>
-      <c r="D41" s="90">
+      <c r="D41" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B42" s="82">
+      <c r="B42" s="60">
         <v>14</v>
       </c>
-      <c r="C42" s="80" t="str">
+      <c r="C42" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B42-D42,$AU$4:AV$21,2,FALSE))</f>
         <v>Bélgica</v>
       </c>
-      <c r="D42" s="90">
+      <c r="D42" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B43" s="82">
+      <c r="B43" s="60">
         <v>15</v>
       </c>
-      <c r="C43" s="80" t="str">
+      <c r="C43" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B43-D43,$AU$4:AV$21,2,FALSE))</f>
         <v>Sérvia</v>
       </c>
-      <c r="D43" s="90">
+      <c r="D43" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B44" s="82">
+      <c r="B44" s="60">
         <v>16</v>
       </c>
-      <c r="C44" s="80" t="str">
+      <c r="C44" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B44-D44,$AU$4:AV$21,2,FALSE))</f>
         <v>Canadá</v>
       </c>
-      <c r="D44" s="90">
+      <c r="D44" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B45" s="82">
+      <c r="B45" s="60">
         <v>17</v>
       </c>
-      <c r="C45" s="80" t="str">
+      <c r="C45" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B45-D45,$AU$4:AV$21,2,FALSE))</f>
         <v>Tailândia</v>
       </c>
-      <c r="D45" s="90">
+      <c r="D45" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="B46" s="82">
+      <c r="B46" s="60">
         <v>18</v>
       </c>
-      <c r="C46" s="80" t="str">
+      <c r="C46" s="58" t="str">
         <f>IF($AY$22&lt;216,"",VLOOKUP(B46-D46,$AU$4:AV$21,2,FALSE))</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="D46" s="90">
+      <c r="D46" s="68">
         <f>IF(B46&lt;=$G$50,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="91">
+      <c r="B50" s="69">
         <v>9</v>
       </c>
-      <c r="C50" s="92" t="str">
+      <c r="C50" s="70" t="str">
         <f t="shared" ref="C50:C58" si="4">IF($AY$22&lt;216,"",AV12)</f>
         <v>França</v>
       </c>
-      <c r="D50" s="90">
+      <c r="D50" s="68">
         <v>1</v>
       </c>
       <c r="E50" s="53"/>
-      <c r="F50" s="93">
+      <c r="F50" s="71">
         <f>SUMIF(C50:C59,Dummy!Z1,Finais!D50:D60)</f>
         <v>0</v>
       </c>
-      <c r="G50" s="94">
+      <c r="G50" s="72">
         <f>IF(F50=1,VLOOKUP(Dummy!Z1,AV4:AW21,2,FALSE),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="91">
+      <c r="B51" s="69">
         <v>10</v>
       </c>
-      <c r="C51" s="92" t="str">
+      <c r="C51" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Holanda</v>
       </c>
-      <c r="D51" s="90">
+      <c r="D51" s="68">
         <v>1</v>
       </c>
       <c r="E51" s="53"/>
-      <c r="F51" s="93"/>
-      <c r="G51" s="94"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="72"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="91">
+      <c r="B52" s="69">
         <v>11</v>
       </c>
-      <c r="C52" s="92" t="str">
+      <c r="C52" s="70" t="str">
         <f t="shared" si="4"/>
         <v>República Tcheca</v>
       </c>
-      <c r="D52" s="90">
+      <c r="D52" s="68">
         <v>1</v>
       </c>
       <c r="E52" s="53"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="94"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="72"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="91">
+      <c r="B53" s="69">
         <v>12</v>
       </c>
-      <c r="C53" s="92" t="str">
+      <c r="C53" s="70" t="str">
         <f t="shared" si="4"/>
         <v>República Dominicana</v>
       </c>
-      <c r="D53" s="90">
+      <c r="D53" s="68">
         <v>1</v>
       </c>
       <c r="E53" s="53"/>
-      <c r="F53" s="93"/>
-      <c r="G53" s="94"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="72"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="91">
+      <c r="B54" s="69">
         <v>13</v>
       </c>
-      <c r="C54" s="92" t="str">
+      <c r="C54" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Bulgária</v>
       </c>
-      <c r="D54" s="90">
+      <c r="D54" s="68">
         <v>1</v>
       </c>
       <c r="E54" s="53"/>
-      <c r="F54" s="93"/>
-      <c r="G54" s="94"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="72"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="91">
+      <c r="B55" s="69">
         <v>14</v>
       </c>
-      <c r="C55" s="92" t="str">
+      <c r="C55" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Bélgica</v>
       </c>
-      <c r="D55" s="90">
+      <c r="D55" s="68">
         <v>1</v>
       </c>
       <c r="E55" s="53"/>
-      <c r="F55" s="93"/>
-      <c r="G55" s="94"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="72"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="91">
+      <c r="B56" s="69">
         <v>15</v>
       </c>
-      <c r="C56" s="92" t="str">
+      <c r="C56" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Sérvia</v>
       </c>
-      <c r="D56" s="90">
+      <c r="D56" s="68">
         <v>1</v>
       </c>
       <c r="E56" s="53"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="94"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="72"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="91">
+      <c r="B57" s="69">
         <v>16</v>
       </c>
-      <c r="C57" s="92" t="str">
+      <c r="C57" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Canadá</v>
       </c>
-      <c r="D57" s="90">
+      <c r="D57" s="68">
         <v>1</v>
       </c>
       <c r="E57" s="53"/>
-      <c r="F57" s="93"/>
-      <c r="G57" s="94"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="72"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="91">
+      <c r="B58" s="69">
         <v>17</v>
       </c>
-      <c r="C58" s="92" t="str">
+      <c r="C58" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Tailândia</v>
       </c>
-      <c r="D58" s="90">
+      <c r="D58" s="68">
         <v>1</v>
       </c>
       <c r="E58" s="53"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="94"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="72"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="91">
+      <c r="B59" s="69">
         <v>18</v>
       </c>
-      <c r="C59" s="92" t="str">
+      <c r="C59" s="70" t="str">
         <f>IF($AY$22&lt;216,"",AV21)</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="D59" s="90">
+      <c r="D59" s="68">
         <v>1</v>
       </c>
       <c r="E59" s="53"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="94"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="72"/>
     </row>
   </sheetData>
   <sheetProtection password="CC01" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -30858,72 +30938,72 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN16:XFD16 BN21:XFD22 BN2:XFD10 BN12:XFD13 BN18:XFD18 BN24:XFD38 AU3:BM20 A1:XFD1 A16:A18 Z16:AT18 B17:Y19 B22:Y27 A43:A1048576 A21:A38 B28 D28:Y28 C36:Y36 C46:Y46 B36:B46 E44:Y45 E37:Y38 Z21:AT33 Z38:AT38 B29:Y35 AA34:AT37 Z43:XFD1048576 A2:AT13 B47:Y1048576 C37:D45">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN11:XFD11">
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN17:XFD17">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN23:XFD23">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:BM2">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV21:BM21">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU21:BM21">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>$AY$22=216</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T25:V25 T19:V19">
-    <cfRule type="expression" dxfId="11" priority="88">
+    <cfRule type="expression" dxfId="10" priority="88">
       <formula>$AA18&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25:S25 Q19:S19">
-    <cfRule type="expression" dxfId="10" priority="90">
+    <cfRule type="expression" dxfId="9" priority="90">
       <formula>$AA18&lt;4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25:P25 N19:P19">
-    <cfRule type="expression" dxfId="9" priority="92">
+    <cfRule type="expression" dxfId="8" priority="92">
       <formula>$AA18&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:M25 K19:M19">
-    <cfRule type="expression" dxfId="8" priority="94">
+    <cfRule type="expression" dxfId="7" priority="94">
       <formula>$AA18&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19:Y19 H25:J25 W25:Y25 H19:J19">
-    <cfRule type="expression" dxfId="7" priority="96">
+    <cfRule type="expression" dxfId="6" priority="96">
       <formula>$AA18=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU28:AU33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"Brasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C36">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$C33=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31270,16 +31350,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0F6A83-8A20-4128-AC08-526BDD0F4F5D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="dc8c2798-6aba-4af7-93a4-b89253b03650"/>
     <ds:schemaRef ds:uri="2c8c20e6-817c-474f-b9c2-eb2b1ac24837"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>